--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/08 Agosto/Liquidacióncvs -agosto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_2D0D28C7D35BA60E62355476585DCE3A8746539F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD7AE208-F68C-4573-9487-AFF940E208CD}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_2D0D28C7D35BA60E62355476585DCE3A8746539F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB01D23A-A786-4BF9-8999-49D9C57F1A24}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="107">
   <si>
     <t>Producto</t>
   </si>
@@ -217,21 +217,12 @@
     <t>22%</t>
   </si>
   <si>
-    <t>52%</t>
-  </si>
-  <si>
     <t>LÃ­der Sandra Arbelaez</t>
   </si>
   <si>
     <t>SABANETA</t>
   </si>
   <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>38%</t>
-  </si>
-  <si>
     <t>Andrea  Arenas Hurtado</t>
   </si>
   <si>
@@ -244,9 +235,6 @@
     <t>71%</t>
   </si>
   <si>
-    <t>5%</t>
-  </si>
-  <si>
     <t>Luz Enith Sanchez Galeano</t>
   </si>
   <si>
@@ -281,6 +269,78 @@
   </si>
   <si>
     <t>Kelly Yuliana Ospina Saldarriaga</t>
+  </si>
+  <si>
+    <t>61%</t>
+  </si>
+  <si>
+    <t>Lider Yolima Mesa Zapata</t>
+  </si>
+  <si>
+    <t>CALDAS</t>
+  </si>
+  <si>
+    <t>68%</t>
+  </si>
+  <si>
+    <t>31%</t>
+  </si>
+  <si>
+    <t>Darinela  Chavarria Carvajal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacaciones del 4 al 19 de agosto - elabora 12 días </t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
+  </si>
+  <si>
+    <t>120%</t>
+  </si>
+  <si>
+    <t>49%</t>
+  </si>
+  <si>
+    <t>58%</t>
+  </si>
+  <si>
+    <t>54%</t>
+  </si>
+  <si>
+    <t>65%</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>Reemplaza vacaciones de Andrea 13 días</t>
+  </si>
+  <si>
+    <t>15%</t>
+  </si>
+  <si>
+    <t>6%</t>
+  </si>
+  <si>
+    <t>Lider Dayana Lopez Llorente</t>
+  </si>
+  <si>
+    <t>SEGOVIA</t>
+  </si>
+  <si>
+    <t>Elabora hasta el 22 , elabora 17 días  meta puntos 623</t>
+  </si>
+  <si>
+    <t>117%</t>
+  </si>
+  <si>
+    <t>Luisa Fernanda Miranda Rodriguez</t>
+  </si>
+  <si>
+    <t>42%</t>
   </si>
 </sst>
 </file>
@@ -644,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -3021,22 +3081,22 @@
         <v>12</v>
       </c>
       <c r="B68">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C68">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D68" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E68" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F68" t="s">
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
@@ -3048,7 +3108,7 @@
         <v>100</v>
       </c>
       <c r="L68">
-        <v>35.299999999999997</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3056,22 +3116,22 @@
         <v>20</v>
       </c>
       <c r="B69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="E69" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F69" t="s">
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -3083,7 +3143,7 @@
         <v>100</v>
       </c>
       <c r="L69">
-        <v>35.299999999999997</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3091,22 +3151,22 @@
         <v>21</v>
       </c>
       <c r="B70">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C70">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E70" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F70" t="s">
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -3118,7 +3178,7 @@
         <v>100</v>
       </c>
       <c r="L70">
-        <v>35.299999999999997</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3126,22 +3186,22 @@
         <v>22</v>
       </c>
       <c r="B71">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C71">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D71" t="s">
         <v>23</v>
       </c>
       <c r="E71" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F71" t="s">
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -3153,7 +3213,7 @@
         <v>100</v>
       </c>
       <c r="L71">
-        <v>35.299999999999997</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3161,7 +3221,7 @@
         <v>24</v>
       </c>
       <c r="B72">
-        <v>600</v>
+        <v>497</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3170,13 +3230,13 @@
         <v>13</v>
       </c>
       <c r="E72" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F72" t="s">
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -3188,7 +3248,7 @@
         <v>100</v>
       </c>
       <c r="L72">
-        <v>35.299999999999997</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3196,7 +3256,7 @@
         <v>25</v>
       </c>
       <c r="B73">
-        <v>1600000</v>
+        <v>1490786</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3205,13 +3265,13 @@
         <v>13</v>
       </c>
       <c r="E73" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F73" t="s">
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -3223,7 +3283,7 @@
         <v>100</v>
       </c>
       <c r="L73">
-        <v>35.299999999999997</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3231,22 +3291,22 @@
         <v>12</v>
       </c>
       <c r="B74">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C74">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D74" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="E74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F74" t="s">
         <v>28</v>
       </c>
       <c r="G74" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -3255,13 +3315,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K74">
         <v>100</v>
       </c>
       <c r="L74">
-        <v>67.8</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3269,22 +3329,22 @@
         <v>20</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D75" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
       </c>
       <c r="G75" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -3296,7 +3356,7 @@
         <v>100</v>
       </c>
       <c r="L75">
-        <v>67.8</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3304,22 +3364,22 @@
         <v>21</v>
       </c>
       <c r="B76">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C76">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
       </c>
       <c r="G76" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -3331,7 +3391,7 @@
         <v>100</v>
       </c>
       <c r="L76">
-        <v>67.8</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3339,23 +3399,23 @@
         <v>22</v>
       </c>
       <c r="B77">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C77">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D77" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" t="s">
+        <v>71</v>
+      </c>
+      <c r="F77" t="s">
+        <v>28</v>
+      </c>
+      <c r="G77" t="s">
         <v>73</v>
       </c>
-      <c r="E77" t="s">
-        <v>70</v>
-      </c>
-      <c r="F77" t="s">
-        <v>28</v>
-      </c>
-      <c r="G77" t="s">
-        <v>67</v>
-      </c>
       <c r="H77" t="s">
         <v>17</v>
       </c>
@@ -3366,7 +3426,7 @@
         <v>100</v>
       </c>
       <c r="L77">
-        <v>67.8</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -3374,7 +3434,7 @@
         <v>24</v>
       </c>
       <c r="B78">
-        <v>413</v>
+        <v>258</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3383,13 +3443,13 @@
         <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
       </c>
       <c r="G78" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -3401,7 +3461,7 @@
         <v>100</v>
       </c>
       <c r="L78">
-        <v>67.8</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -3409,7 +3469,7 @@
         <v>25</v>
       </c>
       <c r="B79">
-        <v>1100000</v>
+        <v>773357</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3418,13 +3478,13 @@
         <v>13</v>
       </c>
       <c r="E79" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
       </c>
       <c r="G79" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -3436,7 +3496,7 @@
         <v>100</v>
       </c>
       <c r="L79">
-        <v>67.8</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -3444,22 +3504,22 @@
         <v>12</v>
       </c>
       <c r="B80">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E80" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
       </c>
       <c r="G80" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -3471,7 +3531,7 @@
         <v>100</v>
       </c>
       <c r="L80">
-        <v>2.2999999999999998</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -3479,22 +3539,22 @@
         <v>20</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C81">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D81" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="E81" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
       </c>
       <c r="G81" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -3506,7 +3566,7 @@
         <v>100</v>
       </c>
       <c r="L81">
-        <v>2.2999999999999998</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -3514,22 +3574,22 @@
         <v>21</v>
       </c>
       <c r="B82">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D82" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="E82" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
       </c>
       <c r="G82" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -3541,7 +3601,7 @@
         <v>100</v>
       </c>
       <c r="L82">
-        <v>2.2999999999999998</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -3549,22 +3609,22 @@
         <v>22</v>
       </c>
       <c r="B83">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
       </c>
       <c r="E83" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
       </c>
       <c r="G83" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -3576,7 +3636,7 @@
         <v>100</v>
       </c>
       <c r="L83">
-        <v>2.2999999999999998</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -3584,7 +3644,7 @@
         <v>24</v>
       </c>
       <c r="B84">
-        <v>488</v>
+        <v>745</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3593,13 +3653,13 @@
         <v>13</v>
       </c>
       <c r="E84" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
       </c>
       <c r="G84" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -3611,7 +3671,7 @@
         <v>100</v>
       </c>
       <c r="L84">
-        <v>2.2999999999999998</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3619,7 +3679,7 @@
         <v>25</v>
       </c>
       <c r="B85">
-        <v>1300000</v>
+        <v>2235857</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -3628,13 +3688,13 @@
         <v>13</v>
       </c>
       <c r="E85" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
       </c>
       <c r="G85" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
@@ -3646,7 +3706,7 @@
         <v>100</v>
       </c>
       <c r="L85">
-        <v>2.2999999999999998</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -3654,22 +3714,22 @@
         <v>12</v>
       </c>
       <c r="B86">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C86">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D86" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="E86" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F86" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G86" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
@@ -3681,7 +3741,7 @@
         <v>100</v>
       </c>
       <c r="L86">
-        <v>38.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -3689,22 +3749,22 @@
         <v>20</v>
       </c>
       <c r="B87">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="E87" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F87" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G87" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -3716,7 +3776,7 @@
         <v>100</v>
       </c>
       <c r="L87">
-        <v>38.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -3724,22 +3784,22 @@
         <v>21</v>
       </c>
       <c r="B88">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C88">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F88" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G88" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -3751,7 +3811,7 @@
         <v>100</v>
       </c>
       <c r="L88">
-        <v>38.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -3759,22 +3819,22 @@
         <v>22</v>
       </c>
       <c r="B89">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C89">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D89" t="s">
         <v>23</v>
       </c>
       <c r="E89" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F89" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G89" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -3786,7 +3846,7 @@
         <v>100</v>
       </c>
       <c r="L89">
-        <v>38.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -3794,7 +3854,7 @@
         <v>24</v>
       </c>
       <c r="B90">
-        <v>497</v>
+        <v>563</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -3803,13 +3863,13 @@
         <v>13</v>
       </c>
       <c r="E90" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F90" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G90" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -3821,7 +3881,7 @@
         <v>100</v>
       </c>
       <c r="L90">
-        <v>38.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -3829,7 +3889,7 @@
         <v>25</v>
       </c>
       <c r="B91">
-        <v>1490786</v>
+        <v>1687500</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -3838,13 +3898,13 @@
         <v>13</v>
       </c>
       <c r="E91" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F91" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="G91" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -3856,7 +3916,7 @@
         <v>100</v>
       </c>
       <c r="L91">
-        <v>38.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -3864,22 +3924,22 @@
         <v>12</v>
       </c>
       <c r="B92">
+        <v>23</v>
+      </c>
+      <c r="C92">
         <v>14</v>
       </c>
-      <c r="C92">
-        <v>9</v>
-      </c>
       <c r="D92" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E92" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F92" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -3887,14 +3947,11 @@
       <c r="I92" t="s">
         <v>18</v>
       </c>
-      <c r="J92" t="s">
-        <v>80</v>
-      </c>
       <c r="K92">
         <v>100</v>
       </c>
       <c r="L92">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -3905,19 +3962,19 @@
         <v>3</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E93" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F93" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -3929,7 +3986,7 @@
         <v>100</v>
       </c>
       <c r="L93">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -3937,22 +3994,22 @@
         <v>21</v>
       </c>
       <c r="B94">
+        <v>41</v>
+      </c>
+      <c r="C94">
+        <v>28</v>
+      </c>
+      <c r="D94" t="s">
+        <v>86</v>
+      </c>
+      <c r="E94" t="s">
+        <v>84</v>
+      </c>
+      <c r="F94" t="s">
         <v>15</v>
       </c>
-      <c r="C94">
-        <v>13</v>
-      </c>
-      <c r="D94" t="s">
-        <v>81</v>
-      </c>
-      <c r="E94" t="s">
-        <v>75</v>
-      </c>
-      <c r="F94" t="s">
-        <v>28</v>
-      </c>
       <c r="G94" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -3964,7 +4021,7 @@
         <v>100</v>
       </c>
       <c r="L94">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -3972,22 +4029,22 @@
         <v>22</v>
       </c>
       <c r="B95">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C95">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="D95" t="s">
         <v>23</v>
       </c>
       <c r="E95" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F95" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -3999,7 +4056,7 @@
         <v>100</v>
       </c>
       <c r="L95">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4007,7 +4064,7 @@
         <v>24</v>
       </c>
       <c r="B96">
-        <v>258</v>
+        <v>487</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4016,13 +4073,13 @@
         <v>13</v>
       </c>
       <c r="E96" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F96" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -4034,7 +4091,7 @@
         <v>100</v>
       </c>
       <c r="L96">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4042,22 +4099,22 @@
         <v>25</v>
       </c>
       <c r="B97">
-        <v>773357</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>4138900</v>
       </c>
       <c r="D97" t="s">
         <v>13</v>
       </c>
       <c r="E97" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F97" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -4069,7 +4126,7 @@
         <v>100</v>
       </c>
       <c r="L97">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4077,22 +4134,22 @@
         <v>12</v>
       </c>
       <c r="B98">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C98">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D98" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E98" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F98" t="s">
         <v>28</v>
       </c>
       <c r="G98" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -4100,11 +4157,14 @@
       <c r="I98" t="s">
         <v>18</v>
       </c>
+      <c r="J98" t="s">
+        <v>89</v>
+      </c>
       <c r="K98">
         <v>100</v>
       </c>
       <c r="L98">
-        <v>22.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4112,22 +4172,22 @@
         <v>20</v>
       </c>
       <c r="B99">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C99">
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>84</v>
+        <v>33</v>
       </c>
       <c r="E99" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F99" t="s">
         <v>28</v>
       </c>
       <c r="G99" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -4139,7 +4199,7 @@
         <v>100</v>
       </c>
       <c r="L99">
-        <v>22.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4147,23 +4207,23 @@
         <v>21</v>
       </c>
       <c r="B100">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C100">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D100" t="s">
+        <v>90</v>
+      </c>
+      <c r="E100" t="s">
+        <v>88</v>
+      </c>
+      <c r="F100" t="s">
+        <v>28</v>
+      </c>
+      <c r="G100" t="s">
         <v>85</v>
       </c>
-      <c r="E100" t="s">
-        <v>83</v>
-      </c>
-      <c r="F100" t="s">
-        <v>28</v>
-      </c>
-      <c r="G100" t="s">
-        <v>77</v>
-      </c>
       <c r="H100" t="s">
         <v>17</v>
       </c>
@@ -4174,7 +4234,7 @@
         <v>100</v>
       </c>
       <c r="L100">
-        <v>22.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4182,22 +4242,22 @@
         <v>22</v>
       </c>
       <c r="B101">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="C101">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D101" t="s">
         <v>23</v>
       </c>
       <c r="E101" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F101" t="s">
         <v>28</v>
       </c>
       <c r="G101" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -4209,7 +4269,7 @@
         <v>100</v>
       </c>
       <c r="L101">
-        <v>22.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4217,7 +4277,7 @@
         <v>24</v>
       </c>
       <c r="B102">
-        <v>745</v>
+        <v>281</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -4226,13 +4286,13 @@
         <v>13</v>
       </c>
       <c r="E102" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F102" t="s">
         <v>28</v>
       </c>
       <c r="G102" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -4244,7 +4304,7 @@
         <v>100</v>
       </c>
       <c r="L102">
-        <v>22.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4252,7 +4312,7 @@
         <v>25</v>
       </c>
       <c r="B103">
-        <v>2235857</v>
+        <v>0</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -4261,13 +4321,13 @@
         <v>13</v>
       </c>
       <c r="E103" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F103" t="s">
         <v>28</v>
       </c>
       <c r="G103" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -4279,7 +4339,7 @@
         <v>100</v>
       </c>
       <c r="L103">
-        <v>22.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4287,22 +4347,22 @@
         <v>12</v>
       </c>
       <c r="B104">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D104" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E104" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F104" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G104" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -4314,7 +4374,7 @@
         <v>100</v>
       </c>
       <c r="L104">
-        <v>0.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4322,22 +4382,22 @@
         <v>20</v>
       </c>
       <c r="B105">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="E105" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F105" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G105" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -4349,7 +4409,7 @@
         <v>100</v>
       </c>
       <c r="L105">
-        <v>0.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4357,22 +4417,22 @@
         <v>21</v>
       </c>
       <c r="B106">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D106" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="E106" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F106" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G106" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -4384,7 +4444,7 @@
         <v>100</v>
       </c>
       <c r="L106">
-        <v>0.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4392,22 +4452,22 @@
         <v>22</v>
       </c>
       <c r="B107">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="C107">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="D107" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="E107" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F107" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G107" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -4419,7 +4479,7 @@
         <v>100</v>
       </c>
       <c r="L107">
-        <v>0.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4427,7 +4487,7 @@
         <v>24</v>
       </c>
       <c r="B108">
-        <v>563</v>
+        <v>731</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -4436,13 +4496,13 @@
         <v>13</v>
       </c>
       <c r="E108" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F108" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -4454,7 +4514,7 @@
         <v>100</v>
       </c>
       <c r="L108">
-        <v>0.5</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4462,7 +4522,7 @@
         <v>25</v>
       </c>
       <c r="B109">
-        <v>1687500</v>
+        <v>0</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -4471,13 +4531,13 @@
         <v>13</v>
       </c>
       <c r="E109" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F109" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G109" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -4489,7 +4549,1066 @@
         <v>100</v>
       </c>
       <c r="L109">
-        <v>0.5</v>
+        <v>51.1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110">
+        <v>25</v>
+      </c>
+      <c r="C110">
+        <v>16</v>
+      </c>
+      <c r="D110" t="s">
+        <v>75</v>
+      </c>
+      <c r="E110" t="s">
+        <v>65</v>
+      </c>
+      <c r="F110" t="s">
+        <v>15</v>
+      </c>
+      <c r="G110" t="s">
+        <v>66</v>
+      </c>
+      <c r="H110" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110" t="s">
+        <v>18</v>
+      </c>
+      <c r="K110">
+        <v>100</v>
+      </c>
+      <c r="L110">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>20</v>
+      </c>
+      <c r="B111">
+        <v>6</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+      <c r="D111" t="s">
+        <v>29</v>
+      </c>
+      <c r="E111" t="s">
+        <v>65</v>
+      </c>
+      <c r="F111" t="s">
+        <v>15</v>
+      </c>
+      <c r="G111" t="s">
+        <v>66</v>
+      </c>
+      <c r="H111" t="s">
+        <v>17</v>
+      </c>
+      <c r="I111" t="s">
+        <v>18</v>
+      </c>
+      <c r="K111">
+        <v>100</v>
+      </c>
+      <c r="L111">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>21</v>
+      </c>
+      <c r="B112">
+        <v>24</v>
+      </c>
+      <c r="C112">
+        <v>13</v>
+      </c>
+      <c r="D112" t="s">
+        <v>95</v>
+      </c>
+      <c r="E112" t="s">
+        <v>65</v>
+      </c>
+      <c r="F112" t="s">
+        <v>15</v>
+      </c>
+      <c r="G112" t="s">
+        <v>66</v>
+      </c>
+      <c r="H112" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" t="s">
+        <v>18</v>
+      </c>
+      <c r="K112">
+        <v>100</v>
+      </c>
+      <c r="L112">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>22</v>
+      </c>
+      <c r="B113">
+        <v>84</v>
+      </c>
+      <c r="C113">
+        <v>39</v>
+      </c>
+      <c r="D113" t="s">
+        <v>23</v>
+      </c>
+      <c r="E113" t="s">
+        <v>65</v>
+      </c>
+      <c r="F113" t="s">
+        <v>15</v>
+      </c>
+      <c r="G113" t="s">
+        <v>66</v>
+      </c>
+      <c r="H113" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113" t="s">
+        <v>18</v>
+      </c>
+      <c r="K113">
+        <v>100</v>
+      </c>
+      <c r="L113">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>24</v>
+      </c>
+      <c r="B114">
+        <v>600</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="s">
+        <v>65</v>
+      </c>
+      <c r="F114" t="s">
+        <v>15</v>
+      </c>
+      <c r="G114" t="s">
+        <v>66</v>
+      </c>
+      <c r="H114" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114" t="s">
+        <v>18</v>
+      </c>
+      <c r="K114">
+        <v>100</v>
+      </c>
+      <c r="L114">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>25</v>
+      </c>
+      <c r="B115">
+        <v>1600000</v>
+      </c>
+      <c r="C115">
+        <v>1067900</v>
+      </c>
+      <c r="D115" t="s">
+        <v>49</v>
+      </c>
+      <c r="E115" t="s">
+        <v>65</v>
+      </c>
+      <c r="F115" t="s">
+        <v>15</v>
+      </c>
+      <c r="G115" t="s">
+        <v>66</v>
+      </c>
+      <c r="H115" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115" t="s">
+        <v>18</v>
+      </c>
+      <c r="K115">
+        <v>100</v>
+      </c>
+      <c r="L115">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>12</v>
+      </c>
+      <c r="B116">
+        <v>17</v>
+      </c>
+      <c r="C116">
+        <v>17</v>
+      </c>
+      <c r="D116" t="s">
+        <v>33</v>
+      </c>
+      <c r="E116" t="s">
+        <v>67</v>
+      </c>
+      <c r="F116" t="s">
+        <v>28</v>
+      </c>
+      <c r="G116" t="s">
+        <v>66</v>
+      </c>
+      <c r="H116" t="s">
+        <v>17</v>
+      </c>
+      <c r="I116" t="s">
+        <v>18</v>
+      </c>
+      <c r="J116" t="s">
+        <v>68</v>
+      </c>
+      <c r="K116">
+        <v>100</v>
+      </c>
+      <c r="L116">
+        <v>68.599999999999994</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>20</v>
+      </c>
+      <c r="B117">
+        <v>4</v>
+      </c>
+      <c r="C117">
+        <v>4</v>
+      </c>
+      <c r="D117" t="s">
+        <v>33</v>
+      </c>
+      <c r="E117" t="s">
+        <v>67</v>
+      </c>
+      <c r="F117" t="s">
+        <v>28</v>
+      </c>
+      <c r="G117" t="s">
+        <v>66</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" t="s">
+        <v>18</v>
+      </c>
+      <c r="K117">
+        <v>100</v>
+      </c>
+      <c r="L117">
+        <v>68.599999999999994</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>21</v>
+      </c>
+      <c r="B118">
+        <v>17</v>
+      </c>
+      <c r="C118">
+        <v>9</v>
+      </c>
+      <c r="D118" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" t="s">
+        <v>67</v>
+      </c>
+      <c r="F118" t="s">
+        <v>28</v>
+      </c>
+      <c r="G118" t="s">
+        <v>66</v>
+      </c>
+      <c r="H118" t="s">
+        <v>17</v>
+      </c>
+      <c r="I118" t="s">
+        <v>18</v>
+      </c>
+      <c r="K118">
+        <v>100</v>
+      </c>
+      <c r="L118">
+        <v>68.599999999999994</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>22</v>
+      </c>
+      <c r="B119">
+        <v>58</v>
+      </c>
+      <c r="C119">
+        <v>41</v>
+      </c>
+      <c r="D119" t="s">
+        <v>70</v>
+      </c>
+      <c r="E119" t="s">
+        <v>67</v>
+      </c>
+      <c r="F119" t="s">
+        <v>28</v>
+      </c>
+      <c r="G119" t="s">
+        <v>66</v>
+      </c>
+      <c r="H119" t="s">
+        <v>17</v>
+      </c>
+      <c r="I119" t="s">
+        <v>18</v>
+      </c>
+      <c r="K119">
+        <v>100</v>
+      </c>
+      <c r="L119">
+        <v>68.599999999999994</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>24</v>
+      </c>
+      <c r="B120">
+        <v>413</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" t="s">
+        <v>67</v>
+      </c>
+      <c r="F120" t="s">
+        <v>28</v>
+      </c>
+      <c r="G120" t="s">
+        <v>66</v>
+      </c>
+      <c r="H120" t="s">
+        <v>17</v>
+      </c>
+      <c r="I120" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120">
+        <v>100</v>
+      </c>
+      <c r="L120">
+        <v>68.599999999999994</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>25</v>
+      </c>
+      <c r="B121">
+        <v>1100000</v>
+      </c>
+      <c r="C121">
+        <v>718800</v>
+      </c>
+      <c r="D121" t="s">
+        <v>96</v>
+      </c>
+      <c r="E121" t="s">
+        <v>67</v>
+      </c>
+      <c r="F121" t="s">
+        <v>28</v>
+      </c>
+      <c r="G121" t="s">
+        <v>66</v>
+      </c>
+      <c r="H121" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121" t="s">
+        <v>18</v>
+      </c>
+      <c r="K121">
+        <v>100</v>
+      </c>
+      <c r="L121">
+        <v>68.599999999999994</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>12</v>
+      </c>
+      <c r="B122">
+        <v>20</v>
+      </c>
+      <c r="C122">
+        <v>2</v>
+      </c>
+      <c r="D122" t="s">
+        <v>97</v>
+      </c>
+      <c r="E122" t="s">
+        <v>71</v>
+      </c>
+      <c r="F122" t="s">
+        <v>28</v>
+      </c>
+      <c r="G122" t="s">
+        <v>66</v>
+      </c>
+      <c r="H122" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" t="s">
+        <v>18</v>
+      </c>
+      <c r="J122" t="s">
+        <v>98</v>
+      </c>
+      <c r="K122">
+        <v>100</v>
+      </c>
+      <c r="L122">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>20</v>
+      </c>
+      <c r="B123">
+        <v>5</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="D123" t="s">
+        <v>80</v>
+      </c>
+      <c r="E123" t="s">
+        <v>71</v>
+      </c>
+      <c r="F123" t="s">
+        <v>28</v>
+      </c>
+      <c r="G123" t="s">
+        <v>66</v>
+      </c>
+      <c r="H123" t="s">
+        <v>17</v>
+      </c>
+      <c r="I123" t="s">
+        <v>18</v>
+      </c>
+      <c r="K123">
+        <v>100</v>
+      </c>
+      <c r="L123">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>21</v>
+      </c>
+      <c r="B124">
+        <v>20</v>
+      </c>
+      <c r="C124">
+        <v>3</v>
+      </c>
+      <c r="D124" t="s">
+        <v>99</v>
+      </c>
+      <c r="E124" t="s">
+        <v>71</v>
+      </c>
+      <c r="F124" t="s">
+        <v>28</v>
+      </c>
+      <c r="G124" t="s">
+        <v>66</v>
+      </c>
+      <c r="H124" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124" t="s">
+        <v>18</v>
+      </c>
+      <c r="K124">
+        <v>100</v>
+      </c>
+      <c r="L124">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>22</v>
+      </c>
+      <c r="B125">
+        <v>68</v>
+      </c>
+      <c r="C125">
+        <v>20</v>
+      </c>
+      <c r="D125" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125" t="s">
+        <v>71</v>
+      </c>
+      <c r="F125" t="s">
+        <v>28</v>
+      </c>
+      <c r="G125" t="s">
+        <v>66</v>
+      </c>
+      <c r="H125" t="s">
+        <v>17</v>
+      </c>
+      <c r="I125" t="s">
+        <v>18</v>
+      </c>
+      <c r="K125">
+        <v>100</v>
+      </c>
+      <c r="L125">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>24</v>
+      </c>
+      <c r="B126">
+        <v>488</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" t="s">
+        <v>71</v>
+      </c>
+      <c r="F126" t="s">
+        <v>28</v>
+      </c>
+      <c r="G126" t="s">
+        <v>66</v>
+      </c>
+      <c r="H126" t="s">
+        <v>17</v>
+      </c>
+      <c r="I126" t="s">
+        <v>18</v>
+      </c>
+      <c r="K126">
+        <v>100</v>
+      </c>
+      <c r="L126">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>25</v>
+      </c>
+      <c r="B127">
+        <v>1300000</v>
+      </c>
+      <c r="C127">
+        <v>80000</v>
+      </c>
+      <c r="D127" t="s">
+        <v>100</v>
+      </c>
+      <c r="E127" t="s">
+        <v>71</v>
+      </c>
+      <c r="F127" t="s">
+        <v>28</v>
+      </c>
+      <c r="G127" t="s">
+        <v>66</v>
+      </c>
+      <c r="H127" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127" t="s">
+        <v>18</v>
+      </c>
+      <c r="K127">
+        <v>100</v>
+      </c>
+      <c r="L127">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>12</v>
+      </c>
+      <c r="B128">
+        <v>16</v>
+      </c>
+      <c r="C128">
+        <v>8</v>
+      </c>
+      <c r="D128" t="s">
+        <v>44</v>
+      </c>
+      <c r="E128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F128" t="s">
+        <v>15</v>
+      </c>
+      <c r="G128" t="s">
+        <v>102</v>
+      </c>
+      <c r="H128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128" t="s">
+        <v>18</v>
+      </c>
+      <c r="J128" t="s">
+        <v>103</v>
+      </c>
+      <c r="K128">
+        <v>100</v>
+      </c>
+      <c r="L128">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>20</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" t="s">
+        <v>101</v>
+      </c>
+      <c r="F129" t="s">
+        <v>15</v>
+      </c>
+      <c r="G129" t="s">
+        <v>102</v>
+      </c>
+      <c r="H129" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129" t="s">
+        <v>18</v>
+      </c>
+      <c r="K129">
+        <v>100</v>
+      </c>
+      <c r="L129">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>21</v>
+      </c>
+      <c r="B130">
+        <v>24</v>
+      </c>
+      <c r="C130">
+        <v>7</v>
+      </c>
+      <c r="D130" t="s">
+        <v>38</v>
+      </c>
+      <c r="E130" t="s">
+        <v>101</v>
+      </c>
+      <c r="F130" t="s">
+        <v>15</v>
+      </c>
+      <c r="G130" t="s">
+        <v>102</v>
+      </c>
+      <c r="H130" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130" t="s">
+        <v>18</v>
+      </c>
+      <c r="K130">
+        <v>100</v>
+      </c>
+      <c r="L130">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>22</v>
+      </c>
+      <c r="B131">
+        <v>88</v>
+      </c>
+      <c r="C131">
+        <v>32</v>
+      </c>
+      <c r="D131" t="s">
+        <v>23</v>
+      </c>
+      <c r="E131" t="s">
+        <v>101</v>
+      </c>
+      <c r="F131" t="s">
+        <v>15</v>
+      </c>
+      <c r="G131" t="s">
+        <v>102</v>
+      </c>
+      <c r="H131" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131" t="s">
+        <v>18</v>
+      </c>
+      <c r="K131">
+        <v>100</v>
+      </c>
+      <c r="L131">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>24</v>
+      </c>
+      <c r="B132">
+        <v>480</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" t="s">
+        <v>101</v>
+      </c>
+      <c r="F132" t="s">
+        <v>15</v>
+      </c>
+      <c r="G132" t="s">
+        <v>102</v>
+      </c>
+      <c r="H132" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132" t="s">
+        <v>18</v>
+      </c>
+      <c r="K132">
+        <v>100</v>
+      </c>
+      <c r="L132">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>25</v>
+      </c>
+      <c r="B133">
+        <v>2000000</v>
+      </c>
+      <c r="C133">
+        <v>950000</v>
+      </c>
+      <c r="D133" t="s">
+        <v>52</v>
+      </c>
+      <c r="E133" t="s">
+        <v>101</v>
+      </c>
+      <c r="F133" t="s">
+        <v>15</v>
+      </c>
+      <c r="G133" t="s">
+        <v>102</v>
+      </c>
+      <c r="H133" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" t="s">
+        <v>18</v>
+      </c>
+      <c r="K133">
+        <v>100</v>
+      </c>
+      <c r="L133">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>12</v>
+      </c>
+      <c r="B134">
+        <v>24</v>
+      </c>
+      <c r="C134">
+        <v>28</v>
+      </c>
+      <c r="D134" t="s">
+        <v>104</v>
+      </c>
+      <c r="E134" t="s">
+        <v>105</v>
+      </c>
+      <c r="F134" t="s">
+        <v>28</v>
+      </c>
+      <c r="G134" t="s">
+        <v>102</v>
+      </c>
+      <c r="H134" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134" t="s">
+        <v>18</v>
+      </c>
+      <c r="K134">
+        <v>100</v>
+      </c>
+      <c r="L134">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>20</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" t="s">
+        <v>105</v>
+      </c>
+      <c r="F135" t="s">
+        <v>28</v>
+      </c>
+      <c r="G135" t="s">
+        <v>102</v>
+      </c>
+      <c r="H135" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" t="s">
+        <v>18</v>
+      </c>
+      <c r="K135">
+        <v>100</v>
+      </c>
+      <c r="L135">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>21</v>
+      </c>
+      <c r="B136">
+        <v>36</v>
+      </c>
+      <c r="C136">
+        <v>15</v>
+      </c>
+      <c r="D136" t="s">
+        <v>106</v>
+      </c>
+      <c r="E136" t="s">
+        <v>105</v>
+      </c>
+      <c r="F136" t="s">
+        <v>28</v>
+      </c>
+      <c r="G136" t="s">
+        <v>102</v>
+      </c>
+      <c r="H136" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" t="s">
+        <v>18</v>
+      </c>
+      <c r="K136">
+        <v>100</v>
+      </c>
+      <c r="L136">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>22</v>
+      </c>
+      <c r="B137">
+        <v>132</v>
+      </c>
+      <c r="C137">
+        <v>127</v>
+      </c>
+      <c r="D137" t="s">
+        <v>23</v>
+      </c>
+      <c r="E137" t="s">
+        <v>105</v>
+      </c>
+      <c r="F137" t="s">
+        <v>28</v>
+      </c>
+      <c r="G137" t="s">
+        <v>102</v>
+      </c>
+      <c r="H137" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137" t="s">
+        <v>18</v>
+      </c>
+      <c r="K137">
+        <v>100</v>
+      </c>
+      <c r="L137">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>24</v>
+      </c>
+      <c r="B138">
+        <v>720</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138" t="s">
+        <v>13</v>
+      </c>
+      <c r="E138" t="s">
+        <v>105</v>
+      </c>
+      <c r="F138" t="s">
+        <v>28</v>
+      </c>
+      <c r="G138" t="s">
+        <v>102</v>
+      </c>
+      <c r="H138" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" t="s">
+        <v>18</v>
+      </c>
+      <c r="K138">
+        <v>100</v>
+      </c>
+      <c r="L138">
+        <v>56.1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>25</v>
+      </c>
+      <c r="B139">
+        <v>3000000</v>
+      </c>
+      <c r="C139">
+        <v>985000</v>
+      </c>
+      <c r="D139" t="s">
+        <v>29</v>
+      </c>
+      <c r="E139" t="s">
+        <v>105</v>
+      </c>
+      <c r="F139" t="s">
+        <v>28</v>
+      </c>
+      <c r="G139" t="s">
+        <v>102</v>
+      </c>
+      <c r="H139" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139" t="s">
+        <v>18</v>
+      </c>
+      <c r="K139">
+        <v>100</v>
+      </c>
+      <c r="L139">
+        <v>56.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/08 Agosto/Liquidacióncvs -agosto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_2D0D28C7D35BA60E62355476585DCE3A8746539F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB01D23A-A786-4BF9-8999-49D9C57F1A24}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_18416A931278660F62355476585DCE3A87463ED7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1EA3E85-E62F-437C-9463-2793996D37E5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="135">
   <si>
     <t>Producto</t>
   </si>
@@ -139,7 +139,145 @@
     <t>29%</t>
   </si>
   <si>
-    <t>12%</t>
+    <t>59%</t>
+  </si>
+  <si>
+    <t>Lider Paola Andrea Clavijo</t>
+  </si>
+  <si>
+    <t>ENVIGADO</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>64%</t>
+  </si>
+  <si>
+    <t>Luz Enith Sanchez Galeano</t>
+  </si>
+  <si>
+    <t>El 15 pasa al CVS de Sabaneta reemplaza vacaciones de Andrea Arenas</t>
+  </si>
+  <si>
+    <t>67%</t>
+  </si>
+  <si>
+    <t>87%</t>
+  </si>
+  <si>
+    <t>30%</t>
+  </si>
+  <si>
+    <t>Yessica  Restrepo Caicedo</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>27%</t>
+  </si>
+  <si>
+    <t>Kelly Yuliana Ospina Saldarriaga</t>
+  </si>
+  <si>
+    <t>SUPERNUMERARIO</t>
+  </si>
+  <si>
+    <t>61%</t>
+  </si>
+  <si>
+    <t>Lider Yolima Mesa Zapata</t>
+  </si>
+  <si>
+    <t>CALDAS</t>
+  </si>
+  <si>
+    <t>68%</t>
+  </si>
+  <si>
+    <t>31%</t>
+  </si>
+  <si>
+    <t>Darinela  Chavarria Carvajal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacaciones del 4 al 19 de agosto - elabora 12 días </t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>53%</t>
+  </si>
+  <si>
+    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
+  </si>
+  <si>
+    <t>120%</t>
+  </si>
+  <si>
+    <t>49%</t>
+  </si>
+  <si>
+    <t>58%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>54%</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>Vacaciones del 15 al 31 elabora 11 días</t>
+  </si>
+  <si>
+    <t>71%</t>
+  </si>
+  <si>
+    <t>65%</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>Reemplaza vacaciones de Andrea 13 días</t>
+  </si>
+  <si>
+    <t>15%</t>
+  </si>
+  <si>
+    <t>6%</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>Lider Dayana Lopez Llorente</t>
+  </si>
+  <si>
+    <t>SEGOVIA</t>
+  </si>
+  <si>
+    <t>Elabora hasta el 22 , elabora 17 días  meta puntos 623</t>
+  </si>
+  <si>
+    <t>48%</t>
+  </si>
+  <si>
+    <t>117%</t>
+  </si>
+  <si>
+    <t>Luisa Fernanda Miranda Rodriguez</t>
+  </si>
+  <si>
+    <t>42%</t>
   </si>
   <si>
     <t>Lider Paulina Andrea Zapata Jimenez</t>
@@ -148,199 +286,145 @@
     <t>BARBOSA</t>
   </si>
   <si>
-    <t>Incap. 3 días  Meta puntos 550           Meta postpago 7</t>
-  </si>
-  <si>
-    <t>Meta Hogar 2</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>Meta terminales 16</t>
-  </si>
-  <si>
-    <t>Meta Otros 22</t>
-  </si>
-  <si>
-    <t>73%</t>
+    <t>94%</t>
+  </si>
+  <si>
+    <t>153%</t>
   </si>
   <si>
     <t>Evelis Mary Ojeda Baldovino</t>
   </si>
   <si>
-    <t>67%</t>
-  </si>
-  <si>
-    <t>91%</t>
+    <t>81%</t>
+  </si>
+  <si>
+    <t>89%</t>
+  </si>
+  <si>
+    <t>155%</t>
   </si>
   <si>
     <t>Sene Del Socorro Suarez Torres</t>
   </si>
   <si>
-    <t>48%</t>
+    <t>150%</t>
+  </si>
+  <si>
+    <t>93%</t>
+  </si>
+  <si>
+    <t>131%</t>
+  </si>
+  <si>
+    <t>103%</t>
   </si>
   <si>
     <t>Sara Julieth Acevedo Gutierrez</t>
   </si>
   <si>
-    <t>SUPERNUMERARIO</t>
-  </si>
-  <si>
     <t>25%</t>
   </si>
   <si>
+    <t>74%</t>
+  </si>
+  <si>
+    <t>Dayanis  Celsa Gamarra</t>
+  </si>
+  <si>
+    <t>EL BAGRE</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>83%</t>
+  </si>
+  <si>
+    <t>Darly Esther Sola Tarriba</t>
+  </si>
+  <si>
+    <t>Vacaciones del 18 de agosto al 3 de septiembre</t>
+  </si>
+  <si>
+    <t>44%</t>
+  </si>
+  <si>
+    <t>130%</t>
+  </si>
+  <si>
+    <t>Jeider Alberto Moreno Solano</t>
+  </si>
+  <si>
+    <t>Ingresa el 10 de agosto</t>
+  </si>
+  <si>
+    <t>45%</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>Líder Sara Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t>GIRARDOTA</t>
+  </si>
+  <si>
+    <t>6 días Líder</t>
+  </si>
+  <si>
+    <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+  </si>
+  <si>
+    <t>15 días sola sin apoyo de líder</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
     <t>57%</t>
   </si>
   <si>
-    <t>Dayanis  Celsa Gamarra</t>
-  </si>
-  <si>
-    <t>EL BAGRE</t>
-  </si>
-  <si>
-    <t>59%</t>
-  </si>
-  <si>
-    <t>Darly Esther Sola Tarriba</t>
+    <t>Yuliana Ospina Saldarriaga</t>
+  </si>
+  <si>
+    <t>3 días Líder</t>
+  </si>
+  <si>
+    <t>Eduar Alonso Olaya Estrada</t>
+  </si>
+  <si>
+    <t>127%</t>
+  </si>
+  <si>
+    <t>Lider Luz Stella Serna</t>
+  </si>
+  <si>
+    <t>TERMINAL NORTE</t>
+  </si>
+  <si>
+    <t>Incapacidad 6 días</t>
+  </si>
+  <si>
+    <t>200%</t>
+  </si>
+  <si>
+    <t>Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t>Líder 6 días</t>
   </si>
   <si>
     <t>36%</t>
   </si>
   <si>
-    <t>Jeider Alberto Moreno Solano</t>
-  </si>
-  <si>
-    <t>Ingresa el 10 de agosto</t>
-  </si>
-  <si>
-    <t>22%</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Arbelaez</t>
-  </si>
-  <si>
-    <t>SABANETA</t>
-  </si>
-  <si>
-    <t>Andrea  Arenas Hurtado</t>
-  </si>
-  <si>
-    <t>Vacaciones del 15 al 31 elabora 11 días</t>
-  </si>
-  <si>
-    <t>53%</t>
-  </si>
-  <si>
-    <t>71%</t>
-  </si>
-  <si>
-    <t>Luz Enith Sanchez Galeano</t>
-  </si>
-  <si>
-    <t>Lider Paola Andrea Clavijo</t>
-  </si>
-  <si>
-    <t>ENVIGADO</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>64%</t>
-  </si>
-  <si>
-    <t>El 15 pasa al CVS de Sabaneta reemplaza vacaciones de Andrea Arenas</t>
-  </si>
-  <si>
-    <t>87%</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>Yessica  Restrepo Caicedo</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>27%</t>
-  </si>
-  <si>
-    <t>Kelly Yuliana Ospina Saldarriaga</t>
-  </si>
-  <si>
-    <t>61%</t>
-  </si>
-  <si>
-    <t>Lider Yolima Mesa Zapata</t>
-  </si>
-  <si>
-    <t>CALDAS</t>
-  </si>
-  <si>
-    <t>68%</t>
-  </si>
-  <si>
-    <t>31%</t>
-  </si>
-  <si>
-    <t>Darinela  Chavarria Carvajal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vacaciones del 4 al 19 de agosto - elabora 12 días </t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
-    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
-  </si>
-  <si>
-    <t>120%</t>
-  </si>
-  <si>
-    <t>49%</t>
-  </si>
-  <si>
-    <t>58%</t>
-  </si>
-  <si>
-    <t>54%</t>
-  </si>
-  <si>
-    <t>65%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>Reemplaza vacaciones de Andrea 13 días</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>Lider Dayana Lopez Llorente</t>
-  </si>
-  <si>
-    <t>SEGOVIA</t>
-  </si>
-  <si>
-    <t>Elabora hasta el 22 , elabora 17 días  meta puntos 623</t>
-  </si>
-  <si>
-    <t>117%</t>
-  </si>
-  <si>
-    <t>Luisa Fernanda Miranda Rodriguez</t>
-  </si>
-  <si>
-    <t>42%</t>
+    <t>Maria Fernanda Posada Galeano</t>
+  </si>
+  <si>
+    <t>62%</t>
+  </si>
+  <si>
+    <t>41%</t>
   </si>
 </sst>
 </file>
@@ -704,7 +788,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L181"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1596,10 +1680,10 @@
         <v>12</v>
       </c>
       <c r="B26">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
         <v>39</v>
@@ -1619,14 +1703,11 @@
       <c r="I26" t="s">
         <v>18</v>
       </c>
-      <c r="J26" t="s">
-        <v>42</v>
-      </c>
       <c r="K26">
         <v>100</v>
       </c>
       <c r="L26">
-        <v>37.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1634,13 +1715,13 @@
         <v>20</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E27" t="s">
         <v>40</v>
@@ -1657,14 +1738,11 @@
       <c r="I27" t="s">
         <v>18</v>
       </c>
-      <c r="J27" t="s">
-        <v>43</v>
-      </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>37.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1672,13 +1750,13 @@
         <v>21</v>
       </c>
       <c r="B28">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E28" t="s">
         <v>40</v>
@@ -1695,14 +1773,11 @@
       <c r="I28" t="s">
         <v>18</v>
       </c>
-      <c r="J28" t="s">
-        <v>45</v>
-      </c>
       <c r="K28">
         <v>100</v>
       </c>
       <c r="L28">
-        <v>37.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -1710,10 +1785,10 @@
         <v>22</v>
       </c>
       <c r="B29">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s">
         <v>23</v>
@@ -1733,14 +1808,11 @@
       <c r="I29" t="s">
         <v>18</v>
       </c>
-      <c r="J29" t="s">
-        <v>46</v>
-      </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>37.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -1748,7 +1820,7 @@
         <v>24</v>
       </c>
       <c r="B30">
-        <v>375</v>
+        <v>497</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1775,7 +1847,7 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>37.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -1783,7 +1855,7 @@
         <v>25</v>
       </c>
       <c r="B31">
-        <v>2000000</v>
+        <v>1490786</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1810,7 +1882,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>37.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -1818,16 +1890,16 @@
         <v>12</v>
       </c>
       <c r="B32">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F32" t="s">
         <v>28</v>
@@ -1841,11 +1913,14 @@
       <c r="I32" t="s">
         <v>18</v>
       </c>
+      <c r="J32" t="s">
+        <v>45</v>
+      </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>59.4</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -1853,16 +1928,16 @@
         <v>20</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s">
         <v>28</v>
@@ -1880,7 +1955,7 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>59.4</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -1888,16 +1963,16 @@
         <v>21</v>
       </c>
       <c r="B34">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C34">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F34" t="s">
         <v>28</v>
@@ -1915,7 +1990,7 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>59.4</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -1923,16 +1998,16 @@
         <v>22</v>
       </c>
       <c r="B35">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C35">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
         <v>23</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F35" t="s">
         <v>28</v>
@@ -1950,7 +2025,7 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>59.4</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -1958,7 +2033,7 @@
         <v>24</v>
       </c>
       <c r="B36">
-        <v>563</v>
+        <v>258</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1967,7 +2042,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F36" t="s">
         <v>28</v>
@@ -1985,7 +2060,7 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>59.4</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -1993,7 +2068,7 @@
         <v>25</v>
       </c>
       <c r="B37">
-        <v>3000000</v>
+        <v>773357</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2002,7 +2077,7 @@
         <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F37" t="s">
         <v>28</v>
@@ -2020,7 +2095,7 @@
         <v>100</v>
       </c>
       <c r="L37">
-        <v>59.4</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2028,16 +2103,16 @@
         <v>12</v>
       </c>
       <c r="B38">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F38" t="s">
         <v>28</v>
@@ -2055,7 +2130,7 @@
         <v>100</v>
       </c>
       <c r="L38">
-        <v>57.7</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2063,16 +2138,16 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="E39" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F39" t="s">
         <v>28</v>
@@ -2090,7 +2165,7 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>57.7</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2098,16 +2173,16 @@
         <v>21</v>
       </c>
       <c r="B40">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F40" t="s">
         <v>28</v>
@@ -2125,7 +2200,7 @@
         <v>100</v>
       </c>
       <c r="L40">
-        <v>57.7</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2133,16 +2208,16 @@
         <v>22</v>
       </c>
       <c r="B41">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="C41">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D41" t="s">
         <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F41" t="s">
         <v>28</v>
@@ -2160,7 +2235,7 @@
         <v>100</v>
       </c>
       <c r="L41">
-        <v>57.7</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2168,7 +2243,7 @@
         <v>24</v>
       </c>
       <c r="B42">
-        <v>563</v>
+        <v>745</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -2177,7 +2252,7 @@
         <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F42" t="s">
         <v>28</v>
@@ -2195,7 +2270,7 @@
         <v>100</v>
       </c>
       <c r="L42">
-        <v>57.7</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2203,7 +2278,7 @@
         <v>25</v>
       </c>
       <c r="B43">
-        <v>3000000</v>
+        <v>2235857</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -2212,7 +2287,7 @@
         <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F43" t="s">
         <v>28</v>
@@ -2230,7 +2305,7 @@
         <v>100</v>
       </c>
       <c r="L43">
-        <v>57.7</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2238,7 +2313,7 @@
         <v>12</v>
       </c>
       <c r="B44">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -2247,10 +2322,10 @@
         <v>13</v>
       </c>
       <c r="E44" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" t="s">
         <v>53</v>
-      </c>
-      <c r="F44" t="s">
-        <v>54</v>
       </c>
       <c r="G44" t="s">
         <v>41</v>
@@ -2265,7 +2340,7 @@
         <v>100</v>
       </c>
       <c r="L44">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2273,19 +2348,19 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
+        <v>52</v>
+      </c>
+      <c r="F45" t="s">
         <v>53</v>
-      </c>
-      <c r="F45" t="s">
-        <v>54</v>
       </c>
       <c r="G45" t="s">
         <v>41</v>
@@ -2300,7 +2375,7 @@
         <v>100</v>
       </c>
       <c r="L45">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2308,7 +2383,7 @@
         <v>21</v>
       </c>
       <c r="B46">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2317,10 +2392,10 @@
         <v>13</v>
       </c>
       <c r="E46" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" t="s">
         <v>53</v>
-      </c>
-      <c r="F46" t="s">
-        <v>54</v>
       </c>
       <c r="G46" t="s">
         <v>41</v>
@@ -2335,7 +2410,7 @@
         <v>100</v>
       </c>
       <c r="L46">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2343,19 +2418,19 @@
         <v>22</v>
       </c>
       <c r="B47">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D47" t="s">
         <v>23</v>
       </c>
       <c r="E47" t="s">
+        <v>52</v>
+      </c>
+      <c r="F47" t="s">
         <v>53</v>
-      </c>
-      <c r="F47" t="s">
-        <v>54</v>
       </c>
       <c r="G47" t="s">
         <v>41</v>
@@ -2370,7 +2445,7 @@
         <v>100</v>
       </c>
       <c r="L47">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2387,10 +2462,10 @@
         <v>13</v>
       </c>
       <c r="E48" t="s">
+        <v>52</v>
+      </c>
+      <c r="F48" t="s">
         <v>53</v>
-      </c>
-      <c r="F48" t="s">
-        <v>54</v>
       </c>
       <c r="G48" t="s">
         <v>41</v>
@@ -2405,7 +2480,7 @@
         <v>100</v>
       </c>
       <c r="L48">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2413,7 +2488,7 @@
         <v>25</v>
       </c>
       <c r="B49">
-        <v>3000000</v>
+        <v>1687500</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -2422,10 +2497,10 @@
         <v>13</v>
       </c>
       <c r="E49" t="s">
+        <v>52</v>
+      </c>
+      <c r="F49" t="s">
         <v>53</v>
-      </c>
-      <c r="F49" t="s">
-        <v>54</v>
       </c>
       <c r="G49" t="s">
         <v>41</v>
@@ -2440,7 +2515,7 @@
         <v>100</v>
       </c>
       <c r="L49">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2448,22 +2523,22 @@
         <v>12</v>
       </c>
       <c r="B50">
+        <v>23</v>
+      </c>
+      <c r="C50">
         <v>14</v>
       </c>
-      <c r="C50">
-        <v>8</v>
-      </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E50" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F50" t="s">
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -2475,7 +2550,7 @@
         <v>100</v>
       </c>
       <c r="L50">
-        <v>47.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2483,22 +2558,22 @@
         <v>20</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E51" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F51" t="s">
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
@@ -2510,7 +2585,7 @@
         <v>100</v>
       </c>
       <c r="L51">
-        <v>47.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2518,22 +2593,22 @@
         <v>21</v>
       </c>
       <c r="B52">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C52">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E52" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F52" t="s">
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -2545,7 +2620,7 @@
         <v>100</v>
       </c>
       <c r="L52">
-        <v>47.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -2553,22 +2628,22 @@
         <v>22</v>
       </c>
       <c r="B53">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C53">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D53" t="s">
         <v>23</v>
       </c>
       <c r="E53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F53" t="s">
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -2580,7 +2655,7 @@
         <v>100</v>
       </c>
       <c r="L53">
-        <v>47.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -2588,7 +2663,7 @@
         <v>24</v>
       </c>
       <c r="B54">
-        <v>431</v>
+        <v>487</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2597,13 +2672,13 @@
         <v>13</v>
       </c>
       <c r="E54" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F54" t="s">
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -2615,7 +2690,7 @@
         <v>100</v>
       </c>
       <c r="L54">
-        <v>47.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -2623,22 +2698,22 @@
         <v>25</v>
       </c>
       <c r="B55">
-        <v>2155714</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>4138900</v>
       </c>
       <c r="D55" t="s">
         <v>13</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F55" t="s">
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
@@ -2650,7 +2725,7 @@
         <v>100</v>
       </c>
       <c r="L55">
-        <v>47.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -2658,34 +2733,37 @@
         <v>12</v>
       </c>
       <c r="B56">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="E56" t="s">
+        <v>59</v>
+      </c>
+      <c r="F56" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" t="s">
+        <v>56</v>
+      </c>
+      <c r="H56" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" t="s">
+        <v>18</v>
+      </c>
+      <c r="J56" t="s">
         <v>60</v>
       </c>
-      <c r="F56" t="s">
-        <v>28</v>
-      </c>
-      <c r="G56" t="s">
-        <v>58</v>
-      </c>
-      <c r="H56" t="s">
-        <v>17</v>
-      </c>
-      <c r="I56" t="s">
-        <v>18</v>
-      </c>
       <c r="K56">
         <v>100</v>
       </c>
       <c r="L56">
-        <v>24.1</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -2693,22 +2771,22 @@
         <v>20</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D57" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E57" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F57" t="s">
         <v>28</v>
       </c>
       <c r="G57" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
@@ -2720,7 +2798,7 @@
         <v>100</v>
       </c>
       <c r="L57">
-        <v>24.1</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -2728,23 +2806,23 @@
         <v>21</v>
       </c>
       <c r="B58">
+        <v>23</v>
+      </c>
+      <c r="C58">
+        <v>8</v>
+      </c>
+      <c r="D58" t="s">
+        <v>61</v>
+      </c>
+      <c r="E58" t="s">
+        <v>59</v>
+      </c>
+      <c r="F58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58" t="s">
         <v>56</v>
       </c>
-      <c r="C58">
-        <v>14</v>
-      </c>
-      <c r="D58" t="s">
-        <v>55</v>
-      </c>
-      <c r="E58" t="s">
-        <v>60</v>
-      </c>
-      <c r="F58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G58" t="s">
-        <v>58</v>
-      </c>
       <c r="H58" t="s">
         <v>17</v>
       </c>
@@ -2755,7 +2833,7 @@
         <v>100</v>
       </c>
       <c r="L58">
-        <v>24.1</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -2763,22 +2841,22 @@
         <v>22</v>
       </c>
       <c r="B59">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="C59">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D59" t="s">
         <v>23</v>
       </c>
       <c r="E59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F59" t="s">
         <v>28</v>
       </c>
       <c r="G59" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
@@ -2790,7 +2868,7 @@
         <v>100</v>
       </c>
       <c r="L59">
-        <v>24.1</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -2798,7 +2876,7 @@
         <v>24</v>
       </c>
       <c r="B60">
-        <v>647</v>
+        <v>281</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2807,13 +2885,13 @@
         <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F60" t="s">
         <v>28</v>
       </c>
       <c r="G60" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -2825,7 +2903,7 @@
         <v>100</v>
       </c>
       <c r="L60">
-        <v>24.1</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -2833,7 +2911,7 @@
         <v>25</v>
       </c>
       <c r="B61">
-        <v>3233571</v>
+        <v>0</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2842,13 +2920,13 @@
         <v>13</v>
       </c>
       <c r="E61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F61" t="s">
         <v>28</v>
       </c>
       <c r="G61" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
@@ -2860,7 +2938,7 @@
         <v>100</v>
       </c>
       <c r="L61">
-        <v>24.1</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -2868,22 +2946,22 @@
         <v>12</v>
       </c>
       <c r="B62">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C62">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F62" t="s">
         <v>28</v>
       </c>
       <c r="G62" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
@@ -2891,14 +2969,11 @@
       <c r="I62" t="s">
         <v>18</v>
       </c>
-      <c r="J62" t="s">
-        <v>63</v>
-      </c>
       <c r="K62">
         <v>100</v>
       </c>
       <c r="L62">
-        <v>30.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -2906,22 +2981,22 @@
         <v>20</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E63" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F63" t="s">
         <v>28</v>
       </c>
       <c r="G63" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
@@ -2933,7 +3008,7 @@
         <v>100</v>
       </c>
       <c r="L63">
-        <v>30.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -2941,22 +3016,22 @@
         <v>21</v>
       </c>
       <c r="B64">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C64">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E64" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F64" t="s">
         <v>28</v>
       </c>
       <c r="G64" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -2968,7 +3043,7 @@
         <v>100</v>
       </c>
       <c r="L64">
-        <v>30.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -2976,22 +3051,22 @@
         <v>22</v>
       </c>
       <c r="B65">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="C65">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="E65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F65" t="s">
         <v>28</v>
       </c>
       <c r="G65" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -3003,7 +3078,7 @@
         <v>100</v>
       </c>
       <c r="L65">
-        <v>30.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3011,7 +3086,7 @@
         <v>24</v>
       </c>
       <c r="B66">
-        <v>422</v>
+        <v>731</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3020,13 +3095,13 @@
         <v>13</v>
       </c>
       <c r="E66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F66" t="s">
         <v>28</v>
       </c>
       <c r="G66" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
@@ -3038,7 +3113,7 @@
         <v>100</v>
       </c>
       <c r="L66">
-        <v>30.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3046,7 +3121,7 @@
         <v>25</v>
       </c>
       <c r="B67">
-        <v>2110714</v>
+        <v>0</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3055,13 +3130,13 @@
         <v>13</v>
       </c>
       <c r="E67" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F67" t="s">
         <v>28</v>
       </c>
       <c r="G67" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -3073,7 +3148,7 @@
         <v>100</v>
       </c>
       <c r="L67">
-        <v>30.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3081,22 +3156,22 @@
         <v>12</v>
       </c>
       <c r="B68">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C68">
         <v>16</v>
       </c>
       <c r="D68" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E68" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F68" t="s">
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
@@ -3108,7 +3183,7 @@
         <v>100</v>
       </c>
       <c r="L68">
-        <v>38.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3116,22 +3191,22 @@
         <v>20</v>
       </c>
       <c r="B69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C69">
         <v>2</v>
       </c>
       <c r="D69" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E69" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F69" t="s">
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -3143,7 +3218,7 @@
         <v>100</v>
       </c>
       <c r="L69">
-        <v>38.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3151,22 +3226,22 @@
         <v>21</v>
       </c>
       <c r="B70">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C70">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E70" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F70" t="s">
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -3178,7 +3253,7 @@
         <v>100</v>
       </c>
       <c r="L70">
-        <v>38.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3186,22 +3261,22 @@
         <v>22</v>
       </c>
       <c r="B71">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C71">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D71" t="s">
         <v>23</v>
       </c>
       <c r="E71" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F71" t="s">
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -3213,7 +3288,7 @@
         <v>100</v>
       </c>
       <c r="L71">
-        <v>38.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3221,7 +3296,7 @@
         <v>24</v>
       </c>
       <c r="B72">
-        <v>497</v>
+        <v>600</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -3230,13 +3305,13 @@
         <v>13</v>
       </c>
       <c r="E72" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F72" t="s">
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -3248,7 +3323,7 @@
         <v>100</v>
       </c>
       <c r="L72">
-        <v>38.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3256,22 +3331,22 @@
         <v>25</v>
       </c>
       <c r="B73">
-        <v>1490786</v>
+        <v>1600000</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1067900</v>
       </c>
       <c r="D73" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="E73" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F73" t="s">
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -3283,7 +3358,7 @@
         <v>100</v>
       </c>
       <c r="L73">
-        <v>38.6</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3291,37 +3366,37 @@
         <v>12</v>
       </c>
       <c r="B74">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C74">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D74" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="E74" t="s">
+        <v>70</v>
+      </c>
+      <c r="F74" t="s">
+        <v>28</v>
+      </c>
+      <c r="G74" t="s">
+        <v>68</v>
+      </c>
+      <c r="H74" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" t="s">
+        <v>18</v>
+      </c>
+      <c r="J74" t="s">
         <v>71</v>
       </c>
-      <c r="F74" t="s">
-        <v>28</v>
-      </c>
-      <c r="G74" t="s">
-        <v>73</v>
-      </c>
-      <c r="H74" t="s">
-        <v>17</v>
-      </c>
-      <c r="I74" t="s">
-        <v>18</v>
-      </c>
-      <c r="J74" t="s">
-        <v>76</v>
-      </c>
       <c r="K74">
         <v>100</v>
       </c>
       <c r="L74">
-        <v>58.3</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3329,22 +3404,22 @@
         <v>20</v>
       </c>
       <c r="B75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E75" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F75" t="s">
         <v>28</v>
       </c>
       <c r="G75" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -3356,7 +3431,7 @@
         <v>100</v>
       </c>
       <c r="L75">
-        <v>58.3</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3364,22 +3439,22 @@
         <v>21</v>
       </c>
       <c r="B76">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C76">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D76" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E76" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F76" t="s">
         <v>28</v>
       </c>
       <c r="G76" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -3391,7 +3466,7 @@
         <v>100</v>
       </c>
       <c r="L76">
-        <v>58.3</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3399,22 +3474,22 @@
         <v>22</v>
       </c>
       <c r="B77">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C77">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D77" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="E77" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F77" t="s">
         <v>28</v>
       </c>
       <c r="G77" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -3426,7 +3501,7 @@
         <v>100</v>
       </c>
       <c r="L77">
-        <v>58.3</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -3434,7 +3509,7 @@
         <v>24</v>
       </c>
       <c r="B78">
-        <v>258</v>
+        <v>413</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3443,13 +3518,13 @@
         <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F78" t="s">
         <v>28</v>
       </c>
       <c r="G78" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -3461,7 +3536,7 @@
         <v>100</v>
       </c>
       <c r="L78">
-        <v>58.3</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -3469,22 +3544,22 @@
         <v>25</v>
       </c>
       <c r="B79">
-        <v>773357</v>
+        <v>1100000</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>718800</v>
       </c>
       <c r="D79" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="E79" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F79" t="s">
         <v>28</v>
       </c>
       <c r="G79" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -3496,7 +3571,7 @@
         <v>100</v>
       </c>
       <c r="L79">
-        <v>58.3</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -3504,22 +3579,22 @@
         <v>12</v>
       </c>
       <c r="B80">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C80">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D80" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E80" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="F80" t="s">
         <v>28</v>
       </c>
       <c r="G80" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -3527,11 +3602,14 @@
       <c r="I80" t="s">
         <v>18</v>
       </c>
+      <c r="J80" t="s">
+        <v>75</v>
+      </c>
       <c r="K80">
         <v>100</v>
       </c>
       <c r="L80">
-        <v>22.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -3539,22 +3617,22 @@
         <v>20</v>
       </c>
       <c r="B81">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E81" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="F81" t="s">
         <v>28</v>
       </c>
       <c r="G81" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -3566,7 +3644,7 @@
         <v>100</v>
       </c>
       <c r="L81">
-        <v>22.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -3574,22 +3652,22 @@
         <v>21</v>
       </c>
       <c r="B82">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C82">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E82" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="F82" t="s">
         <v>28</v>
       </c>
       <c r="G82" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -3601,7 +3679,7 @@
         <v>100</v>
       </c>
       <c r="L82">
-        <v>22.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -3609,22 +3687,22 @@
         <v>22</v>
       </c>
       <c r="B83">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="C83">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D83" t="s">
         <v>23</v>
       </c>
       <c r="E83" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="F83" t="s">
         <v>28</v>
       </c>
       <c r="G83" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -3636,7 +3714,7 @@
         <v>100</v>
       </c>
       <c r="L83">
-        <v>22.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -3644,7 +3722,7 @@
         <v>24</v>
       </c>
       <c r="B84">
-        <v>745</v>
+        <v>488</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3653,13 +3731,13 @@
         <v>13</v>
       </c>
       <c r="E84" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="F84" t="s">
         <v>28</v>
       </c>
       <c r="G84" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -3671,7 +3749,7 @@
         <v>100</v>
       </c>
       <c r="L84">
-        <v>22.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3679,22 +3757,22 @@
         <v>25</v>
       </c>
       <c r="B85">
-        <v>2235857</v>
+        <v>1300000</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="D85" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="E85" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="F85" t="s">
         <v>28</v>
       </c>
       <c r="G85" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
@@ -3706,7 +3784,7 @@
         <v>100</v>
       </c>
       <c r="L85">
-        <v>22.2</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -3714,22 +3792,22 @@
         <v>12</v>
       </c>
       <c r="B86">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D86" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="E86" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F86" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
@@ -3737,11 +3815,14 @@
       <c r="I86" t="s">
         <v>18</v>
       </c>
+      <c r="J86" t="s">
+        <v>81</v>
+      </c>
       <c r="K86">
         <v>100</v>
       </c>
       <c r="L86">
-        <v>0.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -3749,7 +3830,7 @@
         <v>20</v>
       </c>
       <c r="B87">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -3758,13 +3839,13 @@
         <v>13</v>
       </c>
       <c r="E87" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F87" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -3776,7 +3857,7 @@
         <v>100</v>
       </c>
       <c r="L87">
-        <v>0.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -3784,22 +3865,22 @@
         <v>21</v>
       </c>
       <c r="B88">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D88" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E88" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F88" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -3811,7 +3892,7 @@
         <v>100</v>
       </c>
       <c r="L88">
-        <v>0.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -3819,22 +3900,22 @@
         <v>22</v>
       </c>
       <c r="B89">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C89">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D89" t="s">
         <v>23</v>
       </c>
       <c r="E89" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F89" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -3846,7 +3927,7 @@
         <v>100</v>
       </c>
       <c r="L89">
-        <v>0.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -3854,7 +3935,7 @@
         <v>24</v>
       </c>
       <c r="B90">
-        <v>563</v>
+        <v>480</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -3863,13 +3944,13 @@
         <v>13</v>
       </c>
       <c r="E90" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F90" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -3881,7 +3962,7 @@
         <v>100</v>
       </c>
       <c r="L90">
-        <v>0.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -3889,22 +3970,22 @@
         <v>25</v>
       </c>
       <c r="B91">
-        <v>1687500</v>
+        <v>2000000</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>950000</v>
       </c>
       <c r="D91" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="E91" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F91" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -3916,7 +3997,7 @@
         <v>100</v>
       </c>
       <c r="L91">
-        <v>0.5</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -3924,10 +4005,10 @@
         <v>12</v>
       </c>
       <c r="B92">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C92">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D92" t="s">
         <v>83</v>
@@ -3936,10 +4017,10 @@
         <v>84</v>
       </c>
       <c r="F92" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G92" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -3951,7 +4032,7 @@
         <v>100</v>
       </c>
       <c r="L92">
-        <v>58.4</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -3959,22 +4040,22 @@
         <v>20</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E93" t="s">
         <v>84</v>
       </c>
       <c r="F93" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G93" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -3986,7 +4067,7 @@
         <v>100</v>
       </c>
       <c r="L93">
-        <v>58.4</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -3994,22 +4075,22 @@
         <v>21</v>
       </c>
       <c r="B94">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C94">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D94" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E94" t="s">
         <v>84</v>
       </c>
       <c r="F94" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G94" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -4021,7 +4102,7 @@
         <v>100</v>
       </c>
       <c r="L94">
-        <v>58.4</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4029,10 +4110,10 @@
         <v>22</v>
       </c>
       <c r="B95">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="C95">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="D95" t="s">
         <v>23</v>
@@ -4041,10 +4122,10 @@
         <v>84</v>
       </c>
       <c r="F95" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G95" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -4056,7 +4137,7 @@
         <v>100</v>
       </c>
       <c r="L95">
-        <v>58.4</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4064,7 +4145,7 @@
         <v>24</v>
       </c>
       <c r="B96">
-        <v>487</v>
+        <v>720</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4076,10 +4157,10 @@
         <v>84</v>
       </c>
       <c r="F96" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G96" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -4091,7 +4172,7 @@
         <v>100</v>
       </c>
       <c r="L96">
-        <v>58.4</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4099,22 +4180,22 @@
         <v>25</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="C97">
-        <v>4138900</v>
+        <v>985000</v>
       </c>
       <c r="D97" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E97" t="s">
         <v>84</v>
       </c>
       <c r="F97" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G97" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -4126,7 +4207,7 @@
         <v>100</v>
       </c>
       <c r="L97">
-        <v>58.4</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4134,37 +4215,34 @@
         <v>12</v>
       </c>
       <c r="B98">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C98">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D98" t="s">
+        <v>33</v>
+      </c>
+      <c r="E98" t="s">
+        <v>86</v>
+      </c>
+      <c r="F98" t="s">
+        <v>15</v>
+      </c>
+      <c r="G98" t="s">
         <v>87</v>
       </c>
-      <c r="E98" t="s">
-        <v>88</v>
-      </c>
-      <c r="F98" t="s">
-        <v>28</v>
-      </c>
-      <c r="G98" t="s">
-        <v>85</v>
-      </c>
       <c r="H98" t="s">
         <v>17</v>
       </c>
       <c r="I98" t="s">
         <v>18</v>
       </c>
-      <c r="J98" t="s">
-        <v>89</v>
-      </c>
       <c r="K98">
         <v>100</v>
       </c>
       <c r="L98">
-        <v>35.5</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4172,22 +4250,22 @@
         <v>20</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D99" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E99" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F99" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -4199,7 +4277,7 @@
         <v>100</v>
       </c>
       <c r="L99">
-        <v>35.5</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4207,22 +4285,22 @@
         <v>21</v>
       </c>
       <c r="B100">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C100">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D100" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E100" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F100" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -4234,7 +4312,7 @@
         <v>100</v>
       </c>
       <c r="L100">
-        <v>35.5</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4242,22 +4320,22 @@
         <v>22</v>
       </c>
       <c r="B101">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C101">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D101" t="s">
         <v>23</v>
       </c>
       <c r="E101" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F101" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -4269,7 +4347,7 @@
         <v>100</v>
       </c>
       <c r="L101">
-        <v>35.5</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4277,7 +4355,7 @@
         <v>24</v>
       </c>
       <c r="B102">
-        <v>281</v>
+        <v>375</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -4286,13 +4364,13 @@
         <v>13</v>
       </c>
       <c r="E102" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F102" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -4304,7 +4382,7 @@
         <v>100</v>
       </c>
       <c r="L102">
-        <v>35.5</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4312,22 +4390,22 @@
         <v>25</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>3056000</v>
       </c>
       <c r="D103" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="E103" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F103" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -4339,7 +4417,7 @@
         <v>100</v>
       </c>
       <c r="L103">
-        <v>35.5</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4347,22 +4425,22 @@
         <v>12</v>
       </c>
       <c r="B104">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C104">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D104" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="E104" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F104" t="s">
         <v>28</v>
       </c>
       <c r="G104" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -4374,7 +4452,7 @@
         <v>100</v>
       </c>
       <c r="L104">
-        <v>51.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4382,22 +4460,22 @@
         <v>20</v>
       </c>
       <c r="B105">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C105">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="E105" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F105" t="s">
         <v>28</v>
       </c>
       <c r="G105" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -4409,7 +4487,7 @@
         <v>100</v>
       </c>
       <c r="L105">
-        <v>51.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4417,22 +4495,22 @@
         <v>21</v>
       </c>
       <c r="B106">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C106">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D106" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E106" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F106" t="s">
         <v>28</v>
       </c>
       <c r="G106" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -4444,7 +4522,7 @@
         <v>100</v>
       </c>
       <c r="L106">
-        <v>51.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4452,22 +4530,22 @@
         <v>22</v>
       </c>
       <c r="B107">
-        <v>107</v>
+        <v>36</v>
       </c>
       <c r="C107">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D107" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="E107" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F107" t="s">
         <v>28</v>
       </c>
       <c r="G107" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -4479,7 +4557,7 @@
         <v>100</v>
       </c>
       <c r="L107">
-        <v>51.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4487,7 +4565,7 @@
         <v>24</v>
       </c>
       <c r="B108">
-        <v>731</v>
+        <v>563</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -4496,13 +4574,13 @@
         <v>13</v>
       </c>
       <c r="E108" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F108" t="s">
         <v>28</v>
       </c>
       <c r="G108" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -4514,7 +4592,7 @@
         <v>100</v>
       </c>
       <c r="L108">
-        <v>51.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4522,22 +4600,22 @@
         <v>25</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>3000000</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>2658349</v>
       </c>
       <c r="D109" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="E109" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F109" t="s">
         <v>28</v>
       </c>
       <c r="G109" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -4549,7 +4627,7 @@
         <v>100</v>
       </c>
       <c r="L109">
-        <v>51.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4557,22 +4635,22 @@
         <v>12</v>
       </c>
       <c r="B110">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C110">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D110" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E110" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="F110" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G110" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H110" t="s">
         <v>17</v>
@@ -4584,7 +4662,7 @@
         <v>100</v>
       </c>
       <c r="L110">
-        <v>49.9</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -4592,22 +4670,22 @@
         <v>20</v>
       </c>
       <c r="B111">
+        <v>4</v>
+      </c>
+      <c r="C111">
         <v>6</v>
       </c>
-      <c r="C111">
-        <v>2</v>
-      </c>
       <c r="D111" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="E111" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="F111" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G111" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H111" t="s">
         <v>17</v>
@@ -4619,7 +4697,7 @@
         <v>100</v>
       </c>
       <c r="L111">
-        <v>49.9</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -4627,22 +4705,22 @@
         <v>21</v>
       </c>
       <c r="B112">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C112">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E112" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="F112" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G112" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H112" t="s">
         <v>17</v>
@@ -4654,7 +4732,7 @@
         <v>100</v>
       </c>
       <c r="L112">
-        <v>49.9</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -4662,22 +4740,22 @@
         <v>22</v>
       </c>
       <c r="B113">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="C113">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D113" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="E113" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="F113" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G113" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H113" t="s">
         <v>17</v>
@@ -4689,7 +4767,7 @@
         <v>100</v>
       </c>
       <c r="L113">
-        <v>49.9</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -4697,7 +4775,7 @@
         <v>24</v>
       </c>
       <c r="B114">
-        <v>600</v>
+        <v>563</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -4706,13 +4784,13 @@
         <v>13</v>
       </c>
       <c r="E114" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="F114" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G114" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H114" t="s">
         <v>17</v>
@@ -4724,7 +4802,7 @@
         <v>100</v>
       </c>
       <c r="L114">
-        <v>49.9</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -4732,22 +4810,22 @@
         <v>25</v>
       </c>
       <c r="B115">
-        <v>1600000</v>
+        <v>3000000</v>
       </c>
       <c r="C115">
-        <v>1067900</v>
+        <v>3084000</v>
       </c>
       <c r="D115" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="E115" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="F115" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G115" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H115" t="s">
         <v>17</v>
@@ -4759,7 +4837,7 @@
         <v>100</v>
       </c>
       <c r="L115">
-        <v>49.9</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -4767,22 +4845,22 @@
         <v>12</v>
       </c>
       <c r="B116">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C116">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E116" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="F116" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G116" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -4790,14 +4868,11 @@
       <c r="I116" t="s">
         <v>18</v>
       </c>
-      <c r="J116" t="s">
-        <v>68</v>
-      </c>
       <c r="K116">
         <v>100</v>
       </c>
       <c r="L116">
-        <v>68.599999999999994</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -4808,19 +4883,19 @@
         <v>4</v>
       </c>
       <c r="C117">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="E117" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="F117" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G117" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H117" t="s">
         <v>17</v>
@@ -4832,7 +4907,7 @@
         <v>100</v>
       </c>
       <c r="L117">
-        <v>68.599999999999994</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -4840,22 +4915,22 @@
         <v>21</v>
       </c>
       <c r="B118">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C118">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E118" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="F118" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G118" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H118" t="s">
         <v>17</v>
@@ -4867,7 +4942,7 @@
         <v>100</v>
       </c>
       <c r="L118">
-        <v>68.599999999999994</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -4875,22 +4950,22 @@
         <v>22</v>
       </c>
       <c r="B119">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C119">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D119" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="E119" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="F119" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G119" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H119" t="s">
         <v>17</v>
@@ -4902,7 +4977,7 @@
         <v>100</v>
       </c>
       <c r="L119">
-        <v>68.599999999999994</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -4910,7 +4985,7 @@
         <v>24</v>
       </c>
       <c r="B120">
-        <v>413</v>
+        <v>563</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -4919,13 +4994,13 @@
         <v>13</v>
       </c>
       <c r="E120" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="F120" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G120" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H120" t="s">
         <v>17</v>
@@ -4937,7 +5012,7 @@
         <v>100</v>
       </c>
       <c r="L120">
-        <v>68.599999999999994</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -4945,22 +5020,22 @@
         <v>25</v>
       </c>
       <c r="B121">
-        <v>1100000</v>
+        <v>3000000</v>
       </c>
       <c r="C121">
-        <v>718800</v>
+        <v>0</v>
       </c>
       <c r="D121" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="E121" t="s">
-        <v>67</v>
+        <v>99</v>
       </c>
       <c r="F121" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G121" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="H121" t="s">
         <v>17</v>
@@ -4972,7 +5047,7 @@
         <v>100</v>
       </c>
       <c r="L121">
-        <v>68.599999999999994</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -4980,22 +5055,22 @@
         <v>12</v>
       </c>
       <c r="B122">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D122" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E122" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="F122" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G122" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="H122" t="s">
         <v>17</v>
@@ -5003,14 +5078,11 @@
       <c r="I122" t="s">
         <v>18</v>
       </c>
-      <c r="J122" t="s">
-        <v>98</v>
-      </c>
       <c r="K122">
         <v>100</v>
       </c>
       <c r="L122">
-        <v>16.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -5018,22 +5090,22 @@
         <v>20</v>
       </c>
       <c r="B123">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E123" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="F123" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G123" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="H123" t="s">
         <v>17</v>
@@ -5045,7 +5117,7 @@
         <v>100</v>
       </c>
       <c r="L123">
-        <v>16.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5053,22 +5125,22 @@
         <v>21</v>
       </c>
       <c r="B124">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="C124">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="D124" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E124" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="F124" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G124" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="H124" t="s">
         <v>17</v>
@@ -5080,7 +5152,7 @@
         <v>100</v>
       </c>
       <c r="L124">
-        <v>16.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5088,22 +5160,22 @@
         <v>22</v>
       </c>
       <c r="B125">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C125">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D125" t="s">
         <v>23</v>
       </c>
       <c r="E125" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="F125" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G125" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="H125" t="s">
         <v>17</v>
@@ -5115,7 +5187,7 @@
         <v>100</v>
       </c>
       <c r="L125">
-        <v>16.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5123,7 +5195,7 @@
         <v>24</v>
       </c>
       <c r="B126">
-        <v>488</v>
+        <v>675</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -5132,13 +5204,13 @@
         <v>13</v>
       </c>
       <c r="E126" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="F126" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G126" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="H126" t="s">
         <v>17</v>
@@ -5150,7 +5222,7 @@
         <v>100</v>
       </c>
       <c r="L126">
-        <v>16.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -5158,22 +5230,22 @@
         <v>25</v>
       </c>
       <c r="B127">
-        <v>1300000</v>
+        <v>3375000</v>
       </c>
       <c r="C127">
-        <v>80000</v>
+        <v>2813700</v>
       </c>
       <c r="D127" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E127" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="F127" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G127" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="H127" t="s">
         <v>17</v>
@@ -5185,7 +5257,7 @@
         <v>100</v>
       </c>
       <c r="L127">
-        <v>16.5</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5193,22 +5265,22 @@
         <v>12</v>
       </c>
       <c r="B128">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C128">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="E128" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F128" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G128" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H128" t="s">
         <v>17</v>
@@ -5217,13 +5289,13 @@
         <v>18</v>
       </c>
       <c r="J128" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K128">
         <v>100</v>
       </c>
       <c r="L128">
-        <v>33.4</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5240,13 +5312,13 @@
         <v>13</v>
       </c>
       <c r="E129" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F129" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G129" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H129" t="s">
         <v>17</v>
@@ -5258,7 +5330,7 @@
         <v>100</v>
       </c>
       <c r="L129">
-        <v>33.4</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5266,22 +5338,22 @@
         <v>21</v>
       </c>
       <c r="B130">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C130">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D130" t="s">
-        <v>38</v>
+        <v>108</v>
       </c>
       <c r="E130" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F130" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G130" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H130" t="s">
         <v>17</v>
@@ -5293,7 +5365,7 @@
         <v>100</v>
       </c>
       <c r="L130">
-        <v>33.4</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -5301,22 +5373,22 @@
         <v>22</v>
       </c>
       <c r="B131">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="C131">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D131" t="s">
         <v>23</v>
       </c>
       <c r="E131" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F131" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G131" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H131" t="s">
         <v>17</v>
@@ -5328,7 +5400,7 @@
         <v>100</v>
       </c>
       <c r="L131">
-        <v>33.4</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -5336,7 +5408,7 @@
         <v>24</v>
       </c>
       <c r="B132">
-        <v>480</v>
+        <v>366</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -5345,13 +5417,13 @@
         <v>13</v>
       </c>
       <c r="E132" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F132" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G132" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H132" t="s">
         <v>17</v>
@@ -5363,7 +5435,7 @@
         <v>100</v>
       </c>
       <c r="L132">
-        <v>33.4</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5371,22 +5443,22 @@
         <v>25</v>
       </c>
       <c r="B133">
-        <v>2000000</v>
+        <v>1827857</v>
       </c>
       <c r="C133">
-        <v>950000</v>
+        <v>1163900</v>
       </c>
       <c r="D133" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E133" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F133" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G133" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H133" t="s">
         <v>17</v>
@@ -5398,7 +5470,7 @@
         <v>100</v>
       </c>
       <c r="L133">
-        <v>33.4</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5406,22 +5478,22 @@
         <v>12</v>
       </c>
       <c r="B134">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C134">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D134" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E134" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F134" t="s">
         <v>28</v>
       </c>
       <c r="G134" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -5429,11 +5501,14 @@
       <c r="I134" t="s">
         <v>18</v>
       </c>
+      <c r="J134" t="s">
+        <v>111</v>
+      </c>
       <c r="K134">
         <v>100</v>
       </c>
       <c r="L134">
-        <v>56.1</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -5444,19 +5519,19 @@
         <v>0</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D135" t="s">
         <v>13</v>
       </c>
       <c r="E135" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F135" t="s">
         <v>28</v>
       </c>
       <c r="G135" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H135" t="s">
         <v>17</v>
@@ -5468,7 +5543,7 @@
         <v>100</v>
       </c>
       <c r="L135">
-        <v>56.1</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5476,22 +5551,22 @@
         <v>21</v>
       </c>
       <c r="B136">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C136">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D136" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E136" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F136" t="s">
         <v>28</v>
       </c>
       <c r="G136" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
@@ -5503,7 +5578,7 @@
         <v>100</v>
       </c>
       <c r="L136">
-        <v>56.1</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -5511,22 +5586,22 @@
         <v>22</v>
       </c>
       <c r="B137">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="C137">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="D137" t="s">
         <v>23</v>
       </c>
       <c r="E137" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F137" t="s">
         <v>28</v>
       </c>
       <c r="G137" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H137" t="s">
         <v>17</v>
@@ -5538,7 +5613,7 @@
         <v>100</v>
       </c>
       <c r="L137">
-        <v>56.1</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -5546,7 +5621,7 @@
         <v>24</v>
       </c>
       <c r="B138">
-        <v>720</v>
+        <v>591</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -5555,13 +5630,13 @@
         <v>13</v>
       </c>
       <c r="E138" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F138" t="s">
         <v>28</v>
       </c>
       <c r="G138" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H138" t="s">
         <v>17</v>
@@ -5573,7 +5648,7 @@
         <v>100</v>
       </c>
       <c r="L138">
-        <v>56.1</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -5581,22 +5656,22 @@
         <v>25</v>
       </c>
       <c r="B139">
-        <v>3000000</v>
+        <v>2952857</v>
       </c>
       <c r="C139">
-        <v>985000</v>
+        <v>1717900</v>
       </c>
       <c r="D139" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="E139" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F139" t="s">
         <v>28</v>
       </c>
       <c r="G139" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H139" t="s">
         <v>17</v>
@@ -5608,7 +5683,1492 @@
         <v>100</v>
       </c>
       <c r="L139">
-        <v>56.1</v>
+        <v>64.400000000000006</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>12</v>
+      </c>
+      <c r="B140">
+        <v>4</v>
+      </c>
+      <c r="C140">
+        <v>3</v>
+      </c>
+      <c r="D140" t="s">
+        <v>113</v>
+      </c>
+      <c r="E140" t="s">
+        <v>114</v>
+      </c>
+      <c r="F140" t="s">
+        <v>15</v>
+      </c>
+      <c r="G140" t="s">
+        <v>115</v>
+      </c>
+      <c r="H140" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140" t="s">
+        <v>18</v>
+      </c>
+      <c r="J140" t="s">
+        <v>116</v>
+      </c>
+      <c r="K140">
+        <v>100</v>
+      </c>
+      <c r="L140">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>20</v>
+      </c>
+      <c r="B141">
+        <v>1</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141" t="s">
+        <v>13</v>
+      </c>
+      <c r="E141" t="s">
+        <v>114</v>
+      </c>
+      <c r="F141" t="s">
+        <v>15</v>
+      </c>
+      <c r="G141" t="s">
+        <v>115</v>
+      </c>
+      <c r="H141" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" t="s">
+        <v>18</v>
+      </c>
+      <c r="K141">
+        <v>100</v>
+      </c>
+      <c r="L141">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>21</v>
+      </c>
+      <c r="B142">
+        <v>5</v>
+      </c>
+      <c r="C142">
+        <v>5</v>
+      </c>
+      <c r="D142" t="s">
+        <v>33</v>
+      </c>
+      <c r="E142" t="s">
+        <v>114</v>
+      </c>
+      <c r="F142" t="s">
+        <v>15</v>
+      </c>
+      <c r="G142" t="s">
+        <v>115</v>
+      </c>
+      <c r="H142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142" t="s">
+        <v>18</v>
+      </c>
+      <c r="K142">
+        <v>100</v>
+      </c>
+      <c r="L142">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>22</v>
+      </c>
+      <c r="B143">
+        <v>13</v>
+      </c>
+      <c r="C143">
+        <v>9</v>
+      </c>
+      <c r="D143" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143" t="s">
+        <v>114</v>
+      </c>
+      <c r="F143" t="s">
+        <v>15</v>
+      </c>
+      <c r="G143" t="s">
+        <v>115</v>
+      </c>
+      <c r="H143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143" t="s">
+        <v>18</v>
+      </c>
+      <c r="K143">
+        <v>100</v>
+      </c>
+      <c r="L143">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>24</v>
+      </c>
+      <c r="B144">
+        <v>120</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" t="s">
+        <v>114</v>
+      </c>
+      <c r="F144" t="s">
+        <v>15</v>
+      </c>
+      <c r="G144" t="s">
+        <v>115</v>
+      </c>
+      <c r="H144" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144" t="s">
+        <v>18</v>
+      </c>
+      <c r="K144">
+        <v>100</v>
+      </c>
+      <c r="L144">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>25</v>
+      </c>
+      <c r="B145">
+        <v>550000</v>
+      </c>
+      <c r="C145">
+        <v>215000</v>
+      </c>
+      <c r="D145" t="s">
+        <v>30</v>
+      </c>
+      <c r="E145" t="s">
+        <v>114</v>
+      </c>
+      <c r="F145" t="s">
+        <v>15</v>
+      </c>
+      <c r="G145" t="s">
+        <v>115</v>
+      </c>
+      <c r="H145" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145" t="s">
+        <v>18</v>
+      </c>
+      <c r="K145">
+        <v>100</v>
+      </c>
+      <c r="L145">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>12</v>
+      </c>
+      <c r="B146">
+        <v>30</v>
+      </c>
+      <c r="C146">
+        <v>35</v>
+      </c>
+      <c r="D146" t="s">
+        <v>83</v>
+      </c>
+      <c r="E146" t="s">
+        <v>117</v>
+      </c>
+      <c r="F146" t="s">
+        <v>28</v>
+      </c>
+      <c r="G146" t="s">
+        <v>115</v>
+      </c>
+      <c r="H146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146" t="s">
+        <v>18</v>
+      </c>
+      <c r="J146" t="s">
+        <v>118</v>
+      </c>
+      <c r="K146">
+        <v>100</v>
+      </c>
+      <c r="L146">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>20</v>
+      </c>
+      <c r="B147">
+        <v>7</v>
+      </c>
+      <c r="C147">
+        <v>7</v>
+      </c>
+      <c r="D147" t="s">
+        <v>33</v>
+      </c>
+      <c r="E147" t="s">
+        <v>117</v>
+      </c>
+      <c r="F147" t="s">
+        <v>28</v>
+      </c>
+      <c r="G147" t="s">
+        <v>115</v>
+      </c>
+      <c r="H147" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" t="s">
+        <v>18</v>
+      </c>
+      <c r="K147">
+        <v>100</v>
+      </c>
+      <c r="L147">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>21</v>
+      </c>
+      <c r="B148">
+        <v>43</v>
+      </c>
+      <c r="C148">
+        <v>34</v>
+      </c>
+      <c r="D148" t="s">
+        <v>119</v>
+      </c>
+      <c r="E148" t="s">
+        <v>117</v>
+      </c>
+      <c r="F148" t="s">
+        <v>28</v>
+      </c>
+      <c r="G148" t="s">
+        <v>115</v>
+      </c>
+      <c r="H148" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148" t="s">
+        <v>18</v>
+      </c>
+      <c r="K148">
+        <v>100</v>
+      </c>
+      <c r="L148">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>22</v>
+      </c>
+      <c r="B149">
+        <v>111</v>
+      </c>
+      <c r="C149">
+        <v>114</v>
+      </c>
+      <c r="D149" t="s">
+        <v>23</v>
+      </c>
+      <c r="E149" t="s">
+        <v>117</v>
+      </c>
+      <c r="F149" t="s">
+        <v>28</v>
+      </c>
+      <c r="G149" t="s">
+        <v>115</v>
+      </c>
+      <c r="H149" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149" t="s">
+        <v>18</v>
+      </c>
+      <c r="K149">
+        <v>100</v>
+      </c>
+      <c r="L149">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>24</v>
+      </c>
+      <c r="B150">
+        <v>1020</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" t="s">
+        <v>117</v>
+      </c>
+      <c r="F150" t="s">
+        <v>28</v>
+      </c>
+      <c r="G150" t="s">
+        <v>115</v>
+      </c>
+      <c r="H150" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150" t="s">
+        <v>18</v>
+      </c>
+      <c r="K150">
+        <v>100</v>
+      </c>
+      <c r="L150">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>25</v>
+      </c>
+      <c r="B151">
+        <v>4675000</v>
+      </c>
+      <c r="C151">
+        <v>2666000</v>
+      </c>
+      <c r="D151" t="s">
+        <v>120</v>
+      </c>
+      <c r="E151" t="s">
+        <v>117</v>
+      </c>
+      <c r="F151" t="s">
+        <v>28</v>
+      </c>
+      <c r="G151" t="s">
+        <v>115</v>
+      </c>
+      <c r="H151" t="s">
+        <v>17</v>
+      </c>
+      <c r="I151" t="s">
+        <v>18</v>
+      </c>
+      <c r="K151">
+        <v>100</v>
+      </c>
+      <c r="L151">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>12</v>
+      </c>
+      <c r="B152">
+        <v>2</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152" t="s">
+        <v>78</v>
+      </c>
+      <c r="E152" t="s">
+        <v>121</v>
+      </c>
+      <c r="F152" t="s">
+        <v>28</v>
+      </c>
+      <c r="G152" t="s">
+        <v>115</v>
+      </c>
+      <c r="H152" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152" t="s">
+        <v>18</v>
+      </c>
+      <c r="J152" t="s">
+        <v>122</v>
+      </c>
+      <c r="K152">
+        <v>100</v>
+      </c>
+      <c r="L152">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>20</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153" t="s">
+        <v>13</v>
+      </c>
+      <c r="E153" t="s">
+        <v>121</v>
+      </c>
+      <c r="F153" t="s">
+        <v>28</v>
+      </c>
+      <c r="G153" t="s">
+        <v>115</v>
+      </c>
+      <c r="H153" t="s">
+        <v>17</v>
+      </c>
+      <c r="I153" t="s">
+        <v>18</v>
+      </c>
+      <c r="K153">
+        <v>100</v>
+      </c>
+      <c r="L153">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>21</v>
+      </c>
+      <c r="B154">
+        <v>3</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154" t="s">
+        <v>13</v>
+      </c>
+      <c r="E154" t="s">
+        <v>121</v>
+      </c>
+      <c r="F154" t="s">
+        <v>28</v>
+      </c>
+      <c r="G154" t="s">
+        <v>115</v>
+      </c>
+      <c r="H154" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154" t="s">
+        <v>18</v>
+      </c>
+      <c r="K154">
+        <v>100</v>
+      </c>
+      <c r="L154">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>22</v>
+      </c>
+      <c r="B155">
+        <v>7</v>
+      </c>
+      <c r="C155">
+        <v>3</v>
+      </c>
+      <c r="D155" t="s">
+        <v>23</v>
+      </c>
+      <c r="E155" t="s">
+        <v>121</v>
+      </c>
+      <c r="F155" t="s">
+        <v>28</v>
+      </c>
+      <c r="G155" t="s">
+        <v>115</v>
+      </c>
+      <c r="H155" t="s">
+        <v>17</v>
+      </c>
+      <c r="I155" t="s">
+        <v>18</v>
+      </c>
+      <c r="K155">
+        <v>100</v>
+      </c>
+      <c r="L155">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>24</v>
+      </c>
+      <c r="B156">
+        <v>60</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156" t="s">
+        <v>13</v>
+      </c>
+      <c r="E156" t="s">
+        <v>121</v>
+      </c>
+      <c r="F156" t="s">
+        <v>28</v>
+      </c>
+      <c r="G156" t="s">
+        <v>115</v>
+      </c>
+      <c r="H156" t="s">
+        <v>17</v>
+      </c>
+      <c r="I156" t="s">
+        <v>18</v>
+      </c>
+      <c r="K156">
+        <v>100</v>
+      </c>
+      <c r="L156">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>25</v>
+      </c>
+      <c r="B157">
+        <v>275000</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157" t="s">
+        <v>13</v>
+      </c>
+      <c r="E157" t="s">
+        <v>121</v>
+      </c>
+      <c r="F157" t="s">
+        <v>28</v>
+      </c>
+      <c r="G157" t="s">
+        <v>115</v>
+      </c>
+      <c r="H157" t="s">
+        <v>17</v>
+      </c>
+      <c r="I157" t="s">
+        <v>18</v>
+      </c>
+      <c r="K157">
+        <v>100</v>
+      </c>
+      <c r="L157">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>12</v>
+      </c>
+      <c r="B158">
+        <v>13</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" t="s">
+        <v>123</v>
+      </c>
+      <c r="F158" t="s">
+        <v>53</v>
+      </c>
+      <c r="G158" t="s">
+        <v>115</v>
+      </c>
+      <c r="H158" t="s">
+        <v>17</v>
+      </c>
+      <c r="I158" t="s">
+        <v>18</v>
+      </c>
+      <c r="K158">
+        <v>100</v>
+      </c>
+      <c r="L158">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>20</v>
+      </c>
+      <c r="B159">
+        <v>3</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+      <c r="D159" t="s">
+        <v>13</v>
+      </c>
+      <c r="E159" t="s">
+        <v>123</v>
+      </c>
+      <c r="F159" t="s">
+        <v>53</v>
+      </c>
+      <c r="G159" t="s">
+        <v>115</v>
+      </c>
+      <c r="H159" t="s">
+        <v>17</v>
+      </c>
+      <c r="I159" t="s">
+        <v>18</v>
+      </c>
+      <c r="K159">
+        <v>100</v>
+      </c>
+      <c r="L159">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>21</v>
+      </c>
+      <c r="B160">
+        <v>19</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+      <c r="D160" t="s">
+        <v>13</v>
+      </c>
+      <c r="E160" t="s">
+        <v>123</v>
+      </c>
+      <c r="F160" t="s">
+        <v>53</v>
+      </c>
+      <c r="G160" t="s">
+        <v>115</v>
+      </c>
+      <c r="H160" t="s">
+        <v>17</v>
+      </c>
+      <c r="I160" t="s">
+        <v>18</v>
+      </c>
+      <c r="K160">
+        <v>100</v>
+      </c>
+      <c r="L160">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>22</v>
+      </c>
+      <c r="B161">
+        <v>49</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+      <c r="D161" t="s">
+        <v>23</v>
+      </c>
+      <c r="E161" t="s">
+        <v>123</v>
+      </c>
+      <c r="F161" t="s">
+        <v>53</v>
+      </c>
+      <c r="G161" t="s">
+        <v>115</v>
+      </c>
+      <c r="H161" t="s">
+        <v>17</v>
+      </c>
+      <c r="I161" t="s">
+        <v>18</v>
+      </c>
+      <c r="K161">
+        <v>100</v>
+      </c>
+      <c r="L161">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>24</v>
+      </c>
+      <c r="B162">
+        <v>450</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+      <c r="D162" t="s">
+        <v>13</v>
+      </c>
+      <c r="E162" t="s">
+        <v>123</v>
+      </c>
+      <c r="F162" t="s">
+        <v>53</v>
+      </c>
+      <c r="G162" t="s">
+        <v>115</v>
+      </c>
+      <c r="H162" t="s">
+        <v>17</v>
+      </c>
+      <c r="I162" t="s">
+        <v>18</v>
+      </c>
+      <c r="K162">
+        <v>100</v>
+      </c>
+      <c r="L162">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>25</v>
+      </c>
+      <c r="B163">
+        <v>2062500</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+      <c r="D163" t="s">
+        <v>13</v>
+      </c>
+      <c r="E163" t="s">
+        <v>123</v>
+      </c>
+      <c r="F163" t="s">
+        <v>53</v>
+      </c>
+      <c r="G163" t="s">
+        <v>115</v>
+      </c>
+      <c r="H163" t="s">
+        <v>17</v>
+      </c>
+      <c r="I163" t="s">
+        <v>18</v>
+      </c>
+      <c r="K163">
+        <v>100</v>
+      </c>
+      <c r="L163">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>12</v>
+      </c>
+      <c r="B164">
+        <v>11</v>
+      </c>
+      <c r="C164">
+        <v>14</v>
+      </c>
+      <c r="D164" t="s">
+        <v>124</v>
+      </c>
+      <c r="E164" t="s">
+        <v>125</v>
+      </c>
+      <c r="F164" t="s">
+        <v>15</v>
+      </c>
+      <c r="G164" t="s">
+        <v>126</v>
+      </c>
+      <c r="H164" t="s">
+        <v>17</v>
+      </c>
+      <c r="I164" t="s">
+        <v>18</v>
+      </c>
+      <c r="J164" t="s">
+        <v>127</v>
+      </c>
+      <c r="K164">
+        <v>100</v>
+      </c>
+      <c r="L164">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>20</v>
+      </c>
+      <c r="B165">
+        <v>1</v>
+      </c>
+      <c r="C165">
+        <v>2</v>
+      </c>
+      <c r="D165" t="s">
+        <v>128</v>
+      </c>
+      <c r="E165" t="s">
+        <v>125</v>
+      </c>
+      <c r="F165" t="s">
+        <v>15</v>
+      </c>
+      <c r="G165" t="s">
+        <v>126</v>
+      </c>
+      <c r="H165" t="s">
+        <v>17</v>
+      </c>
+      <c r="I165" t="s">
+        <v>18</v>
+      </c>
+      <c r="K165">
+        <v>100</v>
+      </c>
+      <c r="L165">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>21</v>
+      </c>
+      <c r="B166">
+        <v>21</v>
+      </c>
+      <c r="C166">
+        <v>17</v>
+      </c>
+      <c r="D166" t="s">
+        <v>91</v>
+      </c>
+      <c r="E166" t="s">
+        <v>125</v>
+      </c>
+      <c r="F166" t="s">
+        <v>15</v>
+      </c>
+      <c r="G166" t="s">
+        <v>126</v>
+      </c>
+      <c r="H166" t="s">
+        <v>17</v>
+      </c>
+      <c r="I166" t="s">
+        <v>18</v>
+      </c>
+      <c r="K166">
+        <v>100</v>
+      </c>
+      <c r="L166">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>22</v>
+      </c>
+      <c r="B167">
+        <v>54</v>
+      </c>
+      <c r="C167">
+        <v>43</v>
+      </c>
+      <c r="D167" t="s">
+        <v>23</v>
+      </c>
+      <c r="E167" t="s">
+        <v>125</v>
+      </c>
+      <c r="F167" t="s">
+        <v>15</v>
+      </c>
+      <c r="G167" t="s">
+        <v>126</v>
+      </c>
+      <c r="H167" t="s">
+        <v>17</v>
+      </c>
+      <c r="I167" t="s">
+        <v>18</v>
+      </c>
+      <c r="K167">
+        <v>100</v>
+      </c>
+      <c r="L167">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>24</v>
+      </c>
+      <c r="B168">
+        <v>450</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168" t="s">
+        <v>13</v>
+      </c>
+      <c r="E168" t="s">
+        <v>125</v>
+      </c>
+      <c r="F168" t="s">
+        <v>15</v>
+      </c>
+      <c r="G168" t="s">
+        <v>126</v>
+      </c>
+      <c r="H168" t="s">
+        <v>17</v>
+      </c>
+      <c r="I168" t="s">
+        <v>18</v>
+      </c>
+      <c r="K168">
+        <v>100</v>
+      </c>
+      <c r="L168">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>25</v>
+      </c>
+      <c r="B169">
+        <v>1650000</v>
+      </c>
+      <c r="C169">
+        <v>1645900</v>
+      </c>
+      <c r="D169" t="s">
+        <v>33</v>
+      </c>
+      <c r="E169" t="s">
+        <v>125</v>
+      </c>
+      <c r="F169" t="s">
+        <v>15</v>
+      </c>
+      <c r="G169" t="s">
+        <v>126</v>
+      </c>
+      <c r="H169" t="s">
+        <v>17</v>
+      </c>
+      <c r="I169" t="s">
+        <v>18</v>
+      </c>
+      <c r="K169">
+        <v>100</v>
+      </c>
+      <c r="L169">
+        <v>82.3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>12</v>
+      </c>
+      <c r="B170">
+        <v>4</v>
+      </c>
+      <c r="C170">
+        <v>2</v>
+      </c>
+      <c r="D170" t="s">
+        <v>78</v>
+      </c>
+      <c r="E170" t="s">
+        <v>129</v>
+      </c>
+      <c r="F170" t="s">
+        <v>28</v>
+      </c>
+      <c r="G170" t="s">
+        <v>126</v>
+      </c>
+      <c r="H170" t="s">
+        <v>17</v>
+      </c>
+      <c r="I170" t="s">
+        <v>18</v>
+      </c>
+      <c r="J170" t="s">
+        <v>130</v>
+      </c>
+      <c r="K170">
+        <v>100</v>
+      </c>
+      <c r="L170">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>20</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171" t="s">
+        <v>13</v>
+      </c>
+      <c r="E171" t="s">
+        <v>129</v>
+      </c>
+      <c r="F171" t="s">
+        <v>28</v>
+      </c>
+      <c r="G171" t="s">
+        <v>126</v>
+      </c>
+      <c r="H171" t="s">
+        <v>17</v>
+      </c>
+      <c r="I171" t="s">
+        <v>18</v>
+      </c>
+      <c r="K171">
+        <v>100</v>
+      </c>
+      <c r="L171">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>21</v>
+      </c>
+      <c r="B172">
+        <v>7</v>
+      </c>
+      <c r="C172">
+        <v>7</v>
+      </c>
+      <c r="D172" t="s">
+        <v>33</v>
+      </c>
+      <c r="E172" t="s">
+        <v>129</v>
+      </c>
+      <c r="F172" t="s">
+        <v>28</v>
+      </c>
+      <c r="G172" t="s">
+        <v>126</v>
+      </c>
+      <c r="H172" t="s">
+        <v>17</v>
+      </c>
+      <c r="I172" t="s">
+        <v>18</v>
+      </c>
+      <c r="K172">
+        <v>100</v>
+      </c>
+      <c r="L172">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>22</v>
+      </c>
+      <c r="B173">
+        <v>18</v>
+      </c>
+      <c r="C173">
+        <v>3</v>
+      </c>
+      <c r="D173" t="s">
+        <v>23</v>
+      </c>
+      <c r="E173" t="s">
+        <v>129</v>
+      </c>
+      <c r="F173" t="s">
+        <v>28</v>
+      </c>
+      <c r="G173" t="s">
+        <v>126</v>
+      </c>
+      <c r="H173" t="s">
+        <v>17</v>
+      </c>
+      <c r="I173" t="s">
+        <v>18</v>
+      </c>
+      <c r="K173">
+        <v>100</v>
+      </c>
+      <c r="L173">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>24</v>
+      </c>
+      <c r="B174">
+        <v>150</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
+      <c r="D174" t="s">
+        <v>13</v>
+      </c>
+      <c r="E174" t="s">
+        <v>129</v>
+      </c>
+      <c r="F174" t="s">
+        <v>28</v>
+      </c>
+      <c r="G174" t="s">
+        <v>126</v>
+      </c>
+      <c r="H174" t="s">
+        <v>17</v>
+      </c>
+      <c r="I174" t="s">
+        <v>18</v>
+      </c>
+      <c r="K174">
+        <v>100</v>
+      </c>
+      <c r="L174">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>25</v>
+      </c>
+      <c r="B175">
+        <v>550000</v>
+      </c>
+      <c r="C175">
+        <v>200000</v>
+      </c>
+      <c r="D175" t="s">
+        <v>131</v>
+      </c>
+      <c r="E175" t="s">
+        <v>129</v>
+      </c>
+      <c r="F175" t="s">
+        <v>28</v>
+      </c>
+      <c r="G175" t="s">
+        <v>126</v>
+      </c>
+      <c r="H175" t="s">
+        <v>17</v>
+      </c>
+      <c r="I175" t="s">
+        <v>18</v>
+      </c>
+      <c r="K175">
+        <v>100</v>
+      </c>
+      <c r="L175">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>12</v>
+      </c>
+      <c r="B176">
+        <v>21</v>
+      </c>
+      <c r="C176">
+        <v>17</v>
+      </c>
+      <c r="D176" t="s">
+        <v>91</v>
+      </c>
+      <c r="E176" t="s">
+        <v>132</v>
+      </c>
+      <c r="F176" t="s">
+        <v>28</v>
+      </c>
+      <c r="G176" t="s">
+        <v>126</v>
+      </c>
+      <c r="H176" t="s">
+        <v>17</v>
+      </c>
+      <c r="I176" t="s">
+        <v>18</v>
+      </c>
+      <c r="K176">
+        <v>100</v>
+      </c>
+      <c r="L176">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>20</v>
+      </c>
+      <c r="B177">
+        <v>2</v>
+      </c>
+      <c r="C177">
+        <v>0</v>
+      </c>
+      <c r="D177" t="s">
+        <v>13</v>
+      </c>
+      <c r="E177" t="s">
+        <v>132</v>
+      </c>
+      <c r="F177" t="s">
+        <v>28</v>
+      </c>
+      <c r="G177" t="s">
+        <v>126</v>
+      </c>
+      <c r="H177" t="s">
+        <v>17</v>
+      </c>
+      <c r="I177" t="s">
+        <v>18</v>
+      </c>
+      <c r="K177">
+        <v>100</v>
+      </c>
+      <c r="L177">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>21</v>
+      </c>
+      <c r="B178">
+        <v>42</v>
+      </c>
+      <c r="C178">
+        <v>26</v>
+      </c>
+      <c r="D178" t="s">
+        <v>133</v>
+      </c>
+      <c r="E178" t="s">
+        <v>132</v>
+      </c>
+      <c r="F178" t="s">
+        <v>28</v>
+      </c>
+      <c r="G178" t="s">
+        <v>126</v>
+      </c>
+      <c r="H178" t="s">
+        <v>17</v>
+      </c>
+      <c r="I178" t="s">
+        <v>18</v>
+      </c>
+      <c r="K178">
+        <v>100</v>
+      </c>
+      <c r="L178">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>22</v>
+      </c>
+      <c r="B179">
+        <v>108</v>
+      </c>
+      <c r="C179">
+        <v>69</v>
+      </c>
+      <c r="D179" t="s">
+        <v>43</v>
+      </c>
+      <c r="E179" t="s">
+        <v>132</v>
+      </c>
+      <c r="F179" t="s">
+        <v>28</v>
+      </c>
+      <c r="G179" t="s">
+        <v>126</v>
+      </c>
+      <c r="H179" t="s">
+        <v>17</v>
+      </c>
+      <c r="I179" t="s">
+        <v>18</v>
+      </c>
+      <c r="K179">
+        <v>100</v>
+      </c>
+      <c r="L179">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>24</v>
+      </c>
+      <c r="B180">
+        <v>900</v>
+      </c>
+      <c r="C180">
+        <v>0</v>
+      </c>
+      <c r="D180" t="s">
+        <v>13</v>
+      </c>
+      <c r="E180" t="s">
+        <v>132</v>
+      </c>
+      <c r="F180" t="s">
+        <v>28</v>
+      </c>
+      <c r="G180" t="s">
+        <v>126</v>
+      </c>
+      <c r="H180" t="s">
+        <v>17</v>
+      </c>
+      <c r="I180" t="s">
+        <v>18</v>
+      </c>
+      <c r="K180">
+        <v>100</v>
+      </c>
+      <c r="L180">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>25</v>
+      </c>
+      <c r="B181">
+        <v>3300000</v>
+      </c>
+      <c r="C181">
+        <v>1351000</v>
+      </c>
+      <c r="D181" t="s">
+        <v>134</v>
+      </c>
+      <c r="E181" t="s">
+        <v>132</v>
+      </c>
+      <c r="F181" t="s">
+        <v>28</v>
+      </c>
+      <c r="G181" t="s">
+        <v>126</v>
+      </c>
+      <c r="H181" t="s">
+        <v>17</v>
+      </c>
+      <c r="I181" t="s">
+        <v>18</v>
+      </c>
+      <c r="K181">
+        <v>100</v>
+      </c>
+      <c r="L181">
+        <v>56.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/08 Agosto/Liquidacióncvs -agosto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_18416A931278660F62355476585DCE3A87463ED7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1EA3E85-E62F-437C-9463-2793996D37E5}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_2911A43C5441520E62355476585DCE3A87454818" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39A2968A-0D8E-4D62-B09E-6AECCE9CABEE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="155">
   <si>
     <t>Producto</t>
   </si>
@@ -61,370 +61,430 @@
     <t>POSTPAGO</t>
   </si>
   <si>
+    <t>39%</t>
+  </si>
+  <si>
+    <t>Lider Natalie Bolivar Restrepo</t>
+  </si>
+  <si>
+    <t>LIDER</t>
+  </si>
+  <si>
+    <t>CIUDAD BOLIVAR</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>Sin pago (0%)</t>
+  </si>
+  <si>
+    <t>HOGAR</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>TERMINALES</t>
+  </si>
+  <si>
+    <t>69%</t>
+  </si>
+  <si>
+    <t>OTROS</t>
+  </si>
+  <si>
+    <t>Pendiente 4 porta pre</t>
+  </si>
+  <si>
+    <t>CVS PLUS</t>
+  </si>
+  <si>
     <t>0%</t>
   </si>
   <si>
+    <t>ACCESORIOS</t>
+  </si>
+  <si>
+    <t>14%</t>
+  </si>
+  <si>
+    <t>Leidy Yaneth Galeano Ortiz</t>
+  </si>
+  <si>
+    <t>ASESOR</t>
+  </si>
+  <si>
+    <t>Vacaciones del 4 al 20 de agosto</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>59%</t>
+  </si>
+  <si>
+    <t>Lider Paola Andrea Clavijo</t>
+  </si>
+  <si>
+    <t>ENVIGADO</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>64%</t>
+  </si>
+  <si>
+    <t>Luz Enith Sanchez Galeano</t>
+  </si>
+  <si>
+    <t>El 15 pasa al CVS de Sabaneta reemplaza vacaciones de Andrea Arenas</t>
+  </si>
+  <si>
+    <t>67%</t>
+  </si>
+  <si>
+    <t>87%</t>
+  </si>
+  <si>
+    <t>30%</t>
+  </si>
+  <si>
+    <t>Yessica  Restrepo Caicedo</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>27%</t>
+  </si>
+  <si>
+    <t>Kelly Yuliana Ospina Saldarriaga</t>
+  </si>
+  <si>
+    <t>SUPERNUMERARIO</t>
+  </si>
+  <si>
+    <t>61%</t>
+  </si>
+  <si>
+    <t>Lider Yolima Mesa Zapata</t>
+  </si>
+  <si>
+    <t>CALDAS</t>
+  </si>
+  <si>
+    <t>68%</t>
+  </si>
+  <si>
+    <t>31%</t>
+  </si>
+  <si>
+    <t>Darinela  Chavarria Carvajal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacaciones del 4 al 19 de agosto - elabora 12 días </t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>53%</t>
+  </si>
+  <si>
+    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
+  </si>
+  <si>
+    <t>120%</t>
+  </si>
+  <si>
+    <t>49%</t>
+  </si>
+  <si>
+    <t>58%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>54%</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>Vacaciones del 15 al 31 elabora 11 días</t>
+  </si>
+  <si>
+    <t>71%</t>
+  </si>
+  <si>
+    <t>65%</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>Reemplaza vacaciones de Andrea 13 días</t>
+  </si>
+  <si>
+    <t>15%</t>
+  </si>
+  <si>
+    <t>6%</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>Lider Dayana Lopez Llorente</t>
+  </si>
+  <si>
+    <t>SEGOVIA</t>
+  </si>
+  <si>
+    <t>Elabora hasta el 22 , elabora 17 días  meta puntos 623</t>
+  </si>
+  <si>
+    <t>48%</t>
+  </si>
+  <si>
+    <t>117%</t>
+  </si>
+  <si>
+    <t>Luisa Fernanda Miranda Rodriguez</t>
+  </si>
+  <si>
+    <t>42%</t>
+  </si>
+  <si>
+    <t>Lider Paulina Andrea Zapata Jimenez</t>
+  </si>
+  <si>
+    <t>BARBOSA</t>
+  </si>
+  <si>
+    <t>94%</t>
+  </si>
+  <si>
+    <t>153%</t>
+  </si>
+  <si>
+    <t>Evelis Mary Ojeda Baldovino</t>
+  </si>
+  <si>
+    <t>81%</t>
+  </si>
+  <si>
+    <t>89%</t>
+  </si>
+  <si>
+    <t>155%</t>
+  </si>
+  <si>
+    <t>Sene Del Socorro Suarez Torres</t>
+  </si>
+  <si>
+    <t>150%</t>
+  </si>
+  <si>
+    <t>93%</t>
+  </si>
+  <si>
+    <t>131%</t>
+  </si>
+  <si>
+    <t>103%</t>
+  </si>
+  <si>
+    <t>Sara Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>74%</t>
+  </si>
+  <si>
+    <t>Dayanis  Celsa Gamarra</t>
+  </si>
+  <si>
+    <t>EL BAGRE</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>83%</t>
+  </si>
+  <si>
+    <t>Darly Esther Sola Tarriba</t>
+  </si>
+  <si>
+    <t>Vacaciones del 18 de agosto al 3 de septiembre</t>
+  </si>
+  <si>
+    <t>44%</t>
+  </si>
+  <si>
+    <t>130%</t>
+  </si>
+  <si>
+    <t>Jeider Alberto Moreno Solano</t>
+  </si>
+  <si>
+    <t>Ingresa el 10 de agosto</t>
+  </si>
+  <si>
+    <t>45%</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>Líder Sara Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t>GIRARDOTA</t>
+  </si>
+  <si>
+    <t>6 días Líder</t>
+  </si>
+  <si>
+    <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+  </si>
+  <si>
+    <t>15 días sola sin apoyo de líder</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
+    <t>57%</t>
+  </si>
+  <si>
+    <t>Yuliana Ospina Saldarriaga</t>
+  </si>
+  <si>
+    <t>3 días Líder</t>
+  </si>
+  <si>
+    <t>Eduar Alonso Olaya Estrada</t>
+  </si>
+  <si>
+    <t>127%</t>
+  </si>
+  <si>
+    <t>Lider Luz Stella Serna</t>
+  </si>
+  <si>
+    <t>TERMINAL NORTE</t>
+  </si>
+  <si>
+    <t>Incapacidad 6 días</t>
+  </si>
+  <si>
+    <t>200%</t>
+  </si>
+  <si>
+    <t>Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t>Líder 6 días</t>
+  </si>
+  <si>
+    <t>36%</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Posada Galeano</t>
+  </si>
+  <si>
+    <t>62%</t>
+  </si>
+  <si>
+    <t>41%</t>
+  </si>
+  <si>
+    <t>Lider Leider  Alexander Calderon</t>
+  </si>
+  <si>
+    <t>JUNIN</t>
+  </si>
+  <si>
+    <t>138%</t>
+  </si>
+  <si>
+    <t>Jessica Catherine Gutierrez Garcia</t>
+  </si>
+  <si>
+    <t>125%</t>
+  </si>
+  <si>
+    <t>142%</t>
+  </si>
+  <si>
+    <t>Nasly Johanna Martinez Ocampo</t>
+  </si>
+  <si>
+    <t>108%</t>
+  </si>
+  <si>
+    <t>Sandra Milena Carmona Galeano</t>
+  </si>
+  <si>
+    <t>Incapacidad 5 días</t>
+  </si>
+  <si>
+    <t>113%</t>
+  </si>
+  <si>
+    <t>Lider Geraldin Angulo Jaramillo</t>
+  </si>
+  <si>
+    <t>YARUMAL</t>
+  </si>
+  <si>
+    <t>Cubre vacaciones de la cajera del 25 al 31 de agosto</t>
+  </si>
+  <si>
+    <t>106%</t>
+  </si>
+  <si>
+    <t>Laura Carolina Chavarria Amariles</t>
+  </si>
+  <si>
+    <t>76%</t>
+  </si>
+  <si>
     <t>Lider Nechi Maricela Ravelo Hernandez</t>
   </si>
   <si>
-    <t>LIDER</t>
-  </si>
-  <si>
     <t>NECHI</t>
   </si>
   <si>
-    <t>2026-08</t>
-  </si>
-  <si>
-    <t>Sin pago (0%)</t>
-  </si>
-  <si>
     <t>Vac del 1 al 20 de agosto</t>
   </si>
   <si>
-    <t>HOGAR</t>
-  </si>
-  <si>
-    <t>TERMINALES</t>
-  </si>
-  <si>
-    <t>OTROS</t>
-  </si>
-  <si>
-    <t>Pendiente 4 porta pre</t>
-  </si>
-  <si>
-    <t>CVS PLUS</t>
-  </si>
-  <si>
-    <t>ACCESORIOS</t>
-  </si>
-  <si>
-    <t>23%</t>
+    <t>118%</t>
+  </si>
+  <si>
+    <t>123%</t>
+  </si>
+  <si>
+    <t>85%</t>
   </si>
   <si>
     <t>LeidisÂ  Rosa Luna Serpa</t>
   </si>
   <si>
-    <t>ASESOR</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>39%</t>
-  </si>
-  <si>
-    <t>Lider Natalie Bolivar Restrepo</t>
-  </si>
-  <si>
-    <t>CIUDAD BOLIVAR</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>69%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>Leidy Yaneth Galeano Ortiz</t>
-  </si>
-  <si>
-    <t>Vacaciones del 4 al 20 de agosto</t>
-  </si>
-  <si>
-    <t>29%</t>
-  </si>
-  <si>
-    <t>59%</t>
-  </si>
-  <si>
-    <t>Lider Paola Andrea Clavijo</t>
-  </si>
-  <si>
-    <t>ENVIGADO</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>64%</t>
-  </si>
-  <si>
-    <t>Luz Enith Sanchez Galeano</t>
-  </si>
-  <si>
-    <t>El 15 pasa al CVS de Sabaneta reemplaza vacaciones de Andrea Arenas</t>
-  </si>
-  <si>
-    <t>67%</t>
-  </si>
-  <si>
-    <t>87%</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
-    <t>Yessica  Restrepo Caicedo</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>27%</t>
-  </si>
-  <si>
-    <t>Kelly Yuliana Ospina Saldarriaga</t>
-  </si>
-  <si>
-    <t>SUPERNUMERARIO</t>
-  </si>
-  <si>
-    <t>61%</t>
-  </si>
-  <si>
-    <t>Lider Yolima Mesa Zapata</t>
-  </si>
-  <si>
-    <t>CALDAS</t>
-  </si>
-  <si>
-    <t>68%</t>
-  </si>
-  <si>
-    <t>31%</t>
-  </si>
-  <si>
-    <t>Darinela  Chavarria Carvajal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vacaciones del 4 al 19 de agosto - elabora 12 días </t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
-    <t>53%</t>
-  </si>
-  <si>
-    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
-  </si>
-  <si>
-    <t>120%</t>
-  </si>
-  <si>
-    <t>49%</t>
-  </si>
-  <si>
-    <t>58%</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Arbelaez</t>
-  </si>
-  <si>
-    <t>SABANETA</t>
-  </si>
-  <si>
-    <t>54%</t>
-  </si>
-  <si>
-    <t>Andrea  Arenas Hurtado</t>
-  </si>
-  <si>
-    <t>Vacaciones del 15 al 31 elabora 11 días</t>
-  </si>
-  <si>
-    <t>71%</t>
-  </si>
-  <si>
-    <t>65%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>Reemplaza vacaciones de Andrea 13 días</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>Lider Dayana Lopez Llorente</t>
-  </si>
-  <si>
-    <t>SEGOVIA</t>
-  </si>
-  <si>
-    <t>Elabora hasta el 22 , elabora 17 días  meta puntos 623</t>
-  </si>
-  <si>
-    <t>48%</t>
-  </si>
-  <si>
-    <t>117%</t>
-  </si>
-  <si>
-    <t>Luisa Fernanda Miranda Rodriguez</t>
-  </si>
-  <si>
-    <t>42%</t>
-  </si>
-  <si>
-    <t>Lider Paulina Andrea Zapata Jimenez</t>
-  </si>
-  <si>
-    <t>BARBOSA</t>
-  </si>
-  <si>
-    <t>94%</t>
-  </si>
-  <si>
-    <t>153%</t>
-  </si>
-  <si>
-    <t>Evelis Mary Ojeda Baldovino</t>
-  </si>
-  <si>
-    <t>81%</t>
-  </si>
-  <si>
-    <t>89%</t>
-  </si>
-  <si>
-    <t>155%</t>
-  </si>
-  <si>
-    <t>Sene Del Socorro Suarez Torres</t>
-  </si>
-  <si>
-    <t>150%</t>
-  </si>
-  <si>
-    <t>93%</t>
-  </si>
-  <si>
-    <t>131%</t>
-  </si>
-  <si>
-    <t>103%</t>
-  </si>
-  <si>
-    <t>Sara Julieth Acevedo Gutierrez</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>74%</t>
-  </si>
-  <si>
-    <t>Dayanis  Celsa Gamarra</t>
-  </si>
-  <si>
-    <t>EL BAGRE</t>
-  </si>
-  <si>
-    <t>80%</t>
-  </si>
-  <si>
-    <t>83%</t>
-  </si>
-  <si>
-    <t>Darly Esther Sola Tarriba</t>
-  </si>
-  <si>
-    <t>Vacaciones del 18 de agosto al 3 de septiembre</t>
-  </si>
-  <si>
-    <t>44%</t>
-  </si>
-  <si>
-    <t>130%</t>
-  </si>
-  <si>
-    <t>Jeider Alberto Moreno Solano</t>
-  </si>
-  <si>
-    <t>Ingresa el 10 de agosto</t>
-  </si>
-  <si>
-    <t>45%</t>
-  </si>
-  <si>
-    <t>75%</t>
-  </si>
-  <si>
-    <t>Líder Sara Julieth Acevedo Gutierrez</t>
-  </si>
-  <si>
-    <t>GIRARDOTA</t>
-  </si>
-  <si>
-    <t>6 días Líder</t>
-  </si>
-  <si>
-    <t>Narelig Alejandra GarcÃ­a Ramirez</t>
-  </si>
-  <si>
-    <t>15 días sola sin apoyo de líder</t>
-  </si>
-  <si>
-    <t>79%</t>
-  </si>
-  <si>
-    <t>57%</t>
-  </si>
-  <si>
-    <t>Yuliana Ospina Saldarriaga</t>
-  </si>
-  <si>
-    <t>3 días Líder</t>
-  </si>
-  <si>
-    <t>Eduar Alonso Olaya Estrada</t>
-  </si>
-  <si>
-    <t>127%</t>
-  </si>
-  <si>
-    <t>Lider Luz Stella Serna</t>
-  </si>
-  <si>
-    <t>TERMINAL NORTE</t>
-  </si>
-  <si>
-    <t>Incapacidad 6 días</t>
-  </si>
-  <si>
-    <t>200%</t>
-  </si>
-  <si>
-    <t>Julieth Acevedo Gutierrez</t>
-  </si>
-  <si>
-    <t>Líder 6 días</t>
-  </si>
-  <si>
-    <t>36%</t>
-  </si>
-  <si>
-    <t>Maria Fernanda Posada Galeano</t>
-  </si>
-  <si>
-    <t>62%</t>
-  </si>
-  <si>
-    <t>41%</t>
+    <t>66%</t>
   </si>
 </sst>
 </file>
@@ -443,7 +503,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -788,7 +847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L181"/>
+  <dimension ref="A1:L217"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -834,10 +893,10 @@
         <v>12</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
         <v>13</v>
@@ -857,28 +916,25 @@
       <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
       <c r="K2">
         <v>100</v>
       </c>
       <c r="L2">
-        <v>0.3</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
         <v>20</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -899,7 +955,7 @@
         <v>100</v>
       </c>
       <c r="L3">
-        <v>0.3</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -907,13 +963,13 @@
         <v>21</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
         <v>14</v>
@@ -934,21 +990,21 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>0.3</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -969,21 +1025,21 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>0.3</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
         <v>14</v>
@@ -1004,21 +1060,21 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>0.3</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B7">
-        <v>600000</v>
+        <v>3987500</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -1039,7 +1095,7 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>0.3</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -1047,19 +1103,19 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
         <v>16</v>
@@ -1070,16 +1126,19 @@
       <c r="I8" t="s">
         <v>18</v>
       </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>26.3</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1088,13 +1147,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
         <v>16</v>
@@ -1109,7 +1168,7 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>26.3</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -1117,19 +1176,19 @@
         <v>21</v>
       </c>
       <c r="B10">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
         <v>29</v>
       </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
         <v>16</v>
@@ -1144,27 +1203,27 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>26.3</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="C11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
         <v>16</v>
@@ -1179,27 +1238,27 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>26.3</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12">
-        <v>680</v>
+        <v>220</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
         <v>16</v>
@@ -1214,27 +1273,27 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>26.3</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13">
-        <v>3400000</v>
+        <v>1512500</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
         <v>16</v>
@@ -1249,7 +1308,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>26.3</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1257,22 +1316,22 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F14" t="s">
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H14" t="s">
         <v>17</v>
@@ -1284,30 +1343,30 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>62.3</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F15" t="s">
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H15" t="s">
         <v>17</v>
@@ -1319,7 +1378,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>62.3</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1327,22 +1386,22 @@
         <v>21</v>
       </c>
       <c r="B16">
+        <v>30</v>
+      </c>
+      <c r="C16">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
         <v>36</v>
       </c>
-      <c r="C16">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>34</v>
-      </c>
-      <c r="E16" t="s">
-        <v>31</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H16" t="s">
         <v>17</v>
@@ -1354,30 +1413,30 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>62.3</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="C17">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H17" t="s">
         <v>17</v>
@@ -1389,30 +1448,30 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>62.3</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18">
-        <v>580</v>
+        <v>497</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
         <v>15</v>
       </c>
       <c r="G18" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H18" t="s">
         <v>17</v>
@@ -1424,30 +1483,30 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>62.3</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B19">
-        <v>3987500</v>
+        <v>1490786</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
         <v>15</v>
       </c>
       <c r="G19" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H19" t="s">
         <v>17</v>
@@ -1459,7 +1518,7 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>62.3</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
@@ -1467,23 +1526,23 @@
         <v>12</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
         <v>35</v>
       </c>
-      <c r="E20" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G20" t="s">
-        <v>32</v>
-      </c>
       <c r="H20" t="s">
         <v>17</v>
       </c>
@@ -1491,36 +1550,36 @@
         <v>18</v>
       </c>
       <c r="J20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K20">
         <v>100</v>
       </c>
       <c r="L20">
-        <v>30.1</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H21" t="s">
         <v>17</v>
@@ -1532,7 +1591,7 @@
         <v>100</v>
       </c>
       <c r="L21">
-        <v>30.1</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -1540,22 +1599,22 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" t="s">
         <v>38</v>
       </c>
-      <c r="E22" t="s">
-        <v>36</v>
-      </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1567,30 +1626,30 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>30.1</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C23">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F23" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1602,30 +1661,30 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>30.1</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B24">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F24" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1637,30 +1696,30 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>30.1</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B25">
-        <v>1512500</v>
+        <v>773357</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1672,7 +1731,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>30.1</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -1680,22 +1739,22 @@
         <v>12</v>
       </c>
       <c r="B26">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C26">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E26" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -1707,30 +1766,30 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>38.6</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C27">
         <v>2</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E27" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F27" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
@@ -1742,7 +1801,7 @@
         <v>100</v>
       </c>
       <c r="L27">
-        <v>38.6</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1750,22 +1809,22 @@
         <v>21</v>
       </c>
       <c r="B28">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C28">
         <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F28" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G28" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1777,30 +1836,30 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>38.6</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B29">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="C29">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G29" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -1812,30 +1871,30 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>38.6</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B30">
-        <v>497</v>
+        <v>745</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G30" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -1847,30 +1906,30 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>38.6</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B31">
-        <v>1490786</v>
+        <v>2235857</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F31" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G31" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -1882,7 +1941,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>38.6</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -1890,22 +1949,22 @@
         <v>12</v>
       </c>
       <c r="B32">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F32" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G32" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
@@ -1913,37 +1972,34 @@
       <c r="I32" t="s">
         <v>18</v>
       </c>
-      <c r="J32" t="s">
-        <v>45</v>
-      </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>58.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" t="s">
         <v>46</v>
       </c>
-      <c r="E33" t="s">
-        <v>44</v>
-      </c>
       <c r="F33" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G33" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
@@ -1955,7 +2011,7 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>58.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -1963,22 +2019,22 @@
         <v>21</v>
       </c>
       <c r="B34">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C34">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" t="s">
         <v>47</v>
       </c>
-      <c r="E34" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" t="s">
-        <v>28</v>
-      </c>
       <c r="G34" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -1990,30 +2046,30 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>58.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B35">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C35">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F35" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G35" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -2025,30 +2081,30 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>58.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B36">
-        <v>258</v>
+        <v>563</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G36" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -2060,30 +2116,30 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>58.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B37">
-        <v>773357</v>
+        <v>1687500</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F37" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G37" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
@@ -2095,7 +2151,7 @@
         <v>100</v>
       </c>
       <c r="L37">
-        <v>58.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2103,10 +2159,10 @@
         <v>12</v>
       </c>
       <c r="B38">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C38">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D38" t="s">
         <v>48</v>
@@ -2115,10 +2171,10 @@
         <v>49</v>
       </c>
       <c r="F38" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -2130,30 +2186,30 @@
         <v>100</v>
       </c>
       <c r="L38">
-        <v>22.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39">
+        <v>3</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39" t="s">
         <v>20</v>
-      </c>
-      <c r="B39">
-        <v>10</v>
-      </c>
-      <c r="C39">
-        <v>2</v>
-      </c>
-      <c r="D39" t="s">
-        <v>50</v>
       </c>
       <c r="E39" t="s">
         <v>49</v>
       </c>
       <c r="F39" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -2165,7 +2221,7 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>22.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2173,10 +2229,10 @@
         <v>21</v>
       </c>
       <c r="B40">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C40">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D40" t="s">
         <v>51</v>
@@ -2185,10 +2241,10 @@
         <v>49</v>
       </c>
       <c r="F40" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
@@ -2200,30 +2256,30 @@
         <v>100</v>
       </c>
       <c r="L40">
-        <v>22.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B41">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="C41">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E41" t="s">
         <v>49</v>
       </c>
       <c r="F41" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -2235,30 +2291,30 @@
         <v>100</v>
       </c>
       <c r="L41">
-        <v>22.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B42">
-        <v>745</v>
+        <v>487</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E42" t="s">
         <v>49</v>
       </c>
       <c r="F42" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2270,30 +2326,30 @@
         <v>100</v>
       </c>
       <c r="L42">
-        <v>22.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B43">
-        <v>2235857</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>4138900</v>
       </c>
       <c r="D43" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E43" t="s">
         <v>49</v>
       </c>
       <c r="F43" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -2305,7 +2361,7 @@
         <v>100</v>
       </c>
       <c r="L43">
-        <v>22.2</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2313,22 +2369,22 @@
         <v>12</v>
       </c>
       <c r="B44">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="E44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F44" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
@@ -2336,34 +2392,37 @@
       <c r="I44" t="s">
         <v>18</v>
       </c>
+      <c r="J44" t="s">
+        <v>54</v>
+      </c>
       <c r="K44">
         <v>100</v>
       </c>
       <c r="L44">
-        <v>0.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+      <c r="D45" t="s">
         <v>20</v>
       </c>
-      <c r="B45">
-        <v>8</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
-      </c>
-      <c r="D45" t="s">
-        <v>13</v>
-      </c>
       <c r="E45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F45" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
@@ -2375,7 +2434,7 @@
         <v>100</v>
       </c>
       <c r="L45">
-        <v>0.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2383,22 +2442,22 @@
         <v>21</v>
       </c>
       <c r="B46">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F46" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2410,30 +2469,30 @@
         <v>100</v>
       </c>
       <c r="L46">
-        <v>0.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B47">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F47" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2445,30 +2504,30 @@
         <v>100</v>
       </c>
       <c r="L47">
-        <v>0.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B48">
-        <v>563</v>
+        <v>281</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F48" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G48" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
@@ -2480,30 +2539,30 @@
         <v>100</v>
       </c>
       <c r="L48">
-        <v>0.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B49">
-        <v>1687500</v>
+        <v>0</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G49" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -2515,7 +2574,7 @@
         <v>100</v>
       </c>
       <c r="L49">
-        <v>0.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2523,22 +2582,22 @@
         <v>12</v>
       </c>
       <c r="B50">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C50">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F50" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G50" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -2550,30 +2609,30 @@
         <v>100</v>
       </c>
       <c r="L50">
-        <v>58.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="E51" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F51" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
@@ -2585,7 +2644,7 @@
         <v>100</v>
       </c>
       <c r="L51">
-        <v>58.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2593,22 +2652,22 @@
         <v>21</v>
       </c>
       <c r="B52">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C52">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D52" t="s">
+        <v>59</v>
+      </c>
+      <c r="E52" t="s">
         <v>57</v>
       </c>
-      <c r="E52" t="s">
-        <v>55</v>
-      </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G52" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -2620,31 +2679,31 @@
         <v>100</v>
       </c>
       <c r="L52">
-        <v>58.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B53">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="C53">
+        <v>62</v>
+      </c>
+      <c r="D53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" t="s">
+        <v>57</v>
+      </c>
+      <c r="F53" t="s">
+        <v>30</v>
+      </c>
+      <c r="G53" t="s">
         <v>50</v>
       </c>
-      <c r="D53" t="s">
-        <v>23</v>
-      </c>
-      <c r="E53" t="s">
-        <v>55</v>
-      </c>
-      <c r="F53" t="s">
-        <v>15</v>
-      </c>
-      <c r="G53" t="s">
-        <v>56</v>
-      </c>
       <c r="H53" t="s">
         <v>17</v>
       </c>
@@ -2655,30 +2714,30 @@
         <v>100</v>
       </c>
       <c r="L53">
-        <v>58.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B54">
-        <v>487</v>
+        <v>731</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E54" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G54" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -2690,30 +2749,30 @@
         <v>100</v>
       </c>
       <c r="L54">
-        <v>58.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B55">
         <v>0</v>
       </c>
       <c r="C55">
-        <v>4138900</v>
+        <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E55" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G55" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
@@ -2725,7 +2784,7 @@
         <v>100</v>
       </c>
       <c r="L55">
-        <v>58.4</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -2733,22 +2792,22 @@
         <v>12</v>
       </c>
       <c r="B56">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C56">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D56" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E56" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F56" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
@@ -2756,37 +2815,34 @@
       <c r="I56" t="s">
         <v>18</v>
       </c>
-      <c r="J56" t="s">
-        <v>60</v>
-      </c>
       <c r="K56">
         <v>100</v>
       </c>
       <c r="L56">
-        <v>35.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C57">
         <v>2</v>
       </c>
       <c r="D57" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="E57" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F57" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
@@ -2798,7 +2854,7 @@
         <v>100</v>
       </c>
       <c r="L57">
-        <v>35.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -2806,22 +2862,22 @@
         <v>21</v>
       </c>
       <c r="B58">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C58">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D58" t="s">
+        <v>64</v>
+      </c>
+      <c r="E58" t="s">
         <v>61</v>
       </c>
-      <c r="E58" t="s">
-        <v>59</v>
-      </c>
       <c r="F58" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
@@ -2833,30 +2889,30 @@
         <v>100</v>
       </c>
       <c r="L58">
-        <v>35.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B59">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="C59">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F59" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
@@ -2868,30 +2924,30 @@
         <v>100</v>
       </c>
       <c r="L59">
-        <v>35.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B60">
-        <v>281</v>
+        <v>600</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E60" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F60" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -2903,30 +2959,30 @@
         <v>100</v>
       </c>
       <c r="L60">
-        <v>35.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>1600000</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1067900</v>
       </c>
       <c r="D61" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E61" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F61" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
@@ -2938,7 +2994,7 @@
         <v>100</v>
       </c>
       <c r="L61">
-        <v>35.5</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -2946,57 +3002,60 @@
         <v>12</v>
       </c>
       <c r="B62">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C62">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D62" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" t="s">
+        <v>65</v>
+      </c>
+      <c r="F62" t="s">
+        <v>30</v>
+      </c>
+      <c r="G62" t="s">
         <v>62</v>
       </c>
-      <c r="E62" t="s">
-        <v>63</v>
-      </c>
-      <c r="F62" t="s">
-        <v>28</v>
-      </c>
-      <c r="G62" t="s">
-        <v>56</v>
-      </c>
       <c r="H62" t="s">
         <v>17</v>
       </c>
       <c r="I62" t="s">
         <v>18</v>
       </c>
+      <c r="J62" t="s">
+        <v>66</v>
+      </c>
       <c r="K62">
         <v>100</v>
       </c>
       <c r="L62">
-        <v>51.1</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>4</v>
+      </c>
+      <c r="D63" t="s">
         <v>20</v>
       </c>
-      <c r="B63">
-        <v>5</v>
-      </c>
-      <c r="C63">
-        <v>6</v>
-      </c>
-      <c r="D63" t="s">
-        <v>64</v>
-      </c>
       <c r="E63" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F63" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G63" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
@@ -3008,7 +3067,7 @@
         <v>100</v>
       </c>
       <c r="L63">
-        <v>51.1</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3016,22 +3075,22 @@
         <v>21</v>
       </c>
       <c r="B64">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="C64">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>56</v>
+      </c>
+      <c r="E64" t="s">
         <v>65</v>
       </c>
-      <c r="E64" t="s">
-        <v>63</v>
-      </c>
       <c r="F64" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G64" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -3043,31 +3102,31 @@
         <v>100</v>
       </c>
       <c r="L64">
-        <v>51.1</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B65">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="C65">
+        <v>41</v>
+      </c>
+      <c r="D65" t="s">
+        <v>67</v>
+      </c>
+      <c r="E65" t="s">
+        <v>65</v>
+      </c>
+      <c r="F65" t="s">
+        <v>30</v>
+      </c>
+      <c r="G65" t="s">
         <v>62</v>
       </c>
-      <c r="D65" t="s">
-        <v>66</v>
-      </c>
-      <c r="E65" t="s">
-        <v>63</v>
-      </c>
-      <c r="F65" t="s">
-        <v>28</v>
-      </c>
-      <c r="G65" t="s">
-        <v>56</v>
-      </c>
       <c r="H65" t="s">
         <v>17</v>
       </c>
@@ -3078,30 +3137,30 @@
         <v>100</v>
       </c>
       <c r="L65">
-        <v>51.1</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B66">
-        <v>731</v>
+        <v>413</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E66" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F66" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G66" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
@@ -3113,30 +3172,30 @@
         <v>100</v>
       </c>
       <c r="L66">
-        <v>51.1</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>1100000</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>718800</v>
       </c>
       <c r="D67" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="E67" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F67" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G67" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -3148,7 +3207,7 @@
         <v>100</v>
       </c>
       <c r="L67">
-        <v>51.1</v>
+        <v>68.599999999999994</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3156,22 +3215,22 @@
         <v>12</v>
       </c>
       <c r="B68">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C68">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D68" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="E68" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F68" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G68" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
@@ -3179,34 +3238,37 @@
       <c r="I68" t="s">
         <v>18</v>
       </c>
+      <c r="J68" t="s">
+        <v>70</v>
+      </c>
       <c r="K68">
         <v>100</v>
       </c>
       <c r="L68">
-        <v>49.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B69">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E69" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F69" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G69" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -3218,7 +3280,7 @@
         <v>100</v>
       </c>
       <c r="L69">
-        <v>49.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3226,22 +3288,22 @@
         <v>21</v>
       </c>
       <c r="B70">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C70">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E70" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F70" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G70" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -3253,30 +3315,30 @@
         <v>100</v>
       </c>
       <c r="L70">
-        <v>49.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B71">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C71">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F71" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G71" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -3288,30 +3350,30 @@
         <v>100</v>
       </c>
       <c r="L71">
-        <v>49.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B72">
-        <v>600</v>
+        <v>488</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E72" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F72" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G72" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -3323,30 +3385,30 @@
         <v>100</v>
       </c>
       <c r="L72">
-        <v>49.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B73">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="C73">
-        <v>1067900</v>
+        <v>80000</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="E73" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="F73" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G73" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -3358,7 +3420,7 @@
         <v>100</v>
       </c>
       <c r="L73">
-        <v>49.9</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3366,22 +3428,22 @@
         <v>12</v>
       </c>
       <c r="B74">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C74">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D74" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="E74" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F74" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -3390,36 +3452,36 @@
         <v>18</v>
       </c>
       <c r="J74" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K74">
         <v>100</v>
       </c>
       <c r="L74">
-        <v>68.599999999999994</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E75" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F75" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -3431,7 +3493,7 @@
         <v>100</v>
       </c>
       <c r="L75">
-        <v>68.599999999999994</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3439,22 +3501,22 @@
         <v>21</v>
       </c>
       <c r="B76">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C76">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D76" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="E76" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F76" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -3466,30 +3528,30 @@
         <v>100</v>
       </c>
       <c r="L76">
-        <v>68.599999999999994</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B77">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C77">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D77" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F77" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -3501,30 +3563,30 @@
         <v>100</v>
       </c>
       <c r="L77">
-        <v>68.599999999999994</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B78">
-        <v>413</v>
+        <v>480</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E78" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F78" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -3536,30 +3598,30 @@
         <v>100</v>
       </c>
       <c r="L78">
-        <v>68.599999999999994</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B79">
-        <v>1100000</v>
+        <v>2000000</v>
       </c>
       <c r="C79">
-        <v>718800</v>
+        <v>950000</v>
       </c>
       <c r="D79" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E79" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F79" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -3571,7 +3633,7 @@
         <v>100</v>
       </c>
       <c r="L79">
-        <v>68.599999999999994</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -3579,22 +3641,22 @@
         <v>12</v>
       </c>
       <c r="B80">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C80">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D80" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E80" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="F80" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G80" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -3602,37 +3664,34 @@
       <c r="I80" t="s">
         <v>18</v>
       </c>
-      <c r="J80" t="s">
-        <v>75</v>
-      </c>
       <c r="K80">
         <v>100</v>
       </c>
       <c r="L80">
-        <v>16.5</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="E81" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="F81" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G81" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -3644,7 +3703,7 @@
         <v>100</v>
       </c>
       <c r="L81">
-        <v>16.5</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -3652,22 +3711,22 @@
         <v>21</v>
       </c>
       <c r="B82">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D82" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E82" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="F82" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G82" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -3679,30 +3738,30 @@
         <v>100</v>
       </c>
       <c r="L82">
-        <v>16.5</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B83">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="C83">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="D83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="F83" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G83" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -3714,30 +3773,30 @@
         <v>100</v>
       </c>
       <c r="L83">
-        <v>16.5</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B84">
-        <v>488</v>
+        <v>720</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E84" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="F84" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G84" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -3749,30 +3808,30 @@
         <v>100</v>
       </c>
       <c r="L84">
-        <v>16.5</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B85">
-        <v>1300000</v>
+        <v>3000000</v>
       </c>
       <c r="C85">
-        <v>80000</v>
+        <v>985000</v>
       </c>
       <c r="D85" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E85" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="F85" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G85" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
@@ -3784,7 +3843,7 @@
         <v>100</v>
       </c>
       <c r="L85">
-        <v>16.5</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -3792,22 +3851,22 @@
         <v>12</v>
       </c>
       <c r="B86">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C86">
         <v>8</v>
       </c>
       <c r="D86" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F86" t="s">
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
@@ -3815,37 +3874,34 @@
       <c r="I86" t="s">
         <v>18</v>
       </c>
-      <c r="J86" t="s">
-        <v>81</v>
-      </c>
       <c r="K86">
         <v>100</v>
       </c>
       <c r="L86">
-        <v>33.4</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="E87" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F87" t="s">
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -3857,7 +3913,7 @@
         <v>100</v>
       </c>
       <c r="L87">
-        <v>33.4</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -3865,22 +3921,22 @@
         <v>21</v>
       </c>
       <c r="B88">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C88">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D88" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="E88" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F88" t="s">
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -3892,30 +3948,30 @@
         <v>100</v>
       </c>
       <c r="L88">
-        <v>33.4</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B89">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="C89">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E89" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F89" t="s">
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -3927,30 +3983,30 @@
         <v>100</v>
       </c>
       <c r="L89">
-        <v>33.4</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B90">
-        <v>480</v>
+        <v>375</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E90" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F90" t="s">
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -3962,30 +4018,30 @@
         <v>100</v>
       </c>
       <c r="L90">
-        <v>33.4</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B91">
         <v>2000000</v>
       </c>
       <c r="C91">
-        <v>950000</v>
+        <v>3056000</v>
       </c>
       <c r="D91" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E91" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F91" t="s">
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -3997,7 +4053,7 @@
         <v>100</v>
       </c>
       <c r="L91">
-        <v>33.4</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4005,22 +4061,22 @@
         <v>12</v>
       </c>
       <c r="B92">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C92">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="D92" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="E92" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F92" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G92" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -4032,30 +4088,30 @@
         <v>100</v>
       </c>
       <c r="L92">
-        <v>56.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="E93" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F93" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G93" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -4067,7 +4123,7 @@
         <v>100</v>
       </c>
       <c r="L93">
-        <v>56.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4075,22 +4131,22 @@
         <v>21</v>
       </c>
       <c r="B94">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C94">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D94" t="s">
+        <v>86</v>
+      </c>
+      <c r="E94" t="s">
         <v>85</v>
       </c>
-      <c r="E94" t="s">
-        <v>84</v>
-      </c>
       <c r="F94" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G94" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -4102,30 +4158,30 @@
         <v>100</v>
       </c>
       <c r="L94">
-        <v>56.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B95">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="C95">
-        <v>127</v>
+        <v>42</v>
       </c>
       <c r="D95" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="E95" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F95" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G95" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -4137,30 +4193,30 @@
         <v>100</v>
       </c>
       <c r="L95">
-        <v>56.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B96">
-        <v>720</v>
+        <v>563</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E96" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F96" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G96" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -4172,30 +4228,30 @@
         <v>100</v>
       </c>
       <c r="L96">
-        <v>56.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B97">
         <v>3000000</v>
       </c>
       <c r="C97">
-        <v>985000</v>
+        <v>2658349</v>
       </c>
       <c r="D97" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="E97" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F97" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G97" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -4207,7 +4263,7 @@
         <v>100</v>
       </c>
       <c r="L97">
-        <v>56.1</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4215,22 +4271,22 @@
         <v>12</v>
       </c>
       <c r="B98">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C98">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D98" t="s">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="E98" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F98" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G98" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -4242,30 +4298,30 @@
         <v>100</v>
       </c>
       <c r="L98">
-        <v>88.6</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="E99" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F99" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G99" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -4277,7 +4333,7 @@
         <v>100</v>
       </c>
       <c r="L99">
-        <v>88.6</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4285,22 +4341,22 @@
         <v>21</v>
       </c>
       <c r="B100">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C100">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E100" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F100" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G100" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -4312,30 +4368,30 @@
         <v>100</v>
       </c>
       <c r="L100">
-        <v>88.6</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B101">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C101">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="D101" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="E101" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F101" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G101" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -4347,30 +4403,30 @@
         <v>100</v>
       </c>
       <c r="L101">
-        <v>88.6</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B102">
-        <v>375</v>
+        <v>563</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E102" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F102" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G102" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -4382,30 +4438,30 @@
         <v>100</v>
       </c>
       <c r="L102">
-        <v>88.6</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B103">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="C103">
-        <v>3056000</v>
+        <v>3084000</v>
       </c>
       <c r="D103" t="s">
+        <v>93</v>
+      </c>
+      <c r="E103" t="s">
         <v>89</v>
       </c>
-      <c r="E103" t="s">
-        <v>86</v>
-      </c>
       <c r="F103" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G103" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -4417,7 +4473,7 @@
         <v>100</v>
       </c>
       <c r="L103">
-        <v>88.6</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4428,19 +4484,19 @@
         <v>11</v>
       </c>
       <c r="C104">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D104" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E104" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F104" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G104" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -4452,30 +4508,30 @@
         <v>100</v>
       </c>
       <c r="L104">
-        <v>83.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B105">
         <v>4</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="E105" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F105" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G105" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -4487,7 +4543,7 @@
         <v>100</v>
       </c>
       <c r="L105">
-        <v>83.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4498,19 +4554,19 @@
         <v>27</v>
       </c>
       <c r="C106">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D106" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="E106" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F106" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G106" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -4522,30 +4578,30 @@
         <v>100</v>
       </c>
       <c r="L106">
-        <v>83.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B107">
         <v>36</v>
       </c>
       <c r="C107">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D107" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="E107" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F107" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G107" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -4557,12 +4613,12 @@
         <v>100</v>
       </c>
       <c r="L107">
-        <v>83.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B108">
         <v>563</v>
@@ -4571,16 +4627,16 @@
         <v>0</v>
       </c>
       <c r="D108" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E108" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F108" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G108" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -4592,30 +4648,30 @@
         <v>100</v>
       </c>
       <c r="L108">
-        <v>83.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B109">
         <v>3000000</v>
       </c>
       <c r="C109">
-        <v>2658349</v>
+        <v>0</v>
       </c>
       <c r="D109" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="E109" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F109" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G109" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -4627,7 +4683,7 @@
         <v>100</v>
       </c>
       <c r="L109">
-        <v>83.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4635,22 +4691,22 @@
         <v>12</v>
       </c>
       <c r="B110">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C110">
         <v>17</v>
       </c>
       <c r="D110" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E110" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F110" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G110" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H110" t="s">
         <v>17</v>
@@ -4662,30 +4718,30 @@
         <v>100</v>
       </c>
       <c r="L110">
-        <v>107.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B111">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="E111" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F111" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G111" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H111" t="s">
         <v>17</v>
@@ -4697,7 +4753,7 @@
         <v>100</v>
       </c>
       <c r="L111">
-        <v>107.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -4705,22 +4761,22 @@
         <v>21</v>
       </c>
       <c r="B112">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C112">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D112" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E112" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F112" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G112" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H112" t="s">
         <v>17</v>
@@ -4732,30 +4788,30 @@
         <v>100</v>
       </c>
       <c r="L112">
-        <v>107.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B113">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="C113">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="D113" t="s">
+        <v>24</v>
+      </c>
+      <c r="E113" t="s">
         <v>97</v>
       </c>
-      <c r="E113" t="s">
-        <v>94</v>
-      </c>
       <c r="F113" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G113" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H113" t="s">
         <v>17</v>
@@ -4767,30 +4823,30 @@
         <v>100</v>
       </c>
       <c r="L113">
-        <v>107.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B114">
-        <v>563</v>
+        <v>675</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E114" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F114" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G114" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H114" t="s">
         <v>17</v>
@@ -4802,31 +4858,31 @@
         <v>100</v>
       </c>
       <c r="L114">
-        <v>107.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B115">
-        <v>3000000</v>
+        <v>3375000</v>
       </c>
       <c r="C115">
-        <v>3084000</v>
+        <v>2813700</v>
       </c>
       <c r="D115" t="s">
+        <v>100</v>
+      </c>
+      <c r="E115" t="s">
+        <v>97</v>
+      </c>
+      <c r="F115" t="s">
+        <v>15</v>
+      </c>
+      <c r="G115" t="s">
         <v>98</v>
       </c>
-      <c r="E115" t="s">
-        <v>94</v>
-      </c>
-      <c r="F115" t="s">
-        <v>28</v>
-      </c>
-      <c r="G115" t="s">
-        <v>87</v>
-      </c>
       <c r="H115" t="s">
         <v>17</v>
       </c>
@@ -4837,7 +4893,7 @@
         <v>100</v>
       </c>
       <c r="L115">
-        <v>107.8</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -4845,22 +4901,22 @@
         <v>12</v>
       </c>
       <c r="B116">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D116" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="E116" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F116" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G116" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -4868,34 +4924,37 @@
       <c r="I116" t="s">
         <v>18</v>
       </c>
+      <c r="J116" t="s">
+        <v>102</v>
+      </c>
       <c r="K116">
         <v>100</v>
       </c>
       <c r="L116">
-        <v>0.9</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B117">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="E117" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F117" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G117" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H117" t="s">
         <v>17</v>
@@ -4907,7 +4966,7 @@
         <v>100</v>
       </c>
       <c r="L117">
-        <v>0.9</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -4915,22 +4974,22 @@
         <v>21</v>
       </c>
       <c r="B118">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D118" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="E118" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F118" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G118" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H118" t="s">
         <v>17</v>
@@ -4942,30 +5001,30 @@
         <v>100</v>
       </c>
       <c r="L118">
-        <v>0.9</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B119">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E119" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F119" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G119" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H119" t="s">
         <v>17</v>
@@ -4977,30 +5036,30 @@
         <v>100</v>
       </c>
       <c r="L119">
-        <v>0.9</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B120">
-        <v>563</v>
+        <v>366</v>
       </c>
       <c r="C120">
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E120" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F120" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G120" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H120" t="s">
         <v>17</v>
@@ -5012,30 +5071,30 @@
         <v>100</v>
       </c>
       <c r="L120">
-        <v>0.9</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B121">
-        <v>3000000</v>
+        <v>1827857</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>1163900</v>
       </c>
       <c r="D121" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E121" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F121" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G121" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H121" t="s">
         <v>17</v>
@@ -5047,7 +5106,7 @@
         <v>100</v>
       </c>
       <c r="L121">
-        <v>0.9</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5055,22 +5114,22 @@
         <v>12</v>
       </c>
       <c r="B122">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C122">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D122" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E122" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F122" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G122" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H122" t="s">
         <v>17</v>
@@ -5078,34 +5137,37 @@
       <c r="I122" t="s">
         <v>18</v>
       </c>
+      <c r="J122" t="s">
+        <v>106</v>
+      </c>
       <c r="K122">
         <v>100</v>
       </c>
       <c r="L122">
-        <v>67.5</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E123" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F123" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G123" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H123" t="s">
         <v>17</v>
@@ -5117,7 +5179,7 @@
         <v>100</v>
       </c>
       <c r="L123">
-        <v>67.5</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5125,22 +5187,22 @@
         <v>21</v>
       </c>
       <c r="B124">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C124">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D124" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E124" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F124" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G124" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H124" t="s">
         <v>17</v>
@@ -5152,30 +5214,30 @@
         <v>100</v>
       </c>
       <c r="L124">
-        <v>67.5</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B125">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C125">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="D125" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E125" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F125" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G125" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H125" t="s">
         <v>17</v>
@@ -5187,30 +5249,30 @@
         <v>100</v>
       </c>
       <c r="L125">
-        <v>67.5</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B126">
-        <v>675</v>
+        <v>591</v>
       </c>
       <c r="C126">
         <v>0</v>
       </c>
       <c r="D126" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E126" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F126" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G126" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H126" t="s">
         <v>17</v>
@@ -5222,30 +5284,30 @@
         <v>100</v>
       </c>
       <c r="L126">
-        <v>67.5</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B127">
-        <v>3375000</v>
+        <v>2952857</v>
       </c>
       <c r="C127">
-        <v>2813700</v>
+        <v>1717900</v>
       </c>
       <c r="D127" t="s">
+        <v>60</v>
+      </c>
+      <c r="E127" t="s">
         <v>105</v>
       </c>
-      <c r="E127" t="s">
-        <v>102</v>
-      </c>
       <c r="F127" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G127" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="H127" t="s">
         <v>17</v>
@@ -5257,7 +5319,7 @@
         <v>100</v>
       </c>
       <c r="L127">
-        <v>67.5</v>
+        <v>64.400000000000006</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5265,22 +5327,22 @@
         <v>12</v>
       </c>
       <c r="B128">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C128">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D128" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="E128" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F128" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G128" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H128" t="s">
         <v>17</v>
@@ -5289,36 +5351,36 @@
         <v>18</v>
       </c>
       <c r="J128" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K128">
         <v>100</v>
       </c>
       <c r="L128">
-        <v>42.6</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C129">
         <v>0</v>
       </c>
       <c r="D129" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E129" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F129" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G129" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H129" t="s">
         <v>17</v>
@@ -5330,7 +5392,7 @@
         <v>100</v>
       </c>
       <c r="L129">
-        <v>42.6</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5338,22 +5400,22 @@
         <v>21</v>
       </c>
       <c r="B130">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="C130">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D130" t="s">
-        <v>108</v>
+        <v>20</v>
       </c>
       <c r="E130" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F130" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G130" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H130" t="s">
         <v>17</v>
@@ -5365,30 +5427,30 @@
         <v>100</v>
       </c>
       <c r="L130">
-        <v>42.6</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B131">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C131">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D131" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F131" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G131" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H131" t="s">
         <v>17</v>
@@ -5400,30 +5462,30 @@
         <v>100</v>
       </c>
       <c r="L131">
-        <v>42.6</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B132">
-        <v>366</v>
+        <v>120</v>
       </c>
       <c r="C132">
         <v>0</v>
       </c>
       <c r="D132" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E132" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F132" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G132" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H132" t="s">
         <v>17</v>
@@ -5435,30 +5497,30 @@
         <v>100</v>
       </c>
       <c r="L132">
-        <v>42.6</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B133">
-        <v>1827857</v>
+        <v>550000</v>
       </c>
       <c r="C133">
-        <v>1163900</v>
+        <v>215000</v>
       </c>
       <c r="D133" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="E133" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F133" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G133" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H133" t="s">
         <v>17</v>
@@ -5470,7 +5532,7 @@
         <v>100</v>
       </c>
       <c r="L133">
-        <v>42.6</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5478,23 +5540,23 @@
         <v>12</v>
       </c>
       <c r="B134">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C134">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="D134" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E134" t="s">
+        <v>112</v>
+      </c>
+      <c r="F134" t="s">
+        <v>30</v>
+      </c>
+      <c r="G134" t="s">
         <v>110</v>
       </c>
-      <c r="F134" t="s">
-        <v>28</v>
-      </c>
-      <c r="G134" t="s">
-        <v>103</v>
-      </c>
       <c r="H134" t="s">
         <v>17</v>
       </c>
@@ -5502,37 +5564,37 @@
         <v>18</v>
       </c>
       <c r="J134" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K134">
         <v>100</v>
       </c>
       <c r="L134">
-        <v>64.400000000000006</v>
+        <v>93</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>19</v>
+      </c>
+      <c r="B135">
+        <v>7</v>
+      </c>
+      <c r="C135">
+        <v>7</v>
+      </c>
+      <c r="D135" t="s">
         <v>20</v>
       </c>
-      <c r="B135">
-        <v>0</v>
-      </c>
-      <c r="C135">
-        <v>1</v>
-      </c>
-      <c r="D135" t="s">
-        <v>13</v>
-      </c>
       <c r="E135" t="s">
+        <v>112</v>
+      </c>
+      <c r="F135" t="s">
+        <v>30</v>
+      </c>
+      <c r="G135" t="s">
         <v>110</v>
       </c>
-      <c r="F135" t="s">
-        <v>28</v>
-      </c>
-      <c r="G135" t="s">
-        <v>103</v>
-      </c>
       <c r="H135" t="s">
         <v>17</v>
       </c>
@@ -5543,7 +5605,7 @@
         <v>100</v>
       </c>
       <c r="L135">
-        <v>64.400000000000006</v>
+        <v>93</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5551,23 +5613,23 @@
         <v>21</v>
       </c>
       <c r="B136">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C136">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D136" t="s">
+        <v>114</v>
+      </c>
+      <c r="E136" t="s">
         <v>112</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
+        <v>30</v>
+      </c>
+      <c r="G136" t="s">
         <v>110</v>
       </c>
-      <c r="F136" t="s">
-        <v>28</v>
-      </c>
-      <c r="G136" t="s">
-        <v>103</v>
-      </c>
       <c r="H136" t="s">
         <v>17</v>
       </c>
@@ -5578,31 +5640,31 @@
         <v>100</v>
       </c>
       <c r="L136">
-        <v>64.400000000000006</v>
+        <v>93</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B137">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="C137">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E137" t="s">
+        <v>112</v>
+      </c>
+      <c r="F137" t="s">
+        <v>30</v>
+      </c>
+      <c r="G137" t="s">
         <v>110</v>
       </c>
-      <c r="F137" t="s">
-        <v>28</v>
-      </c>
-      <c r="G137" t="s">
-        <v>103</v>
-      </c>
       <c r="H137" t="s">
         <v>17</v>
       </c>
@@ -5613,31 +5675,31 @@
         <v>100</v>
       </c>
       <c r="L137">
-        <v>64.400000000000006</v>
+        <v>93</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B138">
-        <v>591</v>
+        <v>1020</v>
       </c>
       <c r="C138">
         <v>0</v>
       </c>
       <c r="D138" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E138" t="s">
+        <v>112</v>
+      </c>
+      <c r="F138" t="s">
+        <v>30</v>
+      </c>
+      <c r="G138" t="s">
         <v>110</v>
       </c>
-      <c r="F138" t="s">
-        <v>28</v>
-      </c>
-      <c r="G138" t="s">
-        <v>103</v>
-      </c>
       <c r="H138" t="s">
         <v>17</v>
       </c>
@@ -5648,31 +5710,31 @@
         <v>100</v>
       </c>
       <c r="L138">
-        <v>64.400000000000006</v>
+        <v>93</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B139">
-        <v>2952857</v>
+        <v>4675000</v>
       </c>
       <c r="C139">
-        <v>1717900</v>
+        <v>2666000</v>
       </c>
       <c r="D139" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="E139" t="s">
+        <v>112</v>
+      </c>
+      <c r="F139" t="s">
+        <v>30</v>
+      </c>
+      <c r="G139" t="s">
         <v>110</v>
       </c>
-      <c r="F139" t="s">
-        <v>28</v>
-      </c>
-      <c r="G139" t="s">
-        <v>103</v>
-      </c>
       <c r="H139" t="s">
         <v>17</v>
       </c>
@@ -5683,7 +5745,7 @@
         <v>100</v>
       </c>
       <c r="L139">
-        <v>64.400000000000006</v>
+        <v>93</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -5691,22 +5753,22 @@
         <v>12</v>
       </c>
       <c r="B140">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C140">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D140" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="E140" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F140" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G140" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H140" t="s">
         <v>17</v>
@@ -5715,36 +5777,36 @@
         <v>18</v>
       </c>
       <c r="J140" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K140">
         <v>100</v>
       </c>
       <c r="L140">
-        <v>82.3</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C141">
         <v>0</v>
       </c>
       <c r="D141" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E141" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F141" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G141" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H141" t="s">
         <v>17</v>
@@ -5756,7 +5818,7 @@
         <v>100</v>
       </c>
       <c r="L141">
-        <v>82.3</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -5764,22 +5826,22 @@
         <v>21</v>
       </c>
       <c r="B142">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C142">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D142" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E142" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F142" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G142" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H142" t="s">
         <v>17</v>
@@ -5791,30 +5853,30 @@
         <v>100</v>
       </c>
       <c r="L142">
-        <v>82.3</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B143">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C143">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D143" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E143" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F143" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G143" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H143" t="s">
         <v>17</v>
@@ -5826,30 +5888,30 @@
         <v>100</v>
       </c>
       <c r="L143">
-        <v>82.3</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B144">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="C144">
         <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E144" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F144" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G144" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H144" t="s">
         <v>17</v>
@@ -5861,30 +5923,30 @@
         <v>100</v>
       </c>
       <c r="L144">
-        <v>82.3</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B145">
-        <v>550000</v>
+        <v>275000</v>
       </c>
       <c r="C145">
-        <v>215000</v>
+        <v>0</v>
       </c>
       <c r="D145" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E145" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F145" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G145" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H145" t="s">
         <v>17</v>
@@ -5896,7 +5958,7 @@
         <v>100</v>
       </c>
       <c r="L145">
-        <v>82.3</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -5904,22 +5966,22 @@
         <v>12</v>
       </c>
       <c r="B146">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C146">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D146" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="E146" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F146" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G146" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H146" t="s">
         <v>17</v>
@@ -5927,37 +5989,34 @@
       <c r="I146" t="s">
         <v>18</v>
       </c>
-      <c r="J146" t="s">
-        <v>118</v>
-      </c>
       <c r="K146">
         <v>100</v>
       </c>
       <c r="L146">
-        <v>93</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B147">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C147">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D147" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E147" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F147" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G147" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H147" t="s">
         <v>17</v>
@@ -5969,7 +6028,7 @@
         <v>100</v>
       </c>
       <c r="L147">
-        <v>93</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -5977,22 +6036,22 @@
         <v>21</v>
       </c>
       <c r="B148">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="C148">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="E148" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F148" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G148" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H148" t="s">
         <v>17</v>
@@ -6004,30 +6063,30 @@
         <v>100</v>
       </c>
       <c r="L148">
-        <v>93</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B149">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="C149">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="D149" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E149" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F149" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G149" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H149" t="s">
         <v>17</v>
@@ -6039,30 +6098,30 @@
         <v>100</v>
       </c>
       <c r="L149">
-        <v>93</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B150">
-        <v>1020</v>
+        <v>450</v>
       </c>
       <c r="C150">
         <v>0</v>
       </c>
       <c r="D150" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E150" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F150" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G150" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H150" t="s">
         <v>17</v>
@@ -6074,30 +6133,30 @@
         <v>100</v>
       </c>
       <c r="L150">
-        <v>93</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B151">
-        <v>4675000</v>
+        <v>2062500</v>
       </c>
       <c r="C151">
-        <v>2666000</v>
+        <v>0</v>
       </c>
       <c r="D151" t="s">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="E151" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F151" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G151" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H151" t="s">
         <v>17</v>
@@ -6109,7 +6168,7 @@
         <v>100</v>
       </c>
       <c r="L151">
-        <v>93</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -6117,22 +6176,22 @@
         <v>12</v>
       </c>
       <c r="B152">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C152">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D152" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="E152" t="s">
+        <v>120</v>
+      </c>
+      <c r="F152" t="s">
+        <v>15</v>
+      </c>
+      <c r="G152" t="s">
         <v>121</v>
-      </c>
-      <c r="F152" t="s">
-        <v>28</v>
-      </c>
-      <c r="G152" t="s">
-        <v>115</v>
       </c>
       <c r="H152" t="s">
         <v>17</v>
@@ -6147,31 +6206,31 @@
         <v>100</v>
       </c>
       <c r="L152">
-        <v>14.2</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D153" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="E153" t="s">
+        <v>120</v>
+      </c>
+      <c r="F153" t="s">
+        <v>15</v>
+      </c>
+      <c r="G153" t="s">
         <v>121</v>
       </c>
-      <c r="F153" t="s">
-        <v>28</v>
-      </c>
-      <c r="G153" t="s">
-        <v>115</v>
-      </c>
       <c r="H153" t="s">
         <v>17</v>
       </c>
@@ -6182,7 +6241,7 @@
         <v>100</v>
       </c>
       <c r="L153">
-        <v>14.2</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -6190,23 +6249,23 @@
         <v>21</v>
       </c>
       <c r="B154">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D154" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="E154" t="s">
+        <v>120</v>
+      </c>
+      <c r="F154" t="s">
+        <v>15</v>
+      </c>
+      <c r="G154" t="s">
         <v>121</v>
       </c>
-      <c r="F154" t="s">
-        <v>28</v>
-      </c>
-      <c r="G154" t="s">
-        <v>115</v>
-      </c>
       <c r="H154" t="s">
         <v>17</v>
       </c>
@@ -6217,31 +6276,31 @@
         <v>100</v>
       </c>
       <c r="L154">
-        <v>14.2</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B155">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="C155">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="D155" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E155" t="s">
+        <v>120</v>
+      </c>
+      <c r="F155" t="s">
+        <v>15</v>
+      </c>
+      <c r="G155" t="s">
         <v>121</v>
       </c>
-      <c r="F155" t="s">
-        <v>28</v>
-      </c>
-      <c r="G155" t="s">
-        <v>115</v>
-      </c>
       <c r="H155" t="s">
         <v>17</v>
       </c>
@@ -6252,31 +6311,31 @@
         <v>100</v>
       </c>
       <c r="L155">
-        <v>14.2</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B156">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="C156">
         <v>0</v>
       </c>
       <c r="D156" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E156" t="s">
+        <v>120</v>
+      </c>
+      <c r="F156" t="s">
+        <v>15</v>
+      </c>
+      <c r="G156" t="s">
         <v>121</v>
       </c>
-      <c r="F156" t="s">
-        <v>28</v>
-      </c>
-      <c r="G156" t="s">
-        <v>115</v>
-      </c>
       <c r="H156" t="s">
         <v>17</v>
       </c>
@@ -6287,31 +6346,31 @@
         <v>100</v>
       </c>
       <c r="L156">
-        <v>14.2</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B157">
-        <v>275000</v>
+        <v>1650000</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>1645900</v>
       </c>
       <c r="D157" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E157" t="s">
+        <v>120</v>
+      </c>
+      <c r="F157" t="s">
+        <v>15</v>
+      </c>
+      <c r="G157" t="s">
         <v>121</v>
       </c>
-      <c r="F157" t="s">
-        <v>28</v>
-      </c>
-      <c r="G157" t="s">
-        <v>115</v>
-      </c>
       <c r="H157" t="s">
         <v>17</v>
       </c>
@@ -6322,7 +6381,7 @@
         <v>100</v>
       </c>
       <c r="L157">
-        <v>14.2</v>
+        <v>82.3</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -6330,22 +6389,22 @@
         <v>12</v>
       </c>
       <c r="B158">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D158" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="E158" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F158" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G158" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H158" t="s">
         <v>17</v>
@@ -6353,34 +6412,37 @@
       <c r="I158" t="s">
         <v>18</v>
       </c>
+      <c r="J158" t="s">
+        <v>125</v>
+      </c>
       <c r="K158">
         <v>100</v>
       </c>
       <c r="L158">
-        <v>0.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B159">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C159">
         <v>0</v>
       </c>
       <c r="D159" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E159" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F159" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G159" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H159" t="s">
         <v>17</v>
@@ -6392,7 +6454,7 @@
         <v>100</v>
       </c>
       <c r="L159">
-        <v>0.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -6400,22 +6462,22 @@
         <v>21</v>
       </c>
       <c r="B160">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D160" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E160" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F160" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G160" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H160" t="s">
         <v>17</v>
@@ -6427,30 +6489,30 @@
         <v>100</v>
       </c>
       <c r="L160">
-        <v>0.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B161">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C161">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D161" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E161" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F161" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G161" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H161" t="s">
         <v>17</v>
@@ -6462,30 +6524,30 @@
         <v>100</v>
       </c>
       <c r="L161">
-        <v>0.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B162">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="C162">
         <v>0</v>
       </c>
       <c r="D162" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E162" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F162" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G162" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H162" t="s">
         <v>17</v>
@@ -6497,30 +6559,30 @@
         <v>100</v>
       </c>
       <c r="L162">
-        <v>0.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B163">
-        <v>2062500</v>
+        <v>550000</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="D163" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="E163" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F163" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="G163" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H163" t="s">
         <v>17</v>
@@ -6532,7 +6594,7 @@
         <v>100</v>
       </c>
       <c r="L163">
-        <v>0.3</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -6540,22 +6602,22 @@
         <v>12</v>
       </c>
       <c r="B164">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C164">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D164" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="E164" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F164" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G164" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H164" t="s">
         <v>17</v>
@@ -6563,37 +6625,34 @@
       <c r="I164" t="s">
         <v>18</v>
       </c>
-      <c r="J164" t="s">
-        <v>127</v>
-      </c>
       <c r="K164">
         <v>100</v>
       </c>
       <c r="L164">
-        <v>82.3</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C165">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D165" t="s">
-        <v>128</v>
+        <v>26</v>
       </c>
       <c r="E165" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F165" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G165" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H165" t="s">
         <v>17</v>
@@ -6605,7 +6664,7 @@
         <v>100</v>
       </c>
       <c r="L165">
-        <v>82.3</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -6613,22 +6672,22 @@
         <v>21</v>
       </c>
       <c r="B166">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C166">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D166" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="E166" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F166" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G166" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H166" t="s">
         <v>17</v>
@@ -6640,30 +6699,30 @@
         <v>100</v>
       </c>
       <c r="L166">
-        <v>82.3</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B167">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="C167">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D167" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E167" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F167" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G167" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H167" t="s">
         <v>17</v>
@@ -6675,30 +6734,30 @@
         <v>100</v>
       </c>
       <c r="L167">
-        <v>82.3</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B168">
-        <v>450</v>
+        <v>900</v>
       </c>
       <c r="C168">
         <v>0</v>
       </c>
       <c r="D168" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E168" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F168" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G168" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H168" t="s">
         <v>17</v>
@@ -6710,30 +6769,30 @@
         <v>100</v>
       </c>
       <c r="L168">
-        <v>82.3</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B169">
-        <v>1650000</v>
+        <v>3300000</v>
       </c>
       <c r="C169">
-        <v>1645900</v>
+        <v>1351000</v>
       </c>
       <c r="D169" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="E169" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F169" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G169" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H169" t="s">
         <v>17</v>
@@ -6745,7 +6804,7 @@
         <v>100</v>
       </c>
       <c r="L169">
-        <v>82.3</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -6753,22 +6812,22 @@
         <v>12</v>
       </c>
       <c r="B170">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C170">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D170" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E170" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F170" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G170" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H170" t="s">
         <v>17</v>
@@ -6776,37 +6835,34 @@
       <c r="I170" t="s">
         <v>18</v>
       </c>
-      <c r="J170" t="s">
-        <v>130</v>
-      </c>
       <c r="K170">
         <v>100</v>
       </c>
       <c r="L170">
-        <v>47.6</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D171" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="E171" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F171" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G171" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H171" t="s">
         <v>17</v>
@@ -6818,7 +6874,7 @@
         <v>100</v>
       </c>
       <c r="L171">
-        <v>47.6</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -6826,22 +6882,22 @@
         <v>21</v>
       </c>
       <c r="B172">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="C172">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D172" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="E172" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F172" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G172" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H172" t="s">
         <v>17</v>
@@ -6853,30 +6909,30 @@
         <v>100</v>
       </c>
       <c r="L172">
-        <v>47.6</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B173">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="C173">
-        <v>3</v>
+        <v>145</v>
       </c>
       <c r="D173" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="E173" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F173" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G173" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H173" t="s">
         <v>17</v>
@@ -6888,30 +6944,30 @@
         <v>100</v>
       </c>
       <c r="L173">
-        <v>47.6</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B174">
-        <v>150</v>
+        <v>316</v>
       </c>
       <c r="C174">
         <v>0</v>
       </c>
       <c r="D174" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E174" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F174" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="G174" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H174" t="s">
         <v>17</v>
@@ -6923,31 +6979,31 @@
         <v>100</v>
       </c>
       <c r="L174">
-        <v>47.6</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B175">
-        <v>550000</v>
+        <v>1473088</v>
       </c>
       <c r="C175">
-        <v>200000</v>
+        <v>1110000</v>
       </c>
       <c r="D175" t="s">
+        <v>108</v>
+      </c>
+      <c r="E175" t="s">
+        <v>130</v>
+      </c>
+      <c r="F175" t="s">
+        <v>15</v>
+      </c>
+      <c r="G175" t="s">
         <v>131</v>
       </c>
-      <c r="E175" t="s">
-        <v>129</v>
-      </c>
-      <c r="F175" t="s">
-        <v>28</v>
-      </c>
-      <c r="G175" t="s">
-        <v>126</v>
-      </c>
       <c r="H175" t="s">
         <v>17</v>
       </c>
@@ -6958,7 +7014,7 @@
         <v>100</v>
       </c>
       <c r="L175">
-        <v>47.6</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -6966,22 +7022,22 @@
         <v>12</v>
       </c>
       <c r="B176">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C176">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="D176" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="E176" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F176" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G176" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H176" t="s">
         <v>17</v>
@@ -6993,30 +7049,30 @@
         <v>100</v>
       </c>
       <c r="L176">
-        <v>56.2</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B177">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D177" t="s">
-        <v>13</v>
+        <v>134</v>
       </c>
       <c r="E177" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F177" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G177" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H177" t="s">
         <v>17</v>
@@ -7028,7 +7084,7 @@
         <v>100</v>
       </c>
       <c r="L177">
-        <v>56.2</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -7036,22 +7092,22 @@
         <v>21</v>
       </c>
       <c r="B178">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C178">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="D178" t="s">
+        <v>86</v>
+      </c>
+      <c r="E178" t="s">
         <v>133</v>
       </c>
-      <c r="E178" t="s">
-        <v>132</v>
-      </c>
       <c r="F178" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G178" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H178" t="s">
         <v>17</v>
@@ -7063,30 +7119,30 @@
         <v>100</v>
       </c>
       <c r="L178">
-        <v>56.2</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B179">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="C179">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D179" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="E179" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F179" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G179" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H179" t="s">
         <v>17</v>
@@ -7098,30 +7154,30 @@
         <v>100</v>
       </c>
       <c r="L179">
-        <v>56.2</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B180">
-        <v>900</v>
+        <v>434</v>
       </c>
       <c r="C180">
         <v>0</v>
       </c>
       <c r="D180" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E180" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F180" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G180" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H180" t="s">
         <v>17</v>
@@ -7133,42 +7189,1311 @@
         <v>100</v>
       </c>
       <c r="L180">
-        <v>56.2</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>27</v>
+      </c>
+      <c r="B181">
+        <v>2024853</v>
+      </c>
+      <c r="C181">
+        <v>1156000</v>
+      </c>
+      <c r="D181" t="s">
+        <v>115</v>
+      </c>
+      <c r="E181" t="s">
+        <v>133</v>
+      </c>
+      <c r="F181" t="s">
+        <v>30</v>
+      </c>
+      <c r="G181" t="s">
+        <v>131</v>
+      </c>
+      <c r="H181" t="s">
+        <v>17</v>
+      </c>
+      <c r="I181" t="s">
+        <v>18</v>
+      </c>
+      <c r="K181">
+        <v>100</v>
+      </c>
+      <c r="L181">
+        <v>85.8</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>12</v>
+      </c>
+      <c r="B182">
+        <v>40</v>
+      </c>
+      <c r="C182">
+        <v>57</v>
+      </c>
+      <c r="D182" t="s">
+        <v>135</v>
+      </c>
+      <c r="E182" t="s">
+        <v>136</v>
+      </c>
+      <c r="F182" t="s">
+        <v>30</v>
+      </c>
+      <c r="G182" t="s">
+        <v>131</v>
+      </c>
+      <c r="H182" t="s">
+        <v>17</v>
+      </c>
+      <c r="I182" t="s">
+        <v>18</v>
+      </c>
+      <c r="K182">
+        <v>100</v>
+      </c>
+      <c r="L182">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>19</v>
+      </c>
+      <c r="B183">
+        <v>4</v>
+      </c>
+      <c r="C183">
+        <v>8</v>
+      </c>
+      <c r="D183" t="s">
+        <v>123</v>
+      </c>
+      <c r="E183" t="s">
+        <v>136</v>
+      </c>
+      <c r="F183" t="s">
+        <v>30</v>
+      </c>
+      <c r="G183" t="s">
+        <v>131</v>
+      </c>
+      <c r="H183" t="s">
+        <v>17</v>
+      </c>
+      <c r="I183" t="s">
+        <v>18</v>
+      </c>
+      <c r="K183">
+        <v>100</v>
+      </c>
+      <c r="L183">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>21</v>
+      </c>
+      <c r="B184">
+        <v>64</v>
+      </c>
+      <c r="C184">
+        <v>69</v>
+      </c>
+      <c r="D184" t="s">
+        <v>137</v>
+      </c>
+      <c r="E184" t="s">
+        <v>136</v>
+      </c>
+      <c r="F184" t="s">
+        <v>30</v>
+      </c>
+      <c r="G184" t="s">
+        <v>131</v>
+      </c>
+      <c r="H184" t="s">
+        <v>17</v>
+      </c>
+      <c r="I184" t="s">
+        <v>18</v>
+      </c>
+      <c r="K184">
+        <v>100</v>
+      </c>
+      <c r="L184">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>23</v>
+      </c>
+      <c r="B185">
+        <v>145</v>
+      </c>
+      <c r="C185">
+        <v>126</v>
+      </c>
+      <c r="D185" t="s">
+        <v>41</v>
+      </c>
+      <c r="E185" t="s">
+        <v>136</v>
+      </c>
+      <c r="F185" t="s">
+        <v>30</v>
+      </c>
+      <c r="G185" t="s">
+        <v>131</v>
+      </c>
+      <c r="H185" t="s">
+        <v>17</v>
+      </c>
+      <c r="I185" t="s">
+        <v>18</v>
+      </c>
+      <c r="K185">
+        <v>100</v>
+      </c>
+      <c r="L185">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
         <v>25</v>
       </c>
-      <c r="B181">
-        <v>3300000</v>
-      </c>
-      <c r="C181">
-        <v>1351000</v>
-      </c>
-      <c r="D181" t="s">
-        <v>134</v>
-      </c>
-      <c r="E181" t="s">
-        <v>132</v>
-      </c>
-      <c r="F181" t="s">
-        <v>28</v>
-      </c>
-      <c r="G181" t="s">
-        <v>126</v>
-      </c>
-      <c r="H181" t="s">
-        <v>17</v>
-      </c>
-      <c r="I181" t="s">
-        <v>18</v>
-      </c>
-      <c r="K181">
-        <v>100</v>
-      </c>
-      <c r="L181">
-        <v>56.2</v>
+      <c r="B186">
+        <v>434</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="D186" t="s">
+        <v>26</v>
+      </c>
+      <c r="E186" t="s">
+        <v>136</v>
+      </c>
+      <c r="F186" t="s">
+        <v>30</v>
+      </c>
+      <c r="G186" t="s">
+        <v>131</v>
+      </c>
+      <c r="H186" t="s">
+        <v>17</v>
+      </c>
+      <c r="I186" t="s">
+        <v>18</v>
+      </c>
+      <c r="K186">
+        <v>100</v>
+      </c>
+      <c r="L186">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>27</v>
+      </c>
+      <c r="B187">
+        <v>2024853</v>
+      </c>
+      <c r="C187">
+        <v>1498500</v>
+      </c>
+      <c r="D187" t="s">
+        <v>96</v>
+      </c>
+      <c r="E187" t="s">
+        <v>136</v>
+      </c>
+      <c r="F187" t="s">
+        <v>30</v>
+      </c>
+      <c r="G187" t="s">
+        <v>131</v>
+      </c>
+      <c r="H187" t="s">
+        <v>17</v>
+      </c>
+      <c r="I187" t="s">
+        <v>18</v>
+      </c>
+      <c r="K187">
+        <v>100</v>
+      </c>
+      <c r="L187">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>12</v>
+      </c>
+      <c r="B188">
+        <v>30</v>
+      </c>
+      <c r="C188">
+        <v>24</v>
+      </c>
+      <c r="D188" t="s">
+        <v>99</v>
+      </c>
+      <c r="E188" t="s">
+        <v>138</v>
+      </c>
+      <c r="F188" t="s">
+        <v>30</v>
+      </c>
+      <c r="G188" t="s">
+        <v>131</v>
+      </c>
+      <c r="H188" t="s">
+        <v>17</v>
+      </c>
+      <c r="I188" t="s">
+        <v>18</v>
+      </c>
+      <c r="J188" t="s">
+        <v>139</v>
+      </c>
+      <c r="K188">
+        <v>100</v>
+      </c>
+      <c r="L188">
+        <v>78.900000000000006</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>19</v>
+      </c>
+      <c r="B189">
+        <v>3</v>
+      </c>
+      <c r="C189">
+        <v>2</v>
+      </c>
+      <c r="D189" t="s">
+        <v>40</v>
+      </c>
+      <c r="E189" t="s">
+        <v>138</v>
+      </c>
+      <c r="F189" t="s">
+        <v>30</v>
+      </c>
+      <c r="G189" t="s">
+        <v>131</v>
+      </c>
+      <c r="H189" t="s">
+        <v>17</v>
+      </c>
+      <c r="I189" t="s">
+        <v>18</v>
+      </c>
+      <c r="K189">
+        <v>100</v>
+      </c>
+      <c r="L189">
+        <v>78.900000000000006</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>21</v>
+      </c>
+      <c r="B190">
+        <v>46</v>
+      </c>
+      <c r="C190">
+        <v>38</v>
+      </c>
+      <c r="D190" t="s">
+        <v>100</v>
+      </c>
+      <c r="E190" t="s">
+        <v>138</v>
+      </c>
+      <c r="F190" t="s">
+        <v>30</v>
+      </c>
+      <c r="G190" t="s">
+        <v>131</v>
+      </c>
+      <c r="H190" t="s">
+        <v>17</v>
+      </c>
+      <c r="I190" t="s">
+        <v>18</v>
+      </c>
+      <c r="K190">
+        <v>100</v>
+      </c>
+      <c r="L190">
+        <v>78.900000000000006</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>23</v>
+      </c>
+      <c r="B191">
+        <v>106</v>
+      </c>
+      <c r="C191">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>37</v>
+      </c>
+      <c r="E191" t="s">
+        <v>138</v>
+      </c>
+      <c r="F191" t="s">
+        <v>30</v>
+      </c>
+      <c r="G191" t="s">
+        <v>131</v>
+      </c>
+      <c r="H191" t="s">
+        <v>17</v>
+      </c>
+      <c r="I191" t="s">
+        <v>18</v>
+      </c>
+      <c r="K191">
+        <v>100</v>
+      </c>
+      <c r="L191">
+        <v>78.900000000000006</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>25</v>
+      </c>
+      <c r="B192">
+        <v>317</v>
+      </c>
+      <c r="C192">
+        <v>0</v>
+      </c>
+      <c r="D192" t="s">
+        <v>26</v>
+      </c>
+      <c r="E192" t="s">
+        <v>138</v>
+      </c>
+      <c r="F192" t="s">
+        <v>30</v>
+      </c>
+      <c r="G192" t="s">
+        <v>131</v>
+      </c>
+      <c r="H192" t="s">
+        <v>17</v>
+      </c>
+      <c r="I192" t="s">
+        <v>18</v>
+      </c>
+      <c r="K192">
+        <v>100</v>
+      </c>
+      <c r="L192">
+        <v>78.900000000000006</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>27</v>
+      </c>
+      <c r="B193">
+        <v>1477206</v>
+      </c>
+      <c r="C193">
+        <v>1668900</v>
+      </c>
+      <c r="D193" t="s">
+        <v>140</v>
+      </c>
+      <c r="E193" t="s">
+        <v>138</v>
+      </c>
+      <c r="F193" t="s">
+        <v>30</v>
+      </c>
+      <c r="G193" t="s">
+        <v>131</v>
+      </c>
+      <c r="H193" t="s">
+        <v>17</v>
+      </c>
+      <c r="I193" t="s">
+        <v>18</v>
+      </c>
+      <c r="K193">
+        <v>100</v>
+      </c>
+      <c r="L193">
+        <v>78.900000000000006</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>12</v>
+      </c>
+      <c r="B194">
+        <v>12</v>
+      </c>
+      <c r="C194">
+        <v>3</v>
+      </c>
+      <c r="D194" t="s">
+        <v>95</v>
+      </c>
+      <c r="E194" t="s">
+        <v>141</v>
+      </c>
+      <c r="F194" t="s">
+        <v>15</v>
+      </c>
+      <c r="G194" t="s">
+        <v>142</v>
+      </c>
+      <c r="H194" t="s">
+        <v>17</v>
+      </c>
+      <c r="I194" t="s">
+        <v>18</v>
+      </c>
+      <c r="J194" t="s">
+        <v>143</v>
+      </c>
+      <c r="K194">
+        <v>100</v>
+      </c>
+      <c r="L194">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>19</v>
+      </c>
+      <c r="B195">
+        <v>3</v>
+      </c>
+      <c r="C195">
+        <v>3</v>
+      </c>
+      <c r="D195" t="s">
+        <v>20</v>
+      </c>
+      <c r="E195" t="s">
+        <v>141</v>
+      </c>
+      <c r="F195" t="s">
+        <v>15</v>
+      </c>
+      <c r="G195" t="s">
+        <v>142</v>
+      </c>
+      <c r="H195" t="s">
+        <v>17</v>
+      </c>
+      <c r="I195" t="s">
+        <v>18</v>
+      </c>
+      <c r="K195">
+        <v>100</v>
+      </c>
+      <c r="L195">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>21</v>
+      </c>
+      <c r="B196">
+        <v>22</v>
+      </c>
+      <c r="C196">
+        <v>11</v>
+      </c>
+      <c r="D196" t="s">
+        <v>73</v>
+      </c>
+      <c r="E196" t="s">
+        <v>141</v>
+      </c>
+      <c r="F196" t="s">
+        <v>15</v>
+      </c>
+      <c r="G196" t="s">
+        <v>142</v>
+      </c>
+      <c r="H196" t="s">
+        <v>17</v>
+      </c>
+      <c r="I196" t="s">
+        <v>18</v>
+      </c>
+      <c r="K196">
+        <v>100</v>
+      </c>
+      <c r="L196">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>23</v>
+      </c>
+      <c r="B197">
+        <v>64</v>
+      </c>
+      <c r="C197">
+        <v>83</v>
+      </c>
+      <c r="D197" t="s">
+        <v>104</v>
+      </c>
+      <c r="E197" t="s">
+        <v>141</v>
+      </c>
+      <c r="F197" t="s">
+        <v>15</v>
+      </c>
+      <c r="G197" t="s">
+        <v>142</v>
+      </c>
+      <c r="H197" t="s">
+        <v>17</v>
+      </c>
+      <c r="I197" t="s">
+        <v>18</v>
+      </c>
+      <c r="K197">
+        <v>100</v>
+      </c>
+      <c r="L197">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>25</v>
+      </c>
+      <c r="B198">
+        <v>480</v>
+      </c>
+      <c r="C198">
+        <v>0</v>
+      </c>
+      <c r="D198" t="s">
+        <v>26</v>
+      </c>
+      <c r="E198" t="s">
+        <v>141</v>
+      </c>
+      <c r="F198" t="s">
+        <v>15</v>
+      </c>
+      <c r="G198" t="s">
+        <v>142</v>
+      </c>
+      <c r="H198" t="s">
+        <v>17</v>
+      </c>
+      <c r="I198" t="s">
+        <v>18</v>
+      </c>
+      <c r="K198">
+        <v>100</v>
+      </c>
+      <c r="L198">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>27</v>
+      </c>
+      <c r="B199">
+        <v>1200000</v>
+      </c>
+      <c r="C199">
+        <v>684000</v>
+      </c>
+      <c r="D199" t="s">
+        <v>115</v>
+      </c>
+      <c r="E199" t="s">
+        <v>141</v>
+      </c>
+      <c r="F199" t="s">
+        <v>15</v>
+      </c>
+      <c r="G199" t="s">
+        <v>142</v>
+      </c>
+      <c r="H199" t="s">
+        <v>17</v>
+      </c>
+      <c r="I199" t="s">
+        <v>18</v>
+      </c>
+      <c r="K199">
+        <v>100</v>
+      </c>
+      <c r="L199">
+        <v>52.3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>12</v>
+      </c>
+      <c r="B200">
+        <v>18</v>
+      </c>
+      <c r="C200">
+        <v>19</v>
+      </c>
+      <c r="D200" t="s">
+        <v>144</v>
+      </c>
+      <c r="E200" t="s">
+        <v>145</v>
+      </c>
+      <c r="F200" t="s">
+        <v>30</v>
+      </c>
+      <c r="G200" t="s">
+        <v>142</v>
+      </c>
+      <c r="H200" t="s">
+        <v>17</v>
+      </c>
+      <c r="I200" t="s">
+        <v>18</v>
+      </c>
+      <c r="K200">
+        <v>100</v>
+      </c>
+      <c r="L200">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>19</v>
+      </c>
+      <c r="B201">
+        <v>5</v>
+      </c>
+      <c r="C201">
+        <v>4</v>
+      </c>
+      <c r="D201" t="s">
+        <v>99</v>
+      </c>
+      <c r="E201" t="s">
+        <v>145</v>
+      </c>
+      <c r="F201" t="s">
+        <v>30</v>
+      </c>
+      <c r="G201" t="s">
+        <v>142</v>
+      </c>
+      <c r="H201" t="s">
+        <v>17</v>
+      </c>
+      <c r="I201" t="s">
+        <v>18</v>
+      </c>
+      <c r="K201">
+        <v>100</v>
+      </c>
+      <c r="L201">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>21</v>
+      </c>
+      <c r="B202">
+        <v>33</v>
+      </c>
+      <c r="C202">
+        <v>25</v>
+      </c>
+      <c r="D202" t="s">
+        <v>146</v>
+      </c>
+      <c r="E202" t="s">
+        <v>145</v>
+      </c>
+      <c r="F202" t="s">
+        <v>30</v>
+      </c>
+      <c r="G202" t="s">
+        <v>142</v>
+      </c>
+      <c r="H202" t="s">
+        <v>17</v>
+      </c>
+      <c r="I202" t="s">
+        <v>18</v>
+      </c>
+      <c r="K202">
+        <v>100</v>
+      </c>
+      <c r="L202">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>23</v>
+      </c>
+      <c r="B203">
+        <v>96</v>
+      </c>
+      <c r="C203">
+        <v>90</v>
+      </c>
+      <c r="D203" t="s">
+        <v>83</v>
+      </c>
+      <c r="E203" t="s">
+        <v>145</v>
+      </c>
+      <c r="F203" t="s">
+        <v>30</v>
+      </c>
+      <c r="G203" t="s">
+        <v>142</v>
+      </c>
+      <c r="H203" t="s">
+        <v>17</v>
+      </c>
+      <c r="I203" t="s">
+        <v>18</v>
+      </c>
+      <c r="K203">
+        <v>100</v>
+      </c>
+      <c r="L203">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>25</v>
+      </c>
+      <c r="B204">
+        <v>720</v>
+      </c>
+      <c r="C204">
+        <v>0</v>
+      </c>
+      <c r="D204" t="s">
+        <v>26</v>
+      </c>
+      <c r="E204" t="s">
+        <v>145</v>
+      </c>
+      <c r="F204" t="s">
+        <v>30</v>
+      </c>
+      <c r="G204" t="s">
+        <v>142</v>
+      </c>
+      <c r="H204" t="s">
+        <v>17</v>
+      </c>
+      <c r="I204" t="s">
+        <v>18</v>
+      </c>
+      <c r="K204">
+        <v>100</v>
+      </c>
+      <c r="L204">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>27</v>
+      </c>
+      <c r="B205">
+        <v>1800000</v>
+      </c>
+      <c r="C205">
+        <v>553000</v>
+      </c>
+      <c r="D205" t="s">
+        <v>52</v>
+      </c>
+      <c r="E205" t="s">
+        <v>145</v>
+      </c>
+      <c r="F205" t="s">
+        <v>30</v>
+      </c>
+      <c r="G205" t="s">
+        <v>142</v>
+      </c>
+      <c r="H205" t="s">
+        <v>17</v>
+      </c>
+      <c r="I205" t="s">
+        <v>18</v>
+      </c>
+      <c r="K205">
+        <v>100</v>
+      </c>
+      <c r="L205">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>12</v>
+      </c>
+      <c r="B206">
+        <v>2</v>
+      </c>
+      <c r="C206">
+        <v>3</v>
+      </c>
+      <c r="D206" t="s">
+        <v>90</v>
+      </c>
+      <c r="E206" t="s">
+        <v>147</v>
+      </c>
+      <c r="F206" t="s">
+        <v>15</v>
+      </c>
+      <c r="G206" t="s">
+        <v>148</v>
+      </c>
+      <c r="H206" t="s">
+        <v>17</v>
+      </c>
+      <c r="I206" t="s">
+        <v>18</v>
+      </c>
+      <c r="J206" t="s">
+        <v>149</v>
+      </c>
+      <c r="K206">
+        <v>100</v>
+      </c>
+      <c r="L206">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>19</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+      <c r="C207">
+        <v>0</v>
+      </c>
+      <c r="D207" t="s">
+        <v>26</v>
+      </c>
+      <c r="E207" t="s">
+        <v>147</v>
+      </c>
+      <c r="F207" t="s">
+        <v>15</v>
+      </c>
+      <c r="G207" t="s">
+        <v>148</v>
+      </c>
+      <c r="H207" t="s">
+        <v>17</v>
+      </c>
+      <c r="I207" t="s">
+        <v>18</v>
+      </c>
+      <c r="K207">
+        <v>100</v>
+      </c>
+      <c r="L207">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>21</v>
+      </c>
+      <c r="B208">
+        <v>11</v>
+      </c>
+      <c r="C208">
+        <v>13</v>
+      </c>
+      <c r="D208" t="s">
+        <v>150</v>
+      </c>
+      <c r="E208" t="s">
+        <v>147</v>
+      </c>
+      <c r="F208" t="s">
+        <v>15</v>
+      </c>
+      <c r="G208" t="s">
+        <v>148</v>
+      </c>
+      <c r="H208" t="s">
+        <v>17</v>
+      </c>
+      <c r="I208" t="s">
+        <v>18</v>
+      </c>
+      <c r="K208">
+        <v>100</v>
+      </c>
+      <c r="L208">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>23</v>
+      </c>
+      <c r="B209">
+        <v>11</v>
+      </c>
+      <c r="C209">
+        <v>6</v>
+      </c>
+      <c r="D209" t="s">
+        <v>24</v>
+      </c>
+      <c r="E209" t="s">
+        <v>147</v>
+      </c>
+      <c r="F209" t="s">
+        <v>15</v>
+      </c>
+      <c r="G209" t="s">
+        <v>148</v>
+      </c>
+      <c r="H209" t="s">
+        <v>17</v>
+      </c>
+      <c r="I209" t="s">
+        <v>18</v>
+      </c>
+      <c r="K209">
+        <v>100</v>
+      </c>
+      <c r="L209">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>25</v>
+      </c>
+      <c r="B210">
+        <v>120</v>
+      </c>
+      <c r="C210">
+        <v>0</v>
+      </c>
+      <c r="D210" t="s">
+        <v>26</v>
+      </c>
+      <c r="E210" t="s">
+        <v>147</v>
+      </c>
+      <c r="F210" t="s">
+        <v>15</v>
+      </c>
+      <c r="G210" t="s">
+        <v>148</v>
+      </c>
+      <c r="H210" t="s">
+        <v>17</v>
+      </c>
+      <c r="I210" t="s">
+        <v>18</v>
+      </c>
+      <c r="K210">
+        <v>100</v>
+      </c>
+      <c r="L210">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>27</v>
+      </c>
+      <c r="B211">
+        <v>600000</v>
+      </c>
+      <c r="C211">
+        <v>739000</v>
+      </c>
+      <c r="D211" t="s">
+        <v>151</v>
+      </c>
+      <c r="E211" t="s">
+        <v>147</v>
+      </c>
+      <c r="F211" t="s">
+        <v>15</v>
+      </c>
+      <c r="G211" t="s">
+        <v>148</v>
+      </c>
+      <c r="H211" t="s">
+        <v>17</v>
+      </c>
+      <c r="I211" t="s">
+        <v>18</v>
+      </c>
+      <c r="K211">
+        <v>100</v>
+      </c>
+      <c r="L211">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>12</v>
+      </c>
+      <c r="B212">
+        <v>13</v>
+      </c>
+      <c r="C212">
+        <v>11</v>
+      </c>
+      <c r="D212" t="s">
+        <v>152</v>
+      </c>
+      <c r="E212" t="s">
+        <v>153</v>
+      </c>
+      <c r="F212" t="s">
+        <v>30</v>
+      </c>
+      <c r="G212" t="s">
+        <v>148</v>
+      </c>
+      <c r="H212" t="s">
+        <v>17</v>
+      </c>
+      <c r="I212" t="s">
+        <v>18</v>
+      </c>
+      <c r="K212">
+        <v>100</v>
+      </c>
+      <c r="L212">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>19</v>
+      </c>
+      <c r="B213">
+        <v>1</v>
+      </c>
+      <c r="C213">
+        <v>1</v>
+      </c>
+      <c r="D213" t="s">
+        <v>20</v>
+      </c>
+      <c r="E213" t="s">
+        <v>153</v>
+      </c>
+      <c r="F213" t="s">
+        <v>30</v>
+      </c>
+      <c r="G213" t="s">
+        <v>148</v>
+      </c>
+      <c r="H213" t="s">
+        <v>17</v>
+      </c>
+      <c r="I213" t="s">
+        <v>18</v>
+      </c>
+      <c r="K213">
+        <v>100</v>
+      </c>
+      <c r="L213">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>21</v>
+      </c>
+      <c r="B214">
+        <v>64</v>
+      </c>
+      <c r="C214">
+        <v>41</v>
+      </c>
+      <c r="D214" t="s">
+        <v>37</v>
+      </c>
+      <c r="E214" t="s">
+        <v>153</v>
+      </c>
+      <c r="F214" t="s">
+        <v>30</v>
+      </c>
+      <c r="G214" t="s">
+        <v>148</v>
+      </c>
+      <c r="H214" t="s">
+        <v>17</v>
+      </c>
+      <c r="I214" t="s">
+        <v>18</v>
+      </c>
+      <c r="K214">
+        <v>100</v>
+      </c>
+      <c r="L214">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>23</v>
+      </c>
+      <c r="B215">
+        <v>60</v>
+      </c>
+      <c r="C215">
+        <v>57</v>
+      </c>
+      <c r="D215" t="s">
+        <v>24</v>
+      </c>
+      <c r="E215" t="s">
+        <v>153</v>
+      </c>
+      <c r="F215" t="s">
+        <v>30</v>
+      </c>
+      <c r="G215" t="s">
+        <v>148</v>
+      </c>
+      <c r="H215" t="s">
+        <v>17</v>
+      </c>
+      <c r="I215" t="s">
+        <v>18</v>
+      </c>
+      <c r="K215">
+        <v>100</v>
+      </c>
+      <c r="L215">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>25</v>
+      </c>
+      <c r="B216">
+        <v>680</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216" t="s">
+        <v>26</v>
+      </c>
+      <c r="E216" t="s">
+        <v>153</v>
+      </c>
+      <c r="F216" t="s">
+        <v>30</v>
+      </c>
+      <c r="G216" t="s">
+        <v>148</v>
+      </c>
+      <c r="H216" t="s">
+        <v>17</v>
+      </c>
+      <c r="I216" t="s">
+        <v>18</v>
+      </c>
+      <c r="K216">
+        <v>100</v>
+      </c>
+      <c r="L216">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>27</v>
+      </c>
+      <c r="B217">
+        <v>3400000</v>
+      </c>
+      <c r="C217">
+        <v>2229800</v>
+      </c>
+      <c r="D217" t="s">
+        <v>154</v>
+      </c>
+      <c r="E217" t="s">
+        <v>153</v>
+      </c>
+      <c r="F217" t="s">
+        <v>30</v>
+      </c>
+      <c r="G217" t="s">
+        <v>148</v>
+      </c>
+      <c r="H217" t="s">
+        <v>17</v>
+      </c>
+      <c r="I217" t="s">
+        <v>18</v>
+      </c>
+      <c r="K217">
+        <v>100</v>
+      </c>
+      <c r="L217">
+        <v>61.3</v>
       </c>
     </row>
   </sheetData>
